--- a/output/latest/SIFA_DATA_latest.xlsx
+++ b/output/latest/SIFA_DATA_latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:MM19"/>
+  <dimension ref="A1:MM11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3923,1706 +3923,1706 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2022-Q1</t>
+          <t>2024-Q1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-10046.39</v>
+        <v>-2846.84</v>
       </c>
       <c r="C3" t="n">
-        <v>-2838.57</v>
+        <v>10436.47</v>
       </c>
       <c r="D3" t="n">
-        <v>-1605.31</v>
+        <v>-1270.42</v>
       </c>
       <c r="E3" t="n">
-        <v>4952.09</v>
+        <v>4101.86</v>
       </c>
       <c r="F3" t="n">
-        <v>-8846.360000000001</v>
+        <v>-10013.14</v>
       </c>
       <c r="G3" t="n">
-        <v>-6206.61</v>
+        <v>14230.73</v>
       </c>
       <c r="H3" t="n">
-        <v>121.94</v>
+        <v>486.72</v>
       </c>
       <c r="I3" t="n">
-        <v>-8335.84</v>
+        <v>8888.570000000011</v>
       </c>
       <c r="J3" t="n">
-        <v>-3002.02</v>
+        <v>773.6599999999989</v>
       </c>
       <c r="K3" t="n">
-        <v>-35807.07</v>
+        <v>24787.61</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-7542.57</v>
+        <v>-948.4900000000021</v>
       </c>
       <c r="BA3" t="n">
-        <v>-3832.76</v>
+        <v>9851.450000000001</v>
       </c>
       <c r="BB3" t="n">
-        <v>-1637.24</v>
+        <v>-938.16</v>
       </c>
       <c r="BC3" t="n">
-        <v>-1449.74</v>
+        <v>4432.07</v>
       </c>
       <c r="BD3" t="n">
-        <v>-9121.540000000001</v>
+        <v>-3407.28</v>
       </c>
       <c r="BE3" t="n">
-        <v>-2375.63</v>
+        <v>19193.36</v>
       </c>
       <c r="BF3" t="n">
-        <v>-426.11</v>
+        <v>263.81</v>
       </c>
       <c r="BG3" t="n">
-        <v>-7114.16</v>
+        <v>6591.02</v>
       </c>
       <c r="BH3" t="n">
-        <v>-787.73</v>
+        <v>-155.790000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>-34287.48</v>
+        <v>34881.99</v>
       </c>
       <c r="CX3" t="n">
-        <v>-1207.53</v>
+        <v>-1024.35</v>
       </c>
       <c r="CY3" t="n">
-        <v>33.21</v>
+        <v>71.14999999999959</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-187.88</v>
+        <v>-202.73</v>
       </c>
       <c r="DA3" t="n">
-        <v>-2340.13</v>
+        <v>-2287.96</v>
       </c>
       <c r="DB3" t="n">
-        <v>-2150.45</v>
+        <v>-3048.73</v>
       </c>
       <c r="DC3" t="n">
-        <v>-695.61</v>
+        <v>-345.5</v>
       </c>
       <c r="DD3" t="n">
-        <v>433.53</v>
+        <v>107.09</v>
       </c>
       <c r="DE3" t="n">
-        <v>-1358.95</v>
+        <v>-432.839999999998</v>
       </c>
       <c r="DF3" t="n">
-        <v>227.52</v>
+        <v>-635.65</v>
       </c>
       <c r="DG3" t="n">
-        <v>-7246.29</v>
+        <v>-7799.52</v>
       </c>
       <c r="EV3" t="n">
-        <v>-769.66</v>
+        <v>390.27</v>
       </c>
       <c r="EW3" t="n">
-        <v>916.09</v>
+        <v>1680.87</v>
       </c>
       <c r="EX3" t="n">
-        <v>45.4</v>
+        <v>-59.9</v>
       </c>
       <c r="EY3" t="n">
-        <v>2986.24</v>
+        <v>4599.73</v>
       </c>
       <c r="EZ3" t="n">
-        <v>196.2</v>
+        <v>-2129.56</v>
       </c>
       <c r="FA3" t="n">
-        <v>-5432.46</v>
+        <v>-1226.1</v>
       </c>
       <c r="FB3" t="n">
-        <v>46.36</v>
+        <v>614.16</v>
       </c>
       <c r="FC3" t="n">
-        <v>-587.92</v>
+        <v>4184.94</v>
       </c>
       <c r="FD3" t="n">
-        <v>-1726.26</v>
+        <v>2313.61</v>
       </c>
       <c r="FE3" t="n">
-        <v>-4326.01</v>
+        <v>10368.02</v>
       </c>
       <c r="GT3" t="n">
-        <v>-719.84</v>
+        <v>-875.0900000000011</v>
       </c>
       <c r="GU3" t="n">
-        <v>-152.48</v>
+        <v>-90.78</v>
       </c>
       <c r="GV3" t="n">
-        <v>175.73</v>
+        <v>-61.5</v>
       </c>
       <c r="GW3" t="n">
-        <v>5704.44</v>
+        <v>-2558.44</v>
       </c>
       <c r="GX3" t="n">
-        <v>2207.66</v>
+        <v>-1391.51</v>
       </c>
       <c r="GY3" t="n">
-        <v>2390.51</v>
+        <v>-3375.92</v>
       </c>
       <c r="GZ3" t="n">
-        <v>-195.78</v>
+        <v>-306.15</v>
       </c>
       <c r="HA3" t="n">
-        <v>-319.06</v>
+        <v>-657.019999999999</v>
       </c>
       <c r="HB3" t="n">
-        <v>-952.66</v>
+        <v>-623.5599999999999</v>
       </c>
       <c r="HC3" t="n">
-        <v>8138.52</v>
+        <v>-9939.969999999999</v>
       </c>
       <c r="IR3" t="n">
-        <v>116.85</v>
+        <v>-173.68</v>
       </c>
       <c r="IS3" t="n">
-        <v>204.25</v>
+        <v>-1075.71</v>
       </c>
       <c r="IT3" t="n">
-        <v>-0.33</v>
+        <v>-7.36</v>
       </c>
       <c r="IU3" t="n">
-        <v>64.75</v>
+        <v>-80.04000000000001</v>
       </c>
       <c r="IV3" t="n">
-        <v>21.77</v>
+        <v>-36.06</v>
       </c>
       <c r="IW3" t="n">
-        <v>-193.83</v>
+        <v>-15.42</v>
       </c>
       <c r="IX3" t="n">
-        <v>13.64</v>
+        <v>-196.03</v>
       </c>
       <c r="IY3" t="n">
-        <v>398.74</v>
+        <v>-1162.39</v>
       </c>
       <c r="IZ3" t="n">
-        <v>109.3</v>
+        <v>-117</v>
       </c>
       <c r="JA3" t="n">
-        <v>735.14</v>
+        <v>-2863.69</v>
       </c>
       <c r="KP3" t="n">
-        <v>76.36</v>
+        <v>-215.5</v>
       </c>
       <c r="KQ3" t="n">
-        <v>-6.88</v>
+        <v>-0.51</v>
       </c>
       <c r="KR3" t="n">
-        <v>-0.99</v>
+        <v>-0.77</v>
       </c>
       <c r="KS3" t="n">
-        <v>-13.47</v>
+        <v>-3.5</v>
       </c>
       <c r="KT3" t="n">
         <v>0</v>
       </c>
       <c r="KU3" t="n">
-        <v>100.41</v>
+        <v>0.31</v>
       </c>
       <c r="KV3" t="n">
-        <v>250.3</v>
+        <v>3.84</v>
       </c>
       <c r="KW3" t="n">
-        <v>645.51</v>
+        <v>364.86</v>
       </c>
       <c r="KX3" t="n">
-        <v>127.81</v>
+        <v>-7.94999999999999</v>
       </c>
       <c r="KY3" t="n">
-        <v>1179.05</v>
+        <v>140.78</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2022-Q2</t>
+          <t>2024-Q2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-2081.96</v>
+        <v>-2604.05</v>
       </c>
       <c r="C4" t="n">
-        <v>1732.76</v>
+        <v>5805.8</v>
       </c>
       <c r="D4" t="n">
-        <v>-1259.69</v>
+        <v>-1159.05</v>
       </c>
       <c r="E4" t="n">
-        <v>5172.03</v>
+        <v>10616.64</v>
       </c>
       <c r="F4" t="n">
-        <v>2898.5</v>
+        <v>3856.92</v>
       </c>
       <c r="G4" t="n">
-        <v>1586.63</v>
+        <v>22212.95</v>
       </c>
       <c r="H4" t="n">
-        <v>175.22</v>
+        <v>1058.41</v>
       </c>
       <c r="I4" t="n">
-        <v>-8825.51</v>
+        <v>9432.750000000009</v>
       </c>
       <c r="J4" t="n">
-        <v>-1348.57</v>
+        <v>5075.74</v>
       </c>
       <c r="K4" t="n">
-        <v>-1950.59</v>
+        <v>54296.11</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-743.73</v>
+        <v>-1794.31</v>
       </c>
       <c r="BA4" t="n">
-        <v>-1229.29</v>
+        <v>4982.56</v>
       </c>
       <c r="BB4" t="n">
-        <v>-936.1900000000001</v>
+        <v>-925.76</v>
       </c>
       <c r="BC4" t="n">
-        <v>5304.49</v>
+        <v>8908.57</v>
       </c>
       <c r="BD4" t="n">
-        <v>-2491.27</v>
+        <v>3517.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>808.26</v>
+        <v>17350.57</v>
       </c>
       <c r="BF4" t="n">
-        <v>-1187.44</v>
+        <v>-445.64</v>
       </c>
       <c r="BG4" t="n">
-        <v>-1035.51</v>
+        <v>3293.09</v>
       </c>
       <c r="BH4" t="n">
-        <v>-1831.76</v>
+        <v>415.979999999998</v>
       </c>
       <c r="BI4" t="n">
-        <v>-3342.44</v>
+        <v>35302.86</v>
       </c>
       <c r="CX4" t="n">
-        <v>-928.34</v>
+        <v>-1360.41</v>
       </c>
       <c r="CY4" t="n">
-        <v>873.65</v>
+        <v>-267.119999999999</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-280.64</v>
+        <v>-153.33</v>
       </c>
       <c r="DA4" t="n">
-        <v>-1170.01</v>
+        <v>-1934.01</v>
       </c>
       <c r="DB4" t="n">
-        <v>992.29</v>
+        <v>347.53</v>
       </c>
       <c r="DC4" t="n">
-        <v>44.62</v>
+        <v>-247.95</v>
       </c>
       <c r="DD4" t="n">
-        <v>270.66</v>
+        <v>323.78</v>
       </c>
       <c r="DE4" t="n">
-        <v>-515.15</v>
+        <v>-411.089999999999</v>
       </c>
       <c r="DF4" t="n">
-        <v>1448.05</v>
+        <v>-124.7</v>
       </c>
       <c r="DG4" t="n">
-        <v>735.13</v>
+        <v>-3827.3</v>
       </c>
       <c r="EV4" t="n">
-        <v>-835.5599999999999</v>
+        <v>549.310000000001</v>
       </c>
       <c r="EW4" t="n">
-        <v>-7.25</v>
+        <v>950.629999999999</v>
       </c>
       <c r="EX4" t="n">
-        <v>-94.06</v>
+        <v>-43.82</v>
       </c>
       <c r="EY4" t="n">
-        <v>468.8</v>
+        <v>3875.55</v>
       </c>
       <c r="EZ4" t="n">
-        <v>-999.75</v>
+        <v>75.48</v>
       </c>
       <c r="FA4" t="n">
-        <v>-1467.74</v>
+        <v>1324.45</v>
       </c>
       <c r="FB4" t="n">
-        <v>-148.33</v>
+        <v>900.29</v>
       </c>
       <c r="FC4" t="n">
-        <v>-2808.03</v>
+        <v>5331.06</v>
       </c>
       <c r="FD4" t="n">
-        <v>-1805.46</v>
+        <v>4020.53</v>
       </c>
       <c r="FE4" t="n">
-        <v>-7697.38</v>
+        <v>16983.48</v>
       </c>
       <c r="GT4" t="n">
-        <v>-723.63</v>
+        <v>-27.9699999999996</v>
       </c>
       <c r="GU4" t="n">
-        <v>167.2</v>
+        <v>385.44</v>
       </c>
       <c r="GV4" t="n">
-        <v>30.24</v>
+        <v>-29.82</v>
       </c>
       <c r="GW4" t="n">
-        <v>481.18</v>
+        <v>-193.440000000001</v>
       </c>
       <c r="GX4" t="n">
-        <v>758.77</v>
+        <v>-78.72</v>
       </c>
       <c r="GY4" t="n">
-        <v>1443.32</v>
+        <v>3864.63</v>
       </c>
       <c r="GZ4" t="n">
-        <v>406.51</v>
+        <v>35.55</v>
       </c>
       <c r="HA4" t="n">
-        <v>-6640.89</v>
+        <v>1458.74</v>
       </c>
       <c r="HB4" t="n">
-        <v>710.52</v>
+        <v>793.5700000000001</v>
       </c>
       <c r="HC4" t="n">
-        <v>-3366.78</v>
+        <v>6207.98</v>
       </c>
       <c r="IR4" t="n">
-        <v>246.77</v>
+        <v>-30.11</v>
       </c>
       <c r="IS4" t="n">
-        <v>1928.78</v>
+        <v>-245.54</v>
       </c>
       <c r="IT4" t="n">
-        <v>21.55</v>
+        <v>-5.98</v>
       </c>
       <c r="IU4" t="n">
-        <v>90.53</v>
+        <v>-56.27</v>
       </c>
       <c r="IV4" t="n">
-        <v>4638.46</v>
+        <v>-5.17</v>
       </c>
       <c r="IW4" t="n">
-        <v>646.91</v>
+        <v>-78</v>
       </c>
       <c r="IX4" t="n">
-        <v>452.76</v>
+        <v>-42.74</v>
       </c>
       <c r="IY4" t="n">
-        <v>1951.14</v>
+        <v>-40.8800000000001</v>
       </c>
       <c r="IZ4" t="n">
-        <v>135.43</v>
+        <v>5</v>
       </c>
       <c r="JA4" t="n">
-        <v>10112.33</v>
+        <v>-499.69</v>
       </c>
       <c r="KP4" t="n">
-        <v>902.53</v>
+        <v>59.44</v>
       </c>
       <c r="KQ4" t="n">
-        <v>-0.33</v>
+        <v>-0.17</v>
       </c>
       <c r="KR4" t="n">
-        <v>-0.59</v>
+        <v>-0.34</v>
       </c>
       <c r="KS4" t="n">
-        <v>-2.96</v>
+        <v>16.24</v>
       </c>
       <c r="KT4" t="n">
         <v>0</v>
       </c>
       <c r="KU4" t="n">
-        <v>111.26</v>
+        <v>-0.75</v>
       </c>
       <c r="KV4" t="n">
-        <v>381.06</v>
+        <v>287.17</v>
       </c>
       <c r="KW4" t="n">
-        <v>222.93</v>
+        <v>-198.17</v>
       </c>
       <c r="KX4" t="n">
-        <v>-5.35</v>
+        <v>-34.64</v>
       </c>
       <c r="KY4" t="n">
-        <v>1608.55</v>
+        <v>128.78</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2022-Q3</t>
+          <t>2024-Q3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-3173.67</v>
+        <v>-4922.61</v>
       </c>
       <c r="C5" t="n">
-        <v>3577.19</v>
+        <v>8729.84</v>
       </c>
       <c r="D5" t="n">
-        <v>-1070.25</v>
+        <v>-1240.2</v>
       </c>
       <c r="E5" t="n">
-        <v>13629.65</v>
+        <v>13416.36</v>
       </c>
       <c r="F5" t="n">
-        <v>-7683.5</v>
+        <v>-10221.19</v>
       </c>
       <c r="G5" t="n">
-        <v>4048.13</v>
+        <v>12281.74</v>
       </c>
       <c r="H5" t="n">
-        <v>1739.59</v>
+        <v>-917.959999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-7280.58</v>
+        <v>10556.36</v>
       </c>
       <c r="J5" t="n">
-        <v>3827.32</v>
+        <v>7752.66</v>
       </c>
       <c r="K5" t="n">
-        <v>7613.88</v>
+        <v>35435</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-1891.46</v>
+        <v>-4864.27</v>
       </c>
       <c r="BA5" t="n">
-        <v>1441.27</v>
+        <v>6161.11</v>
       </c>
       <c r="BB5" t="n">
-        <v>-641.96</v>
+        <v>-936.16</v>
       </c>
       <c r="BC5" t="n">
-        <v>8035.67</v>
+        <v>8533.73</v>
       </c>
       <c r="BD5" t="n">
-        <v>-1683.47</v>
+        <v>-7266.41</v>
       </c>
       <c r="BE5" t="n">
-        <v>5159.39</v>
+        <v>8161.25</v>
       </c>
       <c r="BF5" t="n">
-        <v>412.69</v>
+        <v>-960.45</v>
       </c>
       <c r="BG5" t="n">
-        <v>-10874.86</v>
+        <v>5021.31999999999</v>
       </c>
       <c r="BH5" t="n">
-        <v>1003.11</v>
+        <v>2278.27</v>
       </c>
       <c r="BI5" t="n">
-        <v>960.38</v>
+        <v>16128.39</v>
       </c>
       <c r="CX5" t="n">
-        <v>-150.05</v>
+        <v>-784.2599999999979</v>
       </c>
       <c r="CY5" t="n">
-        <v>1110.89</v>
+        <v>798.219999999999</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-343.81</v>
+        <v>-309.41</v>
       </c>
       <c r="DA5" t="n">
-        <v>399.01</v>
+        <v>-619.250000000001</v>
       </c>
       <c r="DB5" t="n">
-        <v>-885.3200000000001</v>
+        <v>-2511.12</v>
       </c>
       <c r="DC5" t="n">
-        <v>77.31999999999999</v>
+        <v>507.29</v>
       </c>
       <c r="DD5" t="n">
-        <v>44.3</v>
+        <v>49.96</v>
       </c>
       <c r="DE5" t="n">
-        <v>-85.16</v>
+        <v>600.9900000000021</v>
       </c>
       <c r="DF5" t="n">
-        <v>153.73</v>
+        <v>-209.12</v>
       </c>
       <c r="DG5" t="n">
-        <v>320.91</v>
+        <v>-2476.7</v>
       </c>
       <c r="EV5" t="n">
-        <v>-526.36</v>
+        <v>630.7899999999991</v>
       </c>
       <c r="EW5" t="n">
-        <v>176.81</v>
+        <v>928.05</v>
       </c>
       <c r="EX5" t="n">
-        <v>-58.09</v>
+        <v>-4.56</v>
       </c>
       <c r="EY5" t="n">
-        <v>1337.29</v>
+        <v>3371.11</v>
       </c>
       <c r="EZ5" t="n">
-        <v>-1233.86</v>
+        <v>-648.85</v>
       </c>
       <c r="FA5" t="n">
-        <v>402.31</v>
+        <v>2425.04</v>
       </c>
       <c r="FB5" t="n">
-        <v>647.45</v>
+        <v>-404.48</v>
       </c>
       <c r="FC5" t="n">
-        <v>1945.01</v>
+        <v>-1187.02</v>
       </c>
       <c r="FD5" t="n">
-        <v>1959.22</v>
+        <v>4799.91</v>
       </c>
       <c r="FE5" t="n">
-        <v>4649.78</v>
+        <v>9909.99</v>
       </c>
       <c r="GT5" t="n">
-        <v>-587.15</v>
+        <v>25.55</v>
       </c>
       <c r="GU5" t="n">
-        <v>33.93</v>
+        <v>430.5</v>
       </c>
       <c r="GV5" t="n">
-        <v>-26.01</v>
+        <v>16.38</v>
       </c>
       <c r="GW5" t="n">
-        <v>3767.5</v>
+        <v>2059.91</v>
       </c>
       <c r="GX5" t="n">
-        <v>-151.75</v>
+        <v>218.94</v>
       </c>
       <c r="GY5" t="n">
-        <v>-1135.58</v>
+        <v>1182.4</v>
       </c>
       <c r="GZ5" t="n">
-        <v>587.4</v>
+        <v>294.7</v>
       </c>
       <c r="HA5" t="n">
-        <v>1583.29</v>
+        <v>5306.95</v>
       </c>
       <c r="HB5" t="n">
-        <v>512.3099999999999</v>
+        <v>796.34</v>
       </c>
       <c r="HC5" t="n">
-        <v>4583.94</v>
+        <v>10331.67</v>
       </c>
       <c r="IR5" t="n">
-        <v>19.9</v>
+        <v>48.9499999999998</v>
       </c>
       <c r="IS5" t="n">
-        <v>813.35</v>
+        <v>410.6</v>
       </c>
       <c r="IT5" t="n">
-        <v>0.03</v>
+        <v>-5.86</v>
       </c>
       <c r="IU5" t="n">
-        <v>102.96</v>
+        <v>32.08</v>
       </c>
       <c r="IV5" t="n">
-        <v>-3729.1</v>
+        <v>-13.75</v>
       </c>
       <c r="IW5" t="n">
-        <v>-465.68</v>
+        <v>6.61</v>
       </c>
       <c r="IX5" t="n">
-        <v>47.76</v>
+        <v>102.49</v>
       </c>
       <c r="IY5" t="n">
-        <v>415.36</v>
+        <v>530.8099999999999</v>
       </c>
       <c r="IZ5" t="n">
-        <v>168.25</v>
+        <v>5.75</v>
       </c>
       <c r="JA5" t="n">
-        <v>-2627.17</v>
+        <v>1117.68</v>
       </c>
       <c r="KP5" t="n">
-        <v>-38.55</v>
+        <v>20.63</v>
       </c>
       <c r="KQ5" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.36</v>
       </c>
       <c r="KR5" t="n">
-        <v>-0.41</v>
+        <v>-0.59</v>
       </c>
       <c r="KS5" t="n">
-        <v>-12.78</v>
+        <v>38.78</v>
       </c>
       <c r="KT5" t="n">
         <v>0</v>
       </c>
       <c r="KU5" t="n">
-        <v>10.37</v>
+        <v>-0.85</v>
       </c>
       <c r="KV5" t="n">
-        <v>-0.01</v>
+        <v>-0.18</v>
       </c>
       <c r="KW5" t="n">
-        <v>-264.22</v>
+        <v>283.31</v>
       </c>
       <c r="KX5" t="n">
-        <v>30.7</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="KY5" t="n">
-        <v>-273.96</v>
+        <v>423.97</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2022-Q4</t>
+          <t>2024-Q4</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-4984.43</v>
+        <v>-9229.290000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>6153.41</v>
+        <v>22625.23</v>
       </c>
       <c r="D6" t="n">
-        <v>-1177.74</v>
+        <v>-1909.67</v>
       </c>
       <c r="E6" t="n">
-        <v>14014.75</v>
+        <v>7143.34</v>
       </c>
       <c r="F6" t="n">
-        <v>38679.05</v>
+        <v>33560.91</v>
       </c>
       <c r="G6" t="n">
-        <v>874.01</v>
+        <v>8727.379999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>179.07</v>
+        <v>535.17</v>
       </c>
       <c r="I6" t="n">
-        <v>1568.77</v>
+        <v>15436.3</v>
       </c>
       <c r="J6" t="n">
-        <v>-679.34</v>
+        <v>10491.97</v>
       </c>
       <c r="K6" t="n">
-        <v>54627.55</v>
+        <v>87381.34</v>
       </c>
       <c r="L6" t="n">
-        <v>-20286.45</v>
+        <v>-19602.79</v>
       </c>
       <c r="M6" t="n">
-        <v>8624.790000000001</v>
+        <v>47597.34</v>
       </c>
       <c r="N6" t="n">
-        <v>-5112.99</v>
+        <v>-5579.34</v>
       </c>
       <c r="O6" t="n">
-        <v>37768.52</v>
+        <v>35278.2</v>
       </c>
       <c r="P6" t="n">
-        <v>25047.69</v>
+        <v>17183.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>302.16</v>
+        <v>57452.8</v>
       </c>
       <c r="R6" t="n">
-        <v>2215.82</v>
+        <v>1162.34</v>
       </c>
       <c r="S6" t="n">
-        <v>-22873.16</v>
+        <v>44313.98</v>
       </c>
       <c r="T6" t="n">
-        <v>-1202.61</v>
+        <v>24094.03</v>
       </c>
       <c r="U6" t="n">
-        <v>24483.77</v>
+        <v>201900.06</v>
       </c>
       <c r="V6" t="n">
-        <v>-82.85672510000001</v>
+        <v>-9.709155113673569</v>
       </c>
       <c r="W6" t="n">
-        <v>35.2265603</v>
+        <v>23.574703246745</v>
       </c>
       <c r="X6" t="n">
-        <v>-20.883181</v>
+        <v>-2.763416712209</v>
       </c>
       <c r="Y6" t="n">
-        <v>154.2594135</v>
+        <v>17.4731003051708</v>
       </c>
       <c r="Z6" t="n">
-        <v>102.30324</v>
+        <v>8.51089395416723</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.234123666</v>
+        <v>28.4560589035982</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.050158529999999</v>
+        <v>0.575700670916096</v>
       </c>
       <c r="AC6" t="n">
-        <v>-93.4217239</v>
+        <v>21.9484729226925</v>
       </c>
       <c r="AD6" t="n">
-        <v>-4.91186611</v>
+        <v>11.9336418225928</v>
       </c>
       <c r="AE6" t="n">
         <v>100</v>
       </c>
       <c r="AF6" t="n">
-        <v>523306.31</v>
+        <v>602904.440133573</v>
       </c>
       <c r="AG6" t="n">
-        <v>542950.8</v>
+        <v>772061.327602667</v>
       </c>
       <c r="AH6" t="n">
-        <v>132501.51</v>
+        <v>175604.477330729</v>
       </c>
       <c r="AI6" t="n">
-        <v>1349391.34</v>
+        <v>1883437.34</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1830305.23</v>
+        <v>2692680.01</v>
       </c>
       <c r="AK6" t="n">
-        <v>660818.45</v>
+        <v>878295.283064733</v>
       </c>
       <c r="AL6" t="n">
-        <v>118720.55</v>
+        <v>143261.95</v>
       </c>
       <c r="AM6" t="n">
-        <v>659669.86</v>
+        <v>912634.071868299</v>
       </c>
       <c r="AN6" t="n">
-        <v>137143.52</v>
+        <v>170268.19</v>
       </c>
       <c r="AO6" t="n">
-        <v>5954807.57</v>
+        <v>8231147.09</v>
       </c>
       <c r="AP6" t="n">
-        <v>8.787963400000001</v>
+        <v>7.32467095462356</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.11785635</v>
+        <v>9.379753747088809</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.22511825</v>
+        <v>2.13341440033395</v>
       </c>
       <c r="AS6" t="n">
-        <v>22.66053645</v>
+        <v>22.8818331079053</v>
       </c>
       <c r="AT6" t="n">
-        <v>30.7365974</v>
+        <v>32.7133020532622</v>
       </c>
       <c r="AU6" t="n">
-        <v>11.09722593</v>
+        <v>10.6703874133384</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.993692468</v>
+        <v>1.74048584521164</v>
       </c>
       <c r="AW6" t="n">
-        <v>11.07793749</v>
+        <v>11.0875684991349</v>
       </c>
       <c r="AX6" t="n">
-        <v>2.30307224</v>
+        <v>2.06858397910126</v>
       </c>
       <c r="AY6" t="n">
         <v>100</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-1452.18</v>
+        <v>-11009.67</v>
       </c>
       <c r="BA6" t="n">
-        <v>4892.66</v>
+        <v>13085.37</v>
       </c>
       <c r="BB6" t="n">
-        <v>-719.14</v>
+        <v>-1406.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>12518.97</v>
+        <v>4746.68</v>
       </c>
       <c r="BD6" t="n">
-        <v>26988.05</v>
+        <v>2278.23</v>
       </c>
       <c r="BE6" t="n">
-        <v>3412.22</v>
+        <v>9082.07</v>
       </c>
       <c r="BF6" t="n">
-        <v>76.48999999999999</v>
+        <v>1126.98</v>
       </c>
       <c r="BG6" t="n">
-        <v>531.03</v>
+        <v>4345.63999999998</v>
       </c>
       <c r="BH6" t="n">
-        <v>-1120.85</v>
+        <v>135.799999999997</v>
       </c>
       <c r="BI6" t="n">
-        <v>45127.25</v>
+        <v>22384.9</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-11629.94</v>
+        <v>-948.4900000000021</v>
       </c>
       <c r="BK6" t="n">
-        <v>1271.88</v>
+        <v>9851.450000000001</v>
       </c>
       <c r="BL6" t="n">
-        <v>-3934.53</v>
+        <v>-938.16</v>
       </c>
       <c r="BM6" t="n">
-        <v>24409.39</v>
+        <v>4432.07</v>
       </c>
       <c r="BN6" t="n">
-        <v>13691.77</v>
+        <v>-3407.28</v>
       </c>
       <c r="BO6" t="n">
-        <v>7004.24</v>
+        <v>19193.36</v>
       </c>
       <c r="BP6" t="n">
-        <v>-1124.37</v>
+        <v>263.81</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-18493.5</v>
+        <v>6591.02</v>
       </c>
       <c r="BR6" t="n">
-        <v>-2737.23</v>
+        <v>-155.790000000001</v>
       </c>
       <c r="BS6" t="n">
-        <v>8457.709999999999</v>
+        <v>34881.99</v>
       </c>
       <c r="BT6" t="n">
-        <v>-137.506961</v>
+        <v>-2.71913959037315</v>
       </c>
       <c r="BU6" t="n">
-        <v>15.03811315</v>
+        <v>28.2422247125236</v>
       </c>
       <c r="BV6" t="n">
-        <v>-46.5200391</v>
+        <v>-2.68952545425304</v>
       </c>
       <c r="BW6" t="n">
-        <v>288.60519</v>
+        <v>12.7058977999822</v>
       </c>
       <c r="BX6" t="n">
-        <v>161.885073</v>
+        <v>-9.76802068918659</v>
       </c>
       <c r="BY6" t="n">
-        <v>82.8148518</v>
+        <v>55.0236956091094</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-13.29402403</v>
+        <v>0.7562928605850751</v>
       </c>
       <c r="CA6" t="n">
-        <v>-218.6584785</v>
+        <v>18.8951949129049</v>
       </c>
       <c r="CB6" t="n">
-        <v>-32.36372493</v>
+        <v>-0.446620161292406</v>
       </c>
       <c r="CC6" t="n">
         <v>100</v>
       </c>
       <c r="CD6" t="n">
-        <v>355901.87</v>
+        <v>419761.994273843</v>
       </c>
       <c r="CE6" t="n">
-        <v>249126.39</v>
+        <v>397115.572171507</v>
       </c>
       <c r="CF6" t="n">
-        <v>78980.92</v>
+        <v>107806.70189282</v>
       </c>
       <c r="CG6" t="n">
-        <v>799550.36</v>
+        <v>1209980.46</v>
       </c>
       <c r="CH6" t="n">
-        <v>1400348.75</v>
+        <v>2098721.81</v>
       </c>
       <c r="CI6" t="n">
-        <v>418240.87</v>
+        <v>650546.027386275</v>
       </c>
       <c r="CJ6" t="n">
-        <v>52982.08</v>
+        <v>71211.91</v>
       </c>
       <c r="CK6" t="n">
-        <v>396127.51</v>
+        <v>568388.934275555</v>
       </c>
       <c r="CL6" t="n">
-        <v>70924.25999999999</v>
+        <v>94062.33999999989</v>
       </c>
       <c r="CM6" t="n">
-        <v>3822183.01</v>
+        <v>5617595.75</v>
       </c>
       <c r="CN6" t="n">
-        <v>9.31148166</v>
+        <v>7.47227128747815</v>
       </c>
       <c r="CO6" t="n">
-        <v>6.51790847</v>
+        <v>7.06913757850068</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.06638248</v>
+        <v>1.91908970831196</v>
       </c>
       <c r="CQ6" t="n">
-        <v>20.91868333</v>
+        <v>21.5391159109304</v>
       </c>
       <c r="CR6" t="n">
-        <v>36.6374071</v>
+        <v>37.3597870583692</v>
       </c>
       <c r="CS6" t="n">
-        <v>10.9424606</v>
+        <v>11.5805062581492</v>
       </c>
       <c r="CT6" t="n">
-        <v>1.38617329</v>
+        <v>1.26765814361064</v>
       </c>
       <c r="CU6" t="n">
-        <v>10.36390746</v>
+        <v>10.1180106146932</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.855595606</v>
+        <v>1.67442343995649</v>
       </c>
       <c r="CW6" t="n">
         <v>100</v>
       </c>
       <c r="CX6" t="n">
-        <v>-904.41</v>
+        <v>-1125.12</v>
       </c>
       <c r="CY6" t="n">
-        <v>203.81</v>
+        <v>2469.94</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-347.61</v>
+        <v>-464.22</v>
       </c>
       <c r="DA6" t="n">
-        <v>-974.48</v>
+        <v>-1417.42</v>
       </c>
       <c r="DB6" t="n">
-        <v>-138.51</v>
+        <v>4540.23</v>
       </c>
       <c r="DC6" t="n">
-        <v>-331.97</v>
+        <v>248.7</v>
       </c>
       <c r="DD6" t="n">
-        <v>226.33</v>
+        <v>-131.76</v>
       </c>
       <c r="DE6" t="n">
-        <v>-1070.98</v>
+        <v>-652.96</v>
       </c>
       <c r="DF6" t="n">
-        <v>778.65</v>
+        <v>414.920000000001</v>
       </c>
       <c r="DG6" t="n">
-        <v>-2559.17</v>
+        <v>3882.31</v>
       </c>
       <c r="DH6" t="n">
-        <v>-3190.33</v>
+        <v>-1024.35</v>
       </c>
       <c r="DI6" t="n">
-        <v>2221.56</v>
+        <v>71.14999999999959</v>
       </c>
       <c r="DJ6" t="n">
-        <v>-1159.94</v>
+        <v>-202.73</v>
       </c>
       <c r="DK6" t="n">
-        <v>-4085.61</v>
+        <v>-2287.96</v>
       </c>
       <c r="DL6" t="n">
-        <v>-2181.99</v>
+        <v>-3048.73</v>
       </c>
       <c r="DM6" t="n">
-        <v>-905.64</v>
+        <v>-345.5</v>
       </c>
       <c r="DN6" t="n">
-        <v>974.8200000000001</v>
+        <v>107.09</v>
       </c>
       <c r="DO6" t="n">
-        <v>-3030.24</v>
+        <v>-432.839999999998</v>
       </c>
       <c r="DP6" t="n">
-        <v>2607.95</v>
+        <v>-635.65</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-8749.42</v>
+        <v>-7799.52</v>
       </c>
       <c r="DR6" t="n">
-        <v>36.4633313</v>
+        <v>13.1335005231091</v>
       </c>
       <c r="DS6" t="n">
-        <v>-25.3909402</v>
+        <v>-0.912235624756391</v>
       </c>
       <c r="DT6" t="n">
-        <v>13.25733591</v>
+        <v>2.5992625187191</v>
       </c>
       <c r="DU6" t="n">
-        <v>46.695781</v>
+        <v>29.3346257205572</v>
       </c>
       <c r="DV6" t="n">
-        <v>24.93868165</v>
+        <v>39.0886875089749</v>
       </c>
       <c r="DW6" t="n">
-        <v>10.35085754</v>
+        <v>4.42975978008903</v>
       </c>
       <c r="DX6" t="n">
-        <v>-11.14153852</v>
+        <v>-1.37303321230024</v>
       </c>
       <c r="DY6" t="n">
-        <v>34.63361</v>
+        <v>5.54957228137114</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-29.80711864</v>
+        <v>8.149860504236161</v>
       </c>
       <c r="EA6" t="n">
         <v>100</v>
       </c>
       <c r="EB6" t="n">
-        <v>95484.14</v>
+        <v>105292.563294437</v>
       </c>
       <c r="EC6" t="n">
-        <v>238438.35</v>
+        <v>299348.407649327</v>
       </c>
       <c r="ED6" t="n">
-        <v>49473.31</v>
+        <v>64056.8467694106</v>
       </c>
       <c r="EE6" t="n">
-        <v>406986.51</v>
+        <v>504309.07</v>
       </c>
       <c r="EF6" t="n">
-        <v>308609.45</v>
+        <v>416437.18</v>
       </c>
       <c r="EG6" t="n">
-        <v>85318.84</v>
+        <v>78271.9596439361</v>
       </c>
       <c r="EH6" t="n">
-        <v>30969.77</v>
+        <v>35063.6</v>
       </c>
       <c r="EI6" t="n">
-        <v>38403.54</v>
+        <v>47093.202642889</v>
       </c>
       <c r="EJ6" t="n">
-        <v>10325.66</v>
+        <v>10883.73</v>
       </c>
       <c r="EK6" t="n">
-        <v>1264009.57</v>
+        <v>1560756.56</v>
       </c>
       <c r="EL6" t="n">
-        <v>7.5540678</v>
+        <v>6.74625152909412</v>
       </c>
       <c r="EM6" t="n">
-        <v>18.8636507</v>
+        <v>19.179698828197</v>
       </c>
       <c r="EN6" t="n">
-        <v>3.91399806</v>
+        <v>4.10421768590296</v>
       </c>
       <c r="EO6" t="n">
-        <v>32.19805606</v>
+        <v>32.3118340761611</v>
       </c>
       <c r="EP6" t="n">
-        <v>24.41511974</v>
+        <v>26.6817510605241</v>
       </c>
       <c r="EQ6" t="n">
-        <v>6.74985712</v>
+        <v>5.01500116353419</v>
       </c>
       <c r="ER6" t="n">
-        <v>2.45012148</v>
+        <v>2.24657713436104</v>
       </c>
       <c r="ES6" t="n">
-        <v>3.038231744</v>
+        <v>3.01733171269766</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.8168972960000001</v>
+        <v>0.697336809527809</v>
       </c>
       <c r="EU6" t="n">
         <v>100</v>
       </c>
       <c r="EV6" t="n">
-        <v>-520.49</v>
+        <v>2678.01</v>
       </c>
       <c r="EW6" t="n">
-        <v>311.57</v>
+        <v>1511.54</v>
       </c>
       <c r="EX6" t="n">
-        <v>-71.91</v>
+        <v>-25.71</v>
       </c>
       <c r="EY6" t="n">
-        <v>143.21</v>
+        <v>3707.12</v>
       </c>
       <c r="EZ6" t="n">
-        <v>10270.29</v>
+        <v>26558.65</v>
       </c>
       <c r="FA6" t="n">
-        <v>1744.98</v>
+        <v>1378.13</v>
       </c>
       <c r="FB6" t="n">
-        <v>-351.65</v>
+        <v>-1066.83</v>
       </c>
       <c r="FC6" t="n">
-        <v>471.25</v>
+        <v>1654.49</v>
       </c>
       <c r="FD6" t="n">
-        <v>-241.26</v>
+        <v>10103.84</v>
       </c>
       <c r="FE6" t="n">
-        <v>11755.99</v>
+        <v>46499.24</v>
       </c>
       <c r="FF6" t="n">
-        <v>-2652.07</v>
+        <v>390.27</v>
       </c>
       <c r="FG6" t="n">
-        <v>1397.22</v>
+        <v>1680.87</v>
       </c>
       <c r="FH6" t="n">
-        <v>-178.66</v>
+        <v>-59.9</v>
       </c>
       <c r="FI6" t="n">
-        <v>4935.54</v>
+        <v>4599.73</v>
       </c>
       <c r="FJ6" t="n">
-        <v>8232.879999999999</v>
+        <v>-2129.56</v>
       </c>
       <c r="FK6" t="n">
-        <v>-4752.91</v>
+        <v>-1226.1</v>
       </c>
       <c r="FL6" t="n">
-        <v>193.83</v>
+        <v>614.16</v>
       </c>
       <c r="FM6" t="n">
-        <v>-979.6900000000001</v>
+        <v>4184.94</v>
       </c>
       <c r="FN6" t="n">
-        <v>-1813.76</v>
+        <v>2313.61</v>
       </c>
       <c r="FO6" t="n">
-        <v>4382.38</v>
+        <v>10368.02</v>
       </c>
       <c r="FP6" t="n">
-        <v>-60.5166599</v>
+        <v>3.76417097960845</v>
       </c>
       <c r="FQ6" t="n">
-        <v>31.8826756</v>
+        <v>16.2120636341365</v>
       </c>
       <c r="FR6" t="n">
-        <v>-4.0767802</v>
+        <v>-0.5777380830669691</v>
       </c>
       <c r="FS6" t="n">
-        <v>112.622365</v>
+        <v>44.3645942041007</v>
       </c>
       <c r="FT6" t="n">
-        <v>187.863216</v>
+        <v>-20.5396980329899</v>
       </c>
       <c r="FU6" t="n">
-        <v>-108.4549948</v>
+        <v>-11.8257873730953</v>
       </c>
       <c r="FV6" t="n">
-        <v>4.42293913</v>
+        <v>5.92359968441419</v>
       </c>
       <c r="FW6" t="n">
-        <v>-22.35520425</v>
+        <v>40.3639267671166</v>
       </c>
       <c r="FX6" t="n">
-        <v>-41.3875565</v>
+        <v>22.3148682197758</v>
       </c>
       <c r="FY6" t="n">
         <v>100</v>
       </c>
       <c r="FZ6" t="n">
-        <v>20592.84</v>
+        <v>27841.931617607</v>
       </c>
       <c r="GA6" t="n">
-        <v>42888.95</v>
+        <v>59302.3723026831</v>
       </c>
       <c r="GB6" t="n">
-        <v>1976.47</v>
+        <v>1813.20115011201</v>
       </c>
       <c r="GC6" t="n">
-        <v>73858.50999999999</v>
+        <v>102542.81</v>
       </c>
       <c r="GD6" t="n">
-        <v>105787.67</v>
+        <v>166190.35</v>
       </c>
       <c r="GE6" t="n">
-        <v>70591.39</v>
+        <v>79250.79914902231</v>
       </c>
       <c r="GF6" t="n">
-        <v>22511.17</v>
+        <v>25007.9</v>
       </c>
       <c r="GG6" t="n">
-        <v>123663.74</v>
+        <v>168685.305780576</v>
       </c>
       <c r="GH6" t="n">
-        <v>36683.27</v>
+        <v>47842.95</v>
       </c>
       <c r="GI6" t="n">
-        <v>483845.09</v>
+        <v>678477.62</v>
       </c>
       <c r="GJ6" t="n">
-        <v>4.25608122</v>
+        <v>4.10358879893591</v>
       </c>
       <c r="GK6" t="n">
-        <v>8.8641904</v>
+        <v>8.740505295175851</v>
       </c>
       <c r="GL6" t="n">
-        <v>0.408492313</v>
+        <v>0.267245535690921</v>
       </c>
       <c r="GM6" t="n">
-        <v>15.26490844</v>
+        <v>15.1136613761851</v>
       </c>
       <c r="GN6" t="n">
-        <v>21.86395443</v>
+        <v>24.4945957097303</v>
       </c>
       <c r="GO6" t="n">
-        <v>14.58966753</v>
+        <v>11.6806799241252</v>
       </c>
       <c r="GP6" t="n">
-        <v>4.65255729</v>
+        <v>3.68588428900573</v>
       </c>
       <c r="GQ6" t="n">
-        <v>25.5585398</v>
+        <v>24.8623242400502</v>
       </c>
       <c r="GR6" t="n">
-        <v>7.5816146</v>
+        <v>7.05151483110084</v>
       </c>
       <c r="GS6" t="n">
-        <v>103.040006</v>
+        <v>100</v>
       </c>
       <c r="GT6" t="n">
-        <v>-828.4299999999999</v>
+        <v>11.4300000000007</v>
       </c>
       <c r="GU6" t="n">
-        <v>-197.19</v>
+        <v>5856.58</v>
       </c>
       <c r="GV6" t="n">
-        <v>-27.65</v>
+        <v>-6.15000000000001</v>
       </c>
       <c r="GW6" t="n">
-        <v>2641.28</v>
+        <v>139.76</v>
       </c>
       <c r="GX6" t="n">
-        <v>100.56</v>
+        <v>193.27</v>
       </c>
       <c r="GY6" t="n">
-        <v>-3939.85</v>
+        <v>-1941.4</v>
       </c>
       <c r="GZ6" t="n">
-        <v>130.21</v>
+        <v>517.03</v>
       </c>
       <c r="HA6" t="n">
-        <v>-2127.56</v>
+        <v>7571.79</v>
       </c>
       <c r="HB6" t="n">
-        <v>-392.89</v>
+        <v>-275.71</v>
       </c>
       <c r="HC6" t="n">
-        <v>-4641.52</v>
+        <v>12066.6</v>
       </c>
       <c r="HD6" t="n">
-        <v>-2859.05</v>
+        <v>-875.87</v>
       </c>
       <c r="HE6" t="n">
-        <v>-148.54</v>
+        <v>-90.78</v>
       </c>
       <c r="HF6" t="n">
-        <v>152.31</v>
+        <v>-61.5</v>
       </c>
       <c r="HG6" t="n">
-        <v>12594.4</v>
+        <v>-2558.44</v>
       </c>
       <c r="HH6" t="n">
-        <v>2915.24</v>
+        <v>-1391.51</v>
       </c>
       <c r="HI6" t="n">
-        <v>-1241.6</v>
+        <v>-3375.92</v>
       </c>
       <c r="HJ6" t="n">
-        <v>928.34</v>
+        <v>-306.15</v>
       </c>
       <c r="HK6" t="n">
-        <v>-7504.22</v>
+        <v>-674.699999999995</v>
       </c>
       <c r="HL6" t="n">
-        <v>-122.72</v>
+        <v>-623.5599999999999</v>
       </c>
       <c r="HM6" t="n">
-        <v>4714.16</v>
+        <v>-9958.429999999989</v>
       </c>
       <c r="HN6" t="n">
-        <v>-60.6481324</v>
+        <v>8.795261903733831</v>
       </c>
       <c r="HO6" t="n">
-        <v>-3.15093251</v>
+        <v>0.911589477457792</v>
       </c>
       <c r="HP6" t="n">
-        <v>3.23090434</v>
+        <v>0.617567226962483</v>
       </c>
       <c r="HQ6" t="n">
-        <v>267.1610637</v>
+        <v>25.6911983113804</v>
       </c>
       <c r="HR6" t="n">
-        <v>61.8400733</v>
+        <v>13.973186536432</v>
       </c>
       <c r="HS6" t="n">
-        <v>-26.33767203</v>
+        <v>33.9001228105234</v>
       </c>
       <c r="HT6" t="n">
-        <v>19.69258574</v>
+        <v>3.07427978104983</v>
       </c>
       <c r="HU6" t="n">
-        <v>-159.1846692</v>
+        <v>6.77516435823715</v>
       </c>
       <c r="HV6" t="n">
-        <v>-2.603220934</v>
+        <v>6.26162959422319</v>
       </c>
       <c r="HW6" t="n">
         <v>100</v>
       </c>
       <c r="HX6" t="n">
-        <v>44578.65</v>
+        <v>42485.7909476858</v>
       </c>
       <c r="HY6" t="n">
-        <v>3316.55</v>
+        <v>11521.7054791495</v>
       </c>
       <c r="HZ6" t="n">
-        <v>1662.48</v>
+        <v>1577.68751838647</v>
       </c>
       <c r="IA6" t="n">
-        <v>61065.88</v>
+        <v>59092.6</v>
       </c>
       <c r="IB6" t="n">
-        <v>13196.02</v>
+        <v>11097.25</v>
       </c>
       <c r="IC6" t="n">
-        <v>78120.36</v>
+        <v>68357.336885499</v>
       </c>
       <c r="ID6" t="n">
-        <v>8681.85</v>
+        <v>8538.07</v>
       </c>
       <c r="IE6" t="n">
-        <v>73139.46000000001</v>
+        <v>96695.9691692792</v>
       </c>
       <c r="IF6" t="n">
-        <v>15177.86</v>
+        <v>13232.06</v>
       </c>
       <c r="IG6" t="n">
-        <v>298939.11</v>
+        <v>312598.47</v>
       </c>
       <c r="IH6" t="n">
-        <v>14.9122843</v>
+        <v>13.5911704710793</v>
       </c>
       <c r="II6" t="n">
-        <v>1.10943998</v>
+        <v>3.68578434793668</v>
       </c>
       <c r="IJ6" t="n">
-        <v>0.556126631</v>
+        <v>0.504700972588405</v>
       </c>
       <c r="IK6" t="n">
-        <v>20.4275312</v>
+        <v>18.9036753762742</v>
       </c>
       <c r="IL6" t="n">
-        <v>4.41428356</v>
+        <v>3.55000138036504</v>
       </c>
       <c r="IM6" t="n">
-        <v>26.1325325</v>
+        <v>21.8674572801009</v>
       </c>
       <c r="IN6" t="n">
-        <v>2.904220194</v>
+        <v>2.73132174959142</v>
       </c>
       <c r="IO6" t="n">
-        <v>24.4663403</v>
+        <v>30.9329630337855</v>
       </c>
       <c r="IP6" t="n">
-        <v>5.07724132</v>
+        <v>4.23292538827845</v>
       </c>
       <c r="IQ6" t="n">
         <v>100</v>
       </c>
       <c r="IR6" t="n">
-        <v>63.39</v>
+        <v>-48.5000000000001</v>
       </c>
       <c r="IS6" t="n">
-        <v>943.12</v>
+        <v>-307.96</v>
       </c>
       <c r="IT6" t="n">
-        <v>-11.33</v>
+        <v>-6.75</v>
       </c>
       <c r="IU6" t="n">
-        <v>-206.01</v>
+        <v>-52.43</v>
       </c>
       <c r="IV6" t="n">
-        <v>1458.66</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="IW6" t="n">
-        <v>-55.42</v>
+        <v>-42.39</v>
       </c>
       <c r="IX6" t="n">
-        <v>84.8</v>
+        <v>-46.26</v>
       </c>
       <c r="IY6" t="n">
-        <v>542.89</v>
+        <v>-447.75</v>
       </c>
       <c r="IZ6" t="n">
-        <v>125.36</v>
+        <v>-41.16</v>
       </c>
       <c r="JA6" t="n">
-        <v>2945.46</v>
+        <v>-1002.67</v>
       </c>
       <c r="JB6" t="n">
-        <v>446.91</v>
+        <v>-172.89</v>
       </c>
       <c r="JC6" t="n">
-        <v>3889.5</v>
+        <v>-1075.71</v>
       </c>
       <c r="JD6" t="n">
-        <v>9.92</v>
+        <v>-7.36</v>
       </c>
       <c r="JE6" t="n">
-        <v>52.23</v>
+        <v>-80.04000000000001</v>
       </c>
       <c r="JF6" t="n">
-        <v>2389.79</v>
+        <v>-36.06</v>
       </c>
       <c r="JG6" t="n">
-        <v>-68.02</v>
+        <v>-15.42</v>
       </c>
       <c r="JH6" t="n">
-        <v>598.96</v>
+        <v>-196.03</v>
       </c>
       <c r="JI6" t="n">
-        <v>3308.13</v>
+        <v>-1144.72</v>
       </c>
       <c r="JJ6" t="n">
-        <v>538.34</v>
+        <v>-117</v>
       </c>
       <c r="JK6" t="n">
-        <v>11165.76</v>
+        <v>-2845.23</v>
       </c>
       <c r="JL6" t="n">
-        <v>4.00250408</v>
+        <v>6.07648590799338</v>
       </c>
       <c r="JM6" t="n">
-        <v>34.8341716</v>
+        <v>37.8074883225609</v>
       </c>
       <c r="JN6" t="n">
-        <v>0.08884303440000001</v>
+        <v>0.258678560256992</v>
       </c>
       <c r="JO6" t="n">
-        <v>0.467769323</v>
+        <v>2.81312934279478</v>
       </c>
       <c r="JP6" t="n">
-        <v>21.40284226</v>
+        <v>1.26738435908521</v>
       </c>
       <c r="JQ6" t="n">
-        <v>-0.60918379</v>
+        <v>0.541959700973208</v>
       </c>
       <c r="JR6" t="n">
-        <v>5.36425644</v>
+        <v>6.88977692488832</v>
       </c>
       <c r="JS6" t="n">
-        <v>29.62745035</v>
+        <v>40.2329512904054</v>
       </c>
       <c r="JT6" t="n">
-        <v>4.82134669</v>
+        <v>4.11214559104185</v>
       </c>
       <c r="JU6" t="n">
         <v>100</v>
       </c>
       <c r="JV6" t="n">
-        <v>2064.44</v>
+        <v>1443.13</v>
       </c>
       <c r="JW6" t="n">
-        <v>9074.43</v>
+        <v>4606.12</v>
       </c>
       <c r="JX6" t="n">
-        <v>363.58</v>
+        <v>284.77</v>
       </c>
       <c r="JY6" t="n">
-        <v>2686.12</v>
+        <v>1708.31</v>
       </c>
       <c r="JZ6" t="n">
-        <v>2363.34</v>
+        <v>233.42</v>
       </c>
       <c r="KA6" t="n">
-        <v>7224.75</v>
+        <v>1822.26</v>
       </c>
       <c r="KB6" t="n">
-        <v>1778.8</v>
+        <v>1092.12</v>
       </c>
       <c r="KC6" t="n">
-        <v>11214.39</v>
+        <v>7133.39</v>
       </c>
       <c r="KD6" t="n">
-        <v>1353.89</v>
+        <v>1035.18</v>
       </c>
       <c r="KE6" t="n">
-        <v>38123.74</v>
+        <v>19358.7</v>
       </c>
       <c r="KF6" t="n">
-        <v>5.41510355</v>
+        <v>7.45468445711747</v>
       </c>
       <c r="KG6" t="n">
-        <v>23.80257026</v>
+        <v>23.7935398554655</v>
       </c>
       <c r="KH6" t="n">
-        <v>0.953683977</v>
+        <v>1.47101819853606</v>
       </c>
       <c r="KI6" t="n">
-        <v>7.04579351</v>
+        <v>8.82450784401845</v>
       </c>
       <c r="KJ6" t="n">
-        <v>6.19912947</v>
+        <v>1.20576278365799</v>
       </c>
       <c r="KK6" t="n">
-        <v>18.95079024</v>
+        <v>9.41313208015001</v>
       </c>
       <c r="KL6" t="n">
-        <v>4.66585912</v>
+        <v>5.64149452184289</v>
       </c>
       <c r="KM6" t="n">
-        <v>29.4157656</v>
+        <v>36.8484970581702</v>
       </c>
       <c r="KN6" t="n">
-        <v>3.55130425</v>
+        <v>5.34736320104139</v>
       </c>
       <c r="KO6" t="n">
         <v>100</v>
       </c>
       <c r="KP6" t="n">
-        <v>-1342.31</v>
+        <v>264.56</v>
       </c>
       <c r="KQ6" t="n">
-        <v>-0.5600000000000001</v>
+        <v>9.76</v>
       </c>
       <c r="KR6" t="n">
-        <v>-0.1</v>
+        <v>-0.64</v>
       </c>
       <c r="KS6" t="n">
-        <v>-108.22</v>
+        <v>19.63</v>
       </c>
       <c r="KT6" t="n">
         <v>0</v>
       </c>
       <c r="KU6" t="n">
-        <v>44.05</v>
+        <v>2.27</v>
       </c>
       <c r="KV6" t="n">
-        <v>12.89</v>
+        <v>136.01</v>
       </c>
       <c r="KW6" t="n">
-        <v>3222.14</v>
+        <v>2965.09</v>
       </c>
       <c r="KX6" t="n">
-        <v>171.65</v>
+        <v>154.28</v>
       </c>
       <c r="KY6" t="n">
-        <v>1999.54</v>
+        <v>3550.96</v>
       </c>
       <c r="KZ6" t="n">
-        <v>-401.97</v>
+        <v>-215.5</v>
       </c>
       <c r="LA6" t="n">
-        <v>-6.83</v>
+        <v>-0.51</v>
       </c>
       <c r="LB6" t="n">
-        <v>-2.09</v>
+        <v>-0.77</v>
       </c>
       <c r="LC6" t="n">
-        <v>-137.43</v>
+        <v>-3.5</v>
       </c>
       <c r="LD6" t="n">
         <v>0</v>
       </c>
       <c r="LE6" t="n">
-        <v>266.09</v>
+        <v>0.31</v>
       </c>
       <c r="LF6" t="n">
-        <v>644.24</v>
+        <v>3.84</v>
       </c>
       <c r="LG6" t="n">
-        <v>3826.36</v>
+        <v>364.86</v>
       </c>
       <c r="LH6" t="n">
-        <v>324.81</v>
+        <v>-7.94999999999999</v>
       </c>
       <c r="LI6" t="n">
-        <v>4513.18</v>
+        <v>140.78</v>
       </c>
       <c r="LJ6" t="n">
-        <v>-8.90658028</v>
+        <v>-153.075720983094</v>
       </c>
       <c r="LK6" t="n">
-        <v>-0.1513345357</v>
+        <v>-0.362267367523796</v>
       </c>
       <c r="LL6" t="n">
-        <v>-0.0463088111</v>
+        <v>-0.546952692143771</v>
       </c>
       <c r="LM6" t="n">
-        <v>-3.045081295</v>
+        <v>-2.4861486006535</v>
       </c>
       <c r="LN6" t="n">
         <v>0</v>
       </c>
       <c r="LO6" t="n">
-        <v>5.89584284</v>
+        <v>0.220201733200739</v>
       </c>
       <c r="LP6" t="n">
-        <v>14.27463562</v>
+        <v>2.7276601790027</v>
       </c>
       <c r="LQ6" t="n">
-        <v>84.7819054</v>
+        <v>259.170336695553</v>
       </c>
       <c r="LR6" t="n">
-        <v>7.19692102</v>
+        <v>-5.64710896434152</v>
       </c>
       <c r="LS6" t="n">
         <v>100</v>
       </c>
       <c r="LT6" t="n">
-        <v>4684.37</v>
+        <v>6079.03</v>
       </c>
       <c r="LU6" t="n">
-        <v>106.13</v>
+        <v>167.15</v>
       </c>
       <c r="LV6" t="n">
-        <v>44.75</v>
+        <v>65.27</v>
       </c>
       <c r="LW6" t="n">
-        <v>5243.96</v>
+        <v>5804.09</v>
       </c>
       <c r="LX6" t="n">
         <v>0</v>
       </c>
       <c r="LY6" t="n">
-        <v>1322.24</v>
+        <v>46.9</v>
       </c>
       <c r="LZ6" t="n">
-        <v>1796.88</v>
+        <v>2348.35</v>
       </c>
       <c r="MA6" t="n">
-        <v>17121.22</v>
+        <v>24637.27</v>
       </c>
       <c r="MB6" t="n">
-        <v>2678.58</v>
+        <v>3211.93</v>
       </c>
       <c r="MC6" t="n">
-        <v>32998.13</v>
+        <v>42359.99</v>
       </c>
       <c r="MD6" t="n">
-        <v>14.19586504</v>
+        <v>14.3508768533704</v>
       </c>
       <c r="ME6" t="n">
-        <v>0.321624286</v>
+        <v>0.394594049715309</v>
       </c>
       <c r="MF6" t="n">
-        <v>0.1356137454</v>
+        <v>0.154084077923531</v>
       </c>
       <c r="MG6" t="n">
-        <v>15.8916884</v>
+        <v>13.7018209872099</v>
       </c>
       <c r="MH6" t="n">
         <v>0</v>
       </c>
       <c r="MI6" t="n">
-        <v>4.00701494</v>
+        <v>0.110717684305402</v>
       </c>
       <c r="MJ6" t="n">
-        <v>5.44539948</v>
+        <v>5.54379262129193</v>
       </c>
       <c r="MK6" t="n">
-        <v>51.885425</v>
+        <v>58.1616520683787</v>
       </c>
       <c r="ML6" t="n">
-        <v>8.11736908</v>
+        <v>7.58246165780492</v>
       </c>
       <c r="MM6" t="n">
         <v>100</v>
@@ -5631,1706 +5631,1706 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023-Q1</t>
+          <t>2025-Q1</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1135.85</v>
+        <v>-4445.28666666667</v>
       </c>
       <c r="C7" t="n">
-        <v>9499.200000000001</v>
+        <v>17585.2683333333</v>
       </c>
       <c r="D7" t="n">
-        <v>-1068.97</v>
+        <v>-1459.82583333333</v>
       </c>
       <c r="E7" t="n">
-        <v>15832.12</v>
+        <v>8627.24</v>
       </c>
       <c r="F7" t="n">
-        <v>-8235.559999999999</v>
+        <v>-4406.11</v>
       </c>
       <c r="G7" t="n">
-        <v>11027.26</v>
+        <v>-3783.07583333333</v>
       </c>
       <c r="H7" t="n">
-        <v>168.26</v>
+        <v>1171.41</v>
       </c>
       <c r="I7" t="n">
-        <v>2305.99</v>
+        <v>13756.81</v>
       </c>
       <c r="J7" t="n">
-        <v>-3139.71</v>
+        <v>4649.58999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>25252.74</v>
+        <v>31696.02</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-825.85</v>
+        <v>-3140.8925</v>
       </c>
       <c r="BA7" t="n">
-        <v>7714.72</v>
+        <v>11190.5266666667</v>
       </c>
       <c r="BB7" t="n">
-        <v>-734.4400000000001</v>
+        <v>-1228.15583333333</v>
       </c>
       <c r="BC7" t="n">
-        <v>14077.59</v>
+        <v>4639.73</v>
       </c>
       <c r="BD7" t="n">
-        <v>-3680.48</v>
+        <v>-5457.56</v>
       </c>
       <c r="BE7" t="n">
-        <v>12635.63</v>
+        <v>-9418.83833333333</v>
       </c>
       <c r="BF7" t="n">
-        <v>146.35</v>
+        <v>-320.99</v>
       </c>
       <c r="BG7" t="n">
-        <v>4870.11</v>
+        <v>5290.29999999999</v>
       </c>
       <c r="BH7" t="n">
-        <v>-394.75</v>
+        <v>4191.07999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>33808.88</v>
+        <v>5745.19999999998</v>
       </c>
       <c r="CX7" t="n">
-        <v>-489.93</v>
+        <v>-1550.11666666667</v>
       </c>
       <c r="CY7" t="n">
-        <v>1118.85</v>
+        <v>2578.0425</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-207.57</v>
+        <v>-256.115</v>
       </c>
       <c r="DA7" t="n">
-        <v>-1400.73</v>
+        <v>-2033.82</v>
       </c>
       <c r="DB7" t="n">
-        <v>-3933.29</v>
+        <v>-1629.21</v>
       </c>
       <c r="DC7" t="n">
-        <v>-425.19</v>
+        <v>-938.990833333334</v>
       </c>
       <c r="DD7" t="n">
-        <v>-18.16</v>
+        <v>452.65</v>
       </c>
       <c r="DE7" t="n">
-        <v>-471.93</v>
+        <v>288.05</v>
       </c>
       <c r="DF7" t="n">
-        <v>-783.36</v>
+        <v>-82.0500000000002</v>
       </c>
       <c r="DG7" t="n">
-        <v>-6611.31</v>
+        <v>-3171.56</v>
       </c>
       <c r="EV7" t="n">
-        <v>262.49</v>
+        <v>-240.417499999998</v>
       </c>
       <c r="EW7" t="n">
-        <v>2473.78</v>
+        <v>6049.70166666667</v>
       </c>
       <c r="EX7" t="n">
-        <v>-63.3</v>
+        <v>-8.733333333333331</v>
       </c>
       <c r="EY7" t="n">
-        <v>2567.64</v>
+        <v>2680.92</v>
       </c>
       <c r="EZ7" t="n">
-        <v>1967.04</v>
+        <v>823.9400000000001</v>
       </c>
       <c r="FA7" t="n">
-        <v>2491.89</v>
+        <v>4238.47916666667</v>
       </c>
       <c r="FB7" t="n">
-        <v>544.17</v>
+        <v>1051.99</v>
       </c>
       <c r="FC7" t="n">
-        <v>1465.68</v>
+        <v>7583.34</v>
       </c>
       <c r="FD7" t="n">
-        <v>-1155.4</v>
+        <v>-174.32</v>
       </c>
       <c r="FE7" t="n">
-        <v>10553.99</v>
+        <v>22004.9</v>
       </c>
       <c r="GT7" t="n">
-        <v>263.47</v>
+        <v>278.659999999999</v>
       </c>
       <c r="GU7" t="n">
-        <v>315.69</v>
+        <v>-1959.7425</v>
       </c>
       <c r="GV7" t="n">
-        <v>-48.72</v>
+        <v>37.6683333333333</v>
       </c>
       <c r="GW7" t="n">
-        <v>876.53</v>
+        <v>3431.57</v>
       </c>
       <c r="GX7" t="n">
-        <v>-742.62</v>
+        <v>1880.6</v>
       </c>
       <c r="GY7" t="n">
-        <v>-3540.3</v>
+        <v>2336.08416666667</v>
       </c>
       <c r="GZ7" t="n">
-        <v>-184.97</v>
+        <v>-51.3299999999999</v>
       </c>
       <c r="HA7" t="n">
-        <v>-2085.78</v>
+        <v>921.0599999999901</v>
       </c>
       <c r="HB7" t="n">
-        <v>-562.79</v>
+        <v>579.11</v>
       </c>
       <c r="HC7" t="n">
-        <v>-5709.49</v>
+        <v>7453.67999999999</v>
       </c>
       <c r="IR7" t="n">
-        <v>-175.41</v>
+        <v>-32.75</v>
       </c>
       <c r="IS7" t="n">
-        <v>-2124.81</v>
+        <v>-265.08</v>
       </c>
       <c r="IT7" t="n">
-        <v>-14.71</v>
+        <v>-2.89</v>
       </c>
       <c r="IU7" t="n">
-        <v>-259.58</v>
+        <v>-59.27</v>
       </c>
       <c r="IV7" t="n">
-        <v>-1846.21</v>
+        <v>-23.88</v>
       </c>
       <c r="IW7" t="n">
-        <v>-152.33</v>
+        <v>1.99</v>
       </c>
       <c r="IX7" t="n">
-        <v>-319.13</v>
+        <v>34.06</v>
       </c>
       <c r="IY7" t="n">
-        <v>-1964.02</v>
+        <v>-510.54</v>
       </c>
       <c r="IZ7" t="n">
-        <v>-235</v>
+        <v>38.18</v>
       </c>
       <c r="JA7" t="n">
-        <v>-7091.2</v>
+        <v>-820.1799999999999</v>
       </c>
       <c r="KP7" t="n">
-        <v>-170.62</v>
+        <v>240.23</v>
       </c>
       <c r="KQ7" t="n">
-        <v>0.97</v>
+        <v>-8.18</v>
       </c>
       <c r="KR7" t="n">
-        <v>-0.23</v>
+        <v>-1.6</v>
       </c>
       <c r="KS7" t="n">
-        <v>-29.33</v>
+        <v>-31.89</v>
       </c>
       <c r="KT7" t="n">
         <v>0</v>
       </c>
       <c r="KU7" t="n">
-        <v>17.56</v>
+        <v>-1.8</v>
       </c>
       <c r="KV7" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="KW7" t="n">
-        <v>491.93</v>
+        <v>184.6</v>
       </c>
       <c r="KX7" t="n">
-        <v>-8.41</v>
+        <v>97.59</v>
       </c>
       <c r="KY7" t="n">
-        <v>301.87</v>
+        <v>483.98</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2023-Q2</t>
+          <t>2025-Q2</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-3482.89</v>
+        <v>1534.12333333333</v>
       </c>
       <c r="C8" t="n">
-        <v>7801.32</v>
+        <v>8558.498333333329</v>
       </c>
       <c r="D8" t="n">
-        <v>-889.8200000000001</v>
+        <v>-1224.45583333333</v>
       </c>
       <c r="E8" t="n">
-        <v>18783.77</v>
+        <v>16238.2</v>
       </c>
       <c r="F8" t="n">
-        <v>3453.76</v>
+        <v>-449.37</v>
       </c>
       <c r="G8" t="n">
-        <v>11410.4</v>
+        <v>-1490.09583333333</v>
       </c>
       <c r="H8" t="n">
-        <v>-908.0599999999999</v>
+        <v>165.9</v>
       </c>
       <c r="I8" t="n">
-        <v>-822.48</v>
+        <v>29926.96</v>
       </c>
       <c r="J8" t="n">
-        <v>542.4</v>
+        <v>1574.45</v>
       </c>
       <c r="K8" t="n">
-        <v>35888.4</v>
+        <v>54834.21</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-1723.25</v>
+        <v>-4675.2825</v>
       </c>
       <c r="BA8" t="n">
-        <v>5434.93</v>
+        <v>6512.38666666667</v>
       </c>
       <c r="BB8" t="n">
-        <v>-592.01</v>
+        <v>-1019.79583333333</v>
       </c>
       <c r="BC8" t="n">
-        <v>17597.74</v>
+        <v>22749.82</v>
       </c>
       <c r="BD8" t="n">
-        <v>6645.69</v>
+        <v>-2093.23</v>
       </c>
       <c r="BE8" t="n">
-        <v>11860.04</v>
+        <v>-1353.77833333334</v>
       </c>
       <c r="BF8" t="n">
-        <v>-344.82</v>
+        <v>-450.96</v>
       </c>
       <c r="BG8" t="n">
-        <v>1290.75</v>
+        <v>5756.84000000001</v>
       </c>
       <c r="BH8" t="n">
-        <v>1056.77</v>
+        <v>-15.9299999999967</v>
       </c>
       <c r="BI8" t="n">
-        <v>41225.84</v>
+        <v>25410.07</v>
       </c>
       <c r="CX8" t="n">
-        <v>-919.91</v>
+        <v>3223.54333333333</v>
       </c>
       <c r="CY8" t="n">
-        <v>806.26</v>
+        <v>314.542500000001</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-179.11</v>
+        <v>-224.685</v>
       </c>
       <c r="DA8" t="n">
-        <v>-186.51</v>
+        <v>2080.08</v>
       </c>
       <c r="DB8" t="n">
-        <v>671.7</v>
+        <v>125.83</v>
       </c>
       <c r="DC8" t="n">
-        <v>268.47</v>
+        <v>-4935.89083333333</v>
       </c>
       <c r="DD8" t="n">
-        <v>19.46</v>
+        <v>12.84</v>
       </c>
       <c r="DE8" t="n">
-        <v>-564.15</v>
+        <v>-2.92000000000189</v>
       </c>
       <c r="DF8" t="n">
-        <v>-13.22</v>
+        <v>-133.99</v>
       </c>
       <c r="DG8" t="n">
-        <v>-97.01000000000001</v>
+        <v>459.349999999997</v>
       </c>
       <c r="EV8" t="n">
-        <v>214.49</v>
+        <v>1287.6525</v>
       </c>
       <c r="EW8" t="n">
-        <v>1613.28</v>
+        <v>2510.56166666667</v>
       </c>
       <c r="EX8" t="n">
-        <v>-63.99</v>
+        <v>2.72666666666667</v>
       </c>
       <c r="EY8" t="n">
-        <v>2000.74</v>
+        <v>-4712.74</v>
       </c>
       <c r="EZ8" t="n">
-        <v>-3105.9</v>
+        <v>1347.61</v>
       </c>
       <c r="FA8" t="n">
-        <v>1182.75</v>
+        <v>-712.160833333332</v>
       </c>
       <c r="FB8" t="n">
-        <v>326.38</v>
+        <v>422.01</v>
       </c>
       <c r="FC8" t="n">
-        <v>2119.88</v>
+        <v>21855.49</v>
       </c>
       <c r="FD8" t="n">
-        <v>1690.31</v>
+        <v>1004.52</v>
       </c>
       <c r="FE8" t="n">
-        <v>5977.94</v>
+        <v>23005.67</v>
       </c>
       <c r="GT8" t="n">
-        <v>-900.49</v>
+        <v>1468.53</v>
       </c>
       <c r="GU8" t="n">
-        <v>333.13</v>
+        <v>-587.1725</v>
       </c>
       <c r="GV8" t="n">
-        <v>-47.86</v>
+        <v>20.0283333333333</v>
       </c>
       <c r="GW8" t="n">
-        <v>-608.55</v>
+        <v>-3837.39</v>
       </c>
       <c r="GX8" t="n">
-        <v>-680.04</v>
+        <v>172.83</v>
       </c>
       <c r="GY8" t="n">
-        <v>-1857.95</v>
+        <v>5474.87416666667</v>
       </c>
       <c r="GZ8" t="n">
-        <v>-1033.57</v>
+        <v>87.07000000000011</v>
       </c>
       <c r="HA8" t="n">
-        <v>-4150.04</v>
+        <v>1855.25999999999</v>
       </c>
       <c r="HB8" t="n">
-        <v>-2531.44</v>
+        <v>614.8099999999999</v>
       </c>
       <c r="HC8" t="n">
-        <v>-11476.81</v>
+        <v>5268.84</v>
       </c>
       <c r="IR8" t="n">
-        <v>-111.51</v>
+        <v>-61.92</v>
       </c>
       <c r="IS8" t="n">
-        <v>-386.39</v>
+        <v>-188.78</v>
       </c>
       <c r="IT8" t="n">
-        <v>-6.33</v>
+        <v>-1.64</v>
       </c>
       <c r="IU8" t="n">
-        <v>-70.17</v>
+        <v>-46.68</v>
       </c>
       <c r="IV8" t="n">
-        <v>-77.69</v>
+        <v>-2.41</v>
       </c>
       <c r="IW8" t="n">
-        <v>-59.34</v>
+        <v>38.73</v>
       </c>
       <c r="IX8" t="n">
-        <v>-151.76</v>
+        <v>90.81</v>
       </c>
       <c r="IY8" t="n">
-        <v>-444.12</v>
+        <v>-210.85</v>
       </c>
       <c r="IZ8" t="n">
-        <v>-3</v>
+        <v>22.55</v>
       </c>
       <c r="JA8" t="n">
-        <v>-1310.31</v>
+        <v>-360.19</v>
       </c>
       <c r="KP8" t="n">
-        <v>-42.22</v>
+        <v>291.6</v>
       </c>
       <c r="KQ8" t="n">
-        <v>0.11</v>
+        <v>-3.04</v>
       </c>
       <c r="KR8" t="n">
-        <v>-0.52</v>
+        <v>-1.09</v>
       </c>
       <c r="KS8" t="n">
-        <v>50.52</v>
+        <v>5.11</v>
       </c>
       <c r="KT8" t="n">
         <v>0</v>
       </c>
       <c r="KU8" t="n">
-        <v>16.43</v>
+        <v>-1.87</v>
       </c>
       <c r="KV8" t="n">
-        <v>276.25</v>
+        <v>4.13</v>
       </c>
       <c r="KW8" t="n">
-        <v>925.2</v>
+        <v>673.14</v>
       </c>
       <c r="KX8" t="n">
-        <v>342.98</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="KY8" t="n">
-        <v>1568.75</v>
+        <v>1050.47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2023-Q3</t>
+          <t>2025-Q3</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1818.5</v>
+        <v>-732.225321863454</v>
       </c>
       <c r="C9" t="n">
-        <v>3984.68</v>
+        <v>12888.3084407113</v>
       </c>
       <c r="D9" t="n">
-        <v>-997.78</v>
+        <v>-960.702042147853</v>
       </c>
       <c r="E9" t="n">
-        <v>2537.98</v>
+        <v>16686.64</v>
       </c>
       <c r="F9" t="n">
-        <v>-8200.620000000001</v>
+        <v>-10236.24</v>
       </c>
       <c r="G9" t="n">
-        <v>6703.52</v>
+        <v>9765.483841099989</v>
       </c>
       <c r="H9" t="n">
-        <v>-190.35</v>
+        <v>763.54</v>
       </c>
       <c r="I9" t="n">
-        <v>3410.57</v>
+        <v>1352.36508219998</v>
       </c>
       <c r="J9" t="n">
-        <v>254.33</v>
+        <v>804.099999999997</v>
       </c>
       <c r="K9" t="n">
-        <v>5683.83</v>
+        <v>30331.27</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-1435.12</v>
+        <v>-2926.74985685318</v>
       </c>
       <c r="BA9" t="n">
-        <v>4377.37</v>
+        <v>7980.02418387994</v>
       </c>
       <c r="BB9" t="n">
-        <v>-661.8099999999999</v>
+        <v>-794.050234726752</v>
       </c>
       <c r="BC9" t="n">
-        <v>2046.81</v>
+        <v>21011.21</v>
       </c>
       <c r="BD9" t="n">
-        <v>-4961.99</v>
+        <v>-6748.36</v>
       </c>
       <c r="BE9" t="n">
-        <v>5146.11</v>
+        <v>6949.11814152999</v>
       </c>
       <c r="BF9" t="n">
-        <v>-181.72</v>
+        <v>18.9200000000001</v>
       </c>
       <c r="BG9" t="n">
-        <v>3425.33</v>
+        <v>-353.442233830014</v>
       </c>
       <c r="BH9" t="n">
-        <v>70.39</v>
+        <v>-326.510000000002</v>
       </c>
       <c r="BI9" t="n">
-        <v>7825.37</v>
+        <v>24810.16</v>
       </c>
       <c r="CX9" t="n">
-        <v>-1080.08</v>
+        <v>-503.449643829623</v>
       </c>
       <c r="CY9" t="n">
-        <v>65</v>
+        <v>2461.91358120981</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-261.6</v>
+        <v>-185.293768650188</v>
       </c>
       <c r="DA9" t="n">
-        <v>-1052.93</v>
+        <v>298.450000000001</v>
       </c>
       <c r="DB9" t="n">
-        <v>-1747.23</v>
+        <v>-1892.47</v>
       </c>
       <c r="DC9" t="n">
-        <v>-603.15</v>
+        <v>164.46157488</v>
       </c>
       <c r="DD9" t="n">
-        <v>-70.53</v>
+        <v>110.77</v>
       </c>
       <c r="DE9" t="n">
-        <v>-424.13</v>
+        <v>-132.551743610003</v>
       </c>
       <c r="DF9" t="n">
-        <v>-156.77</v>
+        <v>-16.33</v>
       </c>
       <c r="DG9" t="n">
-        <v>-5331.42</v>
+        <v>305.499999999998</v>
       </c>
       <c r="EV9" t="n">
-        <v>703.86</v>
+        <v>1061.1505120281</v>
       </c>
       <c r="EW9" t="n">
-        <v>231.67</v>
+        <v>2088.93326072448</v>
       </c>
       <c r="EX9" t="n">
-        <v>-51.6</v>
+        <v>-4.39870979258363</v>
       </c>
       <c r="EY9" t="n">
-        <v>2145.46</v>
+        <v>-133.18</v>
       </c>
       <c r="EZ9" t="n">
-        <v>-1286.99</v>
+        <v>-1104.64</v>
       </c>
       <c r="FA9" t="n">
-        <v>2107.65</v>
+        <v>2595.94319398</v>
       </c>
       <c r="FB9" t="n">
-        <v>189.14</v>
+        <v>425.91</v>
       </c>
       <c r="FC9" t="n">
-        <v>1073.12</v>
+        <v>3374.73174306</v>
       </c>
       <c r="FD9" t="n">
-        <v>508.51</v>
+        <v>1101.61</v>
       </c>
       <c r="FE9" t="n">
-        <v>5620.82</v>
+        <v>9406.059999999999</v>
       </c>
       <c r="GT9" t="n">
-        <v>113.82</v>
+        <v>577.883666791246</v>
       </c>
       <c r="GU9" t="n">
-        <v>331.6</v>
+        <v>383.777414897086</v>
       </c>
       <c r="GV9" t="n">
-        <v>-14.94</v>
+        <v>27.3406710216693</v>
       </c>
       <c r="GW9" t="n">
-        <v>-559.12</v>
+        <v>-4419.42</v>
       </c>
       <c r="GX9" t="n">
-        <v>-155.54</v>
+        <v>-488.59</v>
       </c>
       <c r="GY9" t="n">
-        <v>137.89</v>
+        <v>-245.319069290001</v>
       </c>
       <c r="GZ9" t="n">
-        <v>38.72</v>
+        <v>174.74</v>
       </c>
       <c r="HA9" t="n">
-        <v>138.81</v>
+        <v>-2138.01268342</v>
       </c>
       <c r="HB9" t="n">
-        <v>-65.69</v>
+        <v>7.86999999999966</v>
       </c>
       <c r="HC9" t="n">
-        <v>-34.45</v>
+        <v>-6119.73</v>
       </c>
       <c r="IR9" t="n">
-        <v>-136.16</v>
+        <v>157.89</v>
       </c>
       <c r="IS9" t="n">
-        <v>-1018.43</v>
+        <v>-22.77</v>
       </c>
       <c r="IT9" t="n">
-        <v>-7.36</v>
+        <v>-3.45</v>
       </c>
       <c r="IU9" t="n">
-        <v>-68.64</v>
+        <v>-58.02</v>
       </c>
       <c r="IV9" t="n">
-        <v>-48.87</v>
+        <v>-2.18</v>
       </c>
       <c r="IW9" t="n">
-        <v>-57.32</v>
+        <v>302.68</v>
       </c>
       <c r="IX9" t="n">
-        <v>-170.13</v>
+        <v>2.2</v>
       </c>
       <c r="IY9" t="n">
-        <v>-988.5700000000001</v>
+        <v>67.67999999999989</v>
       </c>
       <c r="IZ9" t="n">
-        <v>-141.13</v>
+        <v>-12.3</v>
       </c>
       <c r="JA9" t="n">
-        <v>-2636.61</v>
+        <v>431.73</v>
       </c>
       <c r="KP9" t="n">
-        <v>15.18</v>
+        <v>901.05</v>
       </c>
       <c r="KQ9" t="n">
-        <v>-2.53</v>
+        <v>-3.57</v>
       </c>
       <c r="KR9" t="n">
-        <v>-0.47</v>
+        <v>-0.85</v>
       </c>
       <c r="KS9" t="n">
-        <v>26.4</v>
+        <v>-12.4</v>
       </c>
       <c r="KT9" t="n">
         <v>0</v>
       </c>
       <c r="KU9" t="n">
-        <v>-27.66</v>
+        <v>-1.4</v>
       </c>
       <c r="KV9" t="n">
-        <v>4.17</v>
+        <v>31</v>
       </c>
       <c r="KW9" t="n">
-        <v>186.01</v>
+        <v>533.96</v>
       </c>
       <c r="KX9" t="n">
-        <v>39.02</v>
+        <v>49.76</v>
       </c>
       <c r="KY9" t="n">
-        <v>240.12</v>
+        <v>1497.55</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2023-Q4</t>
+          <t>2025-Q4</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-7044.45</v>
+        <v>2800.79428890999</v>
       </c>
       <c r="C10" t="n">
-        <v>3952.78</v>
+        <v>14300.39618565</v>
       </c>
       <c r="D10" t="n">
-        <v>-1233.03</v>
+        <v>-1864.68798804035</v>
       </c>
       <c r="E10" t="n">
-        <v>9988.58</v>
+        <v>13967.5</v>
       </c>
       <c r="F10" t="n">
-        <v>42067.45</v>
+        <v>44651.99</v>
       </c>
       <c r="G10" t="n">
-        <v>232.09</v>
+        <v>3491.41591012036</v>
       </c>
       <c r="H10" t="n">
-        <v>-1852.15</v>
+        <v>474.92</v>
       </c>
       <c r="I10" t="n">
-        <v>2743.65</v>
+        <v>8269.831603360009</v>
       </c>
       <c r="J10" t="n">
-        <v>-2576.71</v>
+        <v>-602.279999999995</v>
       </c>
       <c r="K10" t="n">
-        <v>46278.21</v>
+        <v>85489.88</v>
       </c>
       <c r="L10" t="n">
-        <v>-13481.69</v>
+        <v>-842.594366286802</v>
       </c>
       <c r="M10" t="n">
-        <v>25237.98</v>
+        <v>53332.471293028</v>
       </c>
       <c r="N10" t="n">
-        <v>-4189.6</v>
+        <v>-5509.67169685487</v>
       </c>
       <c r="O10" t="n">
-        <v>47142.45</v>
+        <v>55519.58</v>
       </c>
       <c r="P10" t="n">
-        <v>29085.03</v>
+        <v>29560.27</v>
       </c>
       <c r="Q10" t="n">
-        <v>29373.27</v>
+        <v>7983.72808455369</v>
       </c>
       <c r="R10" t="n">
-        <v>-2782.3</v>
+        <v>2575.77</v>
       </c>
       <c r="S10" t="n">
-        <v>7637.73</v>
+        <v>53305.96668556</v>
       </c>
       <c r="T10" t="n">
-        <v>-4919.69</v>
+        <v>6425.86</v>
       </c>
       <c r="U10" t="n">
-        <v>113103.18</v>
+        <v>202351.38</v>
       </c>
       <c r="V10" t="n">
-        <v>-11.91981516</v>
+        <v>-0.416401591274941</v>
       </c>
       <c r="W10" t="n">
-        <v>22.3141206</v>
+        <v>26.3563664814285</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.7042283</v>
+        <v>-2.72282388034857</v>
       </c>
       <c r="Y10" t="n">
-        <v>41.6809236</v>
+        <v>27.437213425478</v>
       </c>
       <c r="Z10" t="n">
-        <v>25.71548386</v>
+        <v>14.6083856705104</v>
       </c>
       <c r="AA10" t="n">
-        <v>25.9703308</v>
+        <v>3.94547745834681</v>
       </c>
       <c r="AB10" t="n">
-        <v>-2.4599662</v>
+        <v>1.27291941374455</v>
       </c>
       <c r="AC10" t="n">
-        <v>6.75288705</v>
+        <v>26.3432681731946</v>
       </c>
       <c r="AD10" t="n">
-        <v>-4.34973623</v>
+        <v>3.17559484892072</v>
       </c>
       <c r="AE10" t="n">
         <v>100</v>
       </c>
       <c r="AF10" t="n">
-        <v>578002.62</v>
+        <v>628732.565667425</v>
       </c>
       <c r="AG10" t="n">
-        <v>631916.65</v>
+        <v>860084.683494149</v>
       </c>
       <c r="AH10" t="n">
-        <v>150511.92</v>
+        <v>177034.493353897</v>
       </c>
       <c r="AI10" t="n">
-        <v>1571956.81</v>
+        <v>2216419.76</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2177583.19</v>
+        <v>2859093.89</v>
       </c>
       <c r="AK10" t="n">
-        <v>727463.4399999999</v>
+        <v>894816.96356121</v>
       </c>
       <c r="AL10" t="n">
-        <v>129547.79</v>
+        <v>139669.23</v>
       </c>
       <c r="AM10" t="n">
-        <v>713499.5</v>
+        <v>781962.003923318</v>
       </c>
       <c r="AN10" t="n">
-        <v>141760.76</v>
+        <v>181114.79</v>
       </c>
       <c r="AO10" t="n">
-        <v>6822242.68</v>
+        <v>8738928.380000001</v>
       </c>
       <c r="AP10" t="n">
-        <v>8.472325700000001</v>
+        <v>7.19461858854856</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9.26259413</v>
+        <v>9.841992588731451</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.206194166</v>
+        <v>2.02581467264408</v>
       </c>
       <c r="AS10" t="n">
-        <v>23.0416431</v>
+        <v>25.3626035552886</v>
       </c>
       <c r="AT10" t="n">
-        <v>31.9188761</v>
+        <v>32.7167561705089</v>
       </c>
       <c r="AU10" t="n">
-        <v>10.6631129</v>
+        <v>10.2394358284146</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.89890328</v>
+        <v>1.59824207187289</v>
       </c>
       <c r="AW10" t="n">
-        <v>10.45843036</v>
+        <v>8.948030810195499</v>
       </c>
       <c r="AX10" t="n">
-        <v>2.07792022</v>
+        <v>2.07250571379554</v>
       </c>
       <c r="AY10" t="n">
         <v>100</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-6939.18</v>
+        <v>-1765.12458791001</v>
       </c>
       <c r="BA10" t="n">
-        <v>3617.95</v>
+        <v>7391.93938583</v>
       </c>
       <c r="BB10" t="n">
-        <v>-961.09</v>
+        <v>-1629.39176639026</v>
       </c>
       <c r="BC10" t="n">
-        <v>11244.6</v>
+        <v>7368.11</v>
       </c>
       <c r="BD10" t="n">
-        <v>17549.46</v>
+        <v>32451.96</v>
       </c>
       <c r="BE10" t="n">
-        <v>4249.73</v>
+        <v>716.093239510279</v>
       </c>
       <c r="BF10" t="n">
-        <v>-850.46</v>
+        <v>687.37</v>
       </c>
       <c r="BG10" t="n">
-        <v>-1530.08</v>
+        <v>1237.84372896</v>
       </c>
       <c r="BH10" t="n">
-        <v>-2801.88</v>
+        <v>-188.189999999995</v>
       </c>
       <c r="BI10" t="n">
-        <v>23579.05</v>
+        <v>46270.61</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-10923.4</v>
+        <v>-12508.0494447632</v>
       </c>
       <c r="BK10" t="n">
-        <v>21144.97</v>
+        <v>33074.8769030433</v>
       </c>
       <c r="BL10" t="n">
-        <v>-2949.35</v>
+        <v>-4671.39366778368</v>
       </c>
       <c r="BM10" t="n">
-        <v>44966.74</v>
+        <v>55768.87</v>
       </c>
       <c r="BN10" t="n">
-        <v>15552.68</v>
+        <v>18152.81</v>
       </c>
       <c r="BO10" t="n">
-        <v>33891.51</v>
+        <v>-3107.4052856264</v>
       </c>
       <c r="BP10" t="n">
-        <v>-1230.65</v>
+        <v>-65.6599999999989</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8056.11</v>
+        <v>11931.54149513</v>
       </c>
       <c r="BR10" t="n">
-        <v>-2069.47</v>
+        <v>3660.45</v>
       </c>
       <c r="BS10" t="n">
-        <v>106439.14</v>
+        <v>102236.04</v>
       </c>
       <c r="BT10" t="n">
-        <v>-10.26257822</v>
+        <v>-2.71913959037315</v>
       </c>
       <c r="BU10" t="n">
-        <v>19.86578433</v>
+        <v>28.2422247125236</v>
       </c>
       <c r="BV10" t="n">
-        <v>-2.770926184</v>
+        <v>-2.68952545425304</v>
       </c>
       <c r="BW10" t="n">
-        <v>42.246433</v>
+        <v>12.7058977999822</v>
       </c>
       <c r="BX10" t="n">
-        <v>14.6118054</v>
+        <v>-9.76802068918659</v>
       </c>
       <c r="BY10" t="n">
-        <v>31.8412099</v>
+        <v>55.0236956091094</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-1.156200623</v>
+        <v>0.7562928605850751</v>
       </c>
       <c r="CA10" t="n">
-        <v>7.56874774</v>
+        <v>18.8951949129049</v>
       </c>
       <c r="CB10" t="n">
-        <v>-1.944275386</v>
+        <v>-0.446620161292406</v>
       </c>
       <c r="CC10" t="n">
         <v>100</v>
       </c>
       <c r="CD10" t="n">
-        <v>401564.6</v>
+        <v>424191.912514406</v>
       </c>
       <c r="CE10" t="n">
-        <v>305510.01</v>
+        <v>443197.166485526</v>
       </c>
       <c r="CF10" t="n">
-        <v>91051.24000000001</v>
+        <v>105252.198838984</v>
       </c>
       <c r="CG10" t="n">
-        <v>972126.5</v>
+        <v>1467277.16</v>
       </c>
       <c r="CH10" t="n">
-        <v>1682798.1</v>
+        <v>2222430.51</v>
       </c>
       <c r="CI10" t="n">
-        <v>493686.05</v>
+        <v>656430.683952939</v>
       </c>
       <c r="CJ10" t="n">
-        <v>61476.64</v>
+        <v>65796.00999999999</v>
       </c>
       <c r="CK10" t="n">
-        <v>456138.36</v>
+        <v>452093.838208145</v>
       </c>
       <c r="CL10" t="n">
-        <v>73709.19</v>
+        <v>93611.3300000001</v>
       </c>
       <c r="CM10" t="n">
-        <v>4538060.69</v>
+        <v>5930280.81</v>
       </c>
       <c r="CN10" t="n">
-        <v>8.84881511</v>
+        <v>7.15298189251187</v>
       </c>
       <c r="CO10" t="n">
-        <v>6.7321711</v>
+        <v>7.47346003815166</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.006390972</v>
+        <v>1.77482655899703</v>
       </c>
       <c r="CQ10" t="n">
-        <v>21.42162845</v>
+        <v>24.7421194208171</v>
       </c>
       <c r="CR10" t="n">
-        <v>37.0818774</v>
+        <v>37.475974261664</v>
       </c>
       <c r="CS10" t="n">
-        <v>10.87878906</v>
+        <v>11.0691332330507</v>
       </c>
       <c r="CT10" t="n">
-        <v>1.354689684</v>
+        <v>1.1094923176159</v>
       </c>
       <c r="CU10" t="n">
-        <v>10.051394</v>
+        <v>7.62348112497129</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.624244254</v>
+        <v>1.57853115222043</v>
       </c>
       <c r="CW10" t="n">
         <v>100</v>
       </c>
       <c r="CX10" t="n">
-        <v>-1239.42</v>
+        <v>809.9950665699999</v>
       </c>
       <c r="CY10" t="n">
-        <v>-1419.83</v>
+        <v>3927.37031031</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-212.96</v>
+        <v>-277.702021500091</v>
       </c>
       <c r="DA10" t="n">
-        <v>-1478.69</v>
+        <v>-203.75</v>
       </c>
       <c r="DB10" t="n">
-        <v>5546.34</v>
+        <v>5362.54</v>
       </c>
       <c r="DC10" t="n">
-        <v>-448.82</v>
+        <v>-343.880323789912</v>
       </c>
       <c r="DD10" t="n">
-        <v>217.35</v>
+        <v>-3.26999999999998</v>
       </c>
       <c r="DE10" t="n">
-        <v>-1106.96</v>
+        <v>-678.433031590001</v>
       </c>
       <c r="DF10" t="n">
-        <v>206.17</v>
+        <v>79.4199999999983</v>
       </c>
       <c r="DG10" t="n">
-        <v>63.18</v>
+        <v>8672.290000000001</v>
       </c>
       <c r="DH10" t="n">
-        <v>-3729.34</v>
+        <v>1979.97208940704</v>
       </c>
       <c r="DI10" t="n">
-        <v>570.28</v>
+        <v>9281.868891519811</v>
       </c>
       <c r="DJ10" t="n">
-        <v>-861.24</v>
+        <v>-943.795790150278</v>
       </c>
       <c r="DK10" t="n">
-        <v>-4118.86</v>
+        <v>140.960000000001</v>
       </c>
       <c r="DL10" t="n">
-        <v>537.52</v>
+        <v>1966.69</v>
       </c>
       <c r="DM10" t="n">
-        <v>-1208.69</v>
+        <v>-6054.30041557658</v>
       </c>
       <c r="DN10" t="n">
-        <v>148.12</v>
+        <v>572.99</v>
       </c>
       <c r="DO10" t="n">
-        <v>-2567.17</v>
+        <v>-525.854775200005</v>
       </c>
       <c r="DP10" t="n">
-        <v>-747.1799999999999</v>
+        <v>-152.950000000002</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-11976.56</v>
+        <v>6265.57999999999</v>
       </c>
       <c r="DR10" t="n">
-        <v>31.1386575</v>
+        <v>13.1335005231091</v>
       </c>
       <c r="DS10" t="n">
-        <v>-4.76163439</v>
+        <v>-0.912235624756391</v>
       </c>
       <c r="DT10" t="n">
-        <v>7.19104651</v>
+        <v>2.5992625187191</v>
       </c>
       <c r="DU10" t="n">
-        <v>34.39101044</v>
+        <v>29.3346257205572</v>
       </c>
       <c r="DV10" t="n">
-        <v>-4.48810009</v>
+        <v>39.0886875089749</v>
       </c>
       <c r="DW10" t="n">
-        <v>10.09212996</v>
+        <v>4.42975978008903</v>
       </c>
       <c r="DX10" t="n">
-        <v>-1.236749117</v>
+        <v>-1.37303321230024</v>
       </c>
       <c r="DY10" t="n">
-        <v>21.43495294</v>
+        <v>5.54957228137114</v>
       </c>
       <c r="DZ10" t="n">
-        <v>6.23868623</v>
+        <v>8.149860504236161</v>
       </c>
       <c r="EA10" t="n">
         <v>100</v>
       </c>
       <c r="EB10" t="n">
-        <v>99862.78999999999</v>
+        <v>104791.499677316</v>
       </c>
       <c r="EC10" t="n">
-        <v>263990.26</v>
+        <v>327510.538866278</v>
       </c>
       <c r="ED10" t="n">
-        <v>55639.46</v>
+        <v>67594.9999868849</v>
       </c>
       <c r="EE10" t="n">
-        <v>445316.03</v>
+        <v>533751.04</v>
       </c>
       <c r="EF10" t="n">
-        <v>354186.98</v>
+        <v>444163.2</v>
       </c>
       <c r="EG10" t="n">
-        <v>94136.44</v>
+        <v>81989.84791759439</v>
       </c>
       <c r="EH10" t="n">
-        <v>33601.5</v>
+        <v>37257.53</v>
       </c>
       <c r="EI10" t="n">
-        <v>11843.05</v>
+        <v>36472.7435519267</v>
       </c>
       <c r="EJ10" t="n">
-        <v>14830.58</v>
+        <v>10422.75</v>
       </c>
       <c r="EK10" t="n">
-        <v>1373407.09</v>
+        <v>1643954.15</v>
       </c>
       <c r="EL10" t="n">
-        <v>7.27117187</v>
+        <v>6.37435658879635</v>
       </c>
       <c r="EM10" t="n">
-        <v>19.22155943</v>
+        <v>19.9221212383738</v>
       </c>
       <c r="EN10" t="n">
-        <v>4.051199415</v>
+        <v>4.11173267739157</v>
       </c>
       <c r="EO10" t="n">
-        <v>32.4241831</v>
+        <v>32.4675137685561</v>
       </c>
       <c r="EP10" t="n">
-        <v>25.78892905</v>
+        <v>27.0179797897648</v>
       </c>
       <c r="EQ10" t="n">
-        <v>6.85422703</v>
+        <v>4.9873561204608</v>
       </c>
       <c r="ER10" t="n">
-        <v>2.44657977</v>
+        <v>2.2663363208761</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.862311698</v>
+        <v>2.21859858755347</v>
       </c>
       <c r="ET10" t="n">
-        <v>1.079838608</v>
+        <v>0.634004908226911</v>
       </c>
       <c r="EU10" t="n">
         <v>100</v>
       </c>
       <c r="EV10" t="n">
-        <v>706.1799999999999</v>
+        <v>-605.7320212600021</v>
       </c>
       <c r="EW10" t="n">
-        <v>1180.96</v>
+        <v>2933.36736251</v>
       </c>
       <c r="EX10" t="n">
-        <v>-26.88</v>
+        <v>13.2593378500001</v>
       </c>
       <c r="EY10" t="n">
-        <v>2214.89</v>
+        <v>4774.32</v>
       </c>
       <c r="EZ10" t="n">
-        <v>19512.52</v>
+        <v>6887.15</v>
       </c>
       <c r="FA10" t="n">
-        <v>-1458.86</v>
+        <v>1141.48577966</v>
       </c>
       <c r="FB10" t="n">
-        <v>-975.39</v>
+        <v>-78.0100000000002</v>
       </c>
       <c r="FC10" t="n">
-        <v>6975.84</v>
+        <v>3335.72954124</v>
       </c>
       <c r="FD10" t="n">
-        <v>226.31</v>
+        <v>-1031.07</v>
       </c>
       <c r="FE10" t="n">
-        <v>28355.57</v>
+        <v>17370.5</v>
       </c>
       <c r="FF10" t="n">
-        <v>1887.02</v>
+        <v>1502.6534907681</v>
       </c>
       <c r="FG10" t="n">
-        <v>5499.69</v>
+        <v>13582.5639565678</v>
       </c>
       <c r="FH10" t="n">
-        <v>-205.77</v>
+        <v>2.85396139074979</v>
       </c>
       <c r="FI10" t="n">
-        <v>8928.73</v>
+        <v>2609.32</v>
       </c>
       <c r="FJ10" t="n">
-        <v>17086.67</v>
+        <v>7954.06</v>
       </c>
       <c r="FK10" t="n">
-        <v>4323.43</v>
+        <v>7263.74730697333</v>
       </c>
       <c r="FL10" t="n">
-        <v>84.3</v>
+        <v>1821.9</v>
       </c>
       <c r="FM10" t="n">
-        <v>11634.52</v>
+        <v>36149.2912843</v>
       </c>
       <c r="FN10" t="n">
-        <v>1269.73</v>
+        <v>900.740000000001</v>
       </c>
       <c r="FO10" t="n">
-        <v>50508.32</v>
+        <v>71787.13</v>
       </c>
       <c r="FP10" t="n">
-        <v>3.73605774</v>
+        <v>3.76417097960845</v>
       </c>
       <c r="FQ10" t="n">
-        <v>10.8886813</v>
+        <v>16.2120636341365</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0.407398227</v>
+        <v>-0.5777380830669691</v>
       </c>
       <c r="FS10" t="n">
-        <v>17.677741</v>
+        <v>44.3645942041007</v>
       </c>
       <c r="FT10" t="n">
-        <v>33.8294166</v>
+        <v>-20.5396980329899</v>
       </c>
       <c r="FU10" t="n">
-        <v>8.559837269999999</v>
+        <v>-11.8257873730953</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.1669031954</v>
+        <v>5.92359968441419</v>
       </c>
       <c r="FW10" t="n">
-        <v>23.0348584</v>
+        <v>40.3639267671166</v>
       </c>
       <c r="FX10" t="n">
-        <v>2.51390266</v>
+        <v>22.3148682197758</v>
       </c>
       <c r="FY10" t="n">
         <v>100</v>
       </c>
       <c r="FZ10" t="n">
-        <v>25037.43</v>
+        <v>32583.375578488</v>
       </c>
       <c r="GA10" t="n">
-        <v>51619.35</v>
+        <v>77253.3766761765</v>
       </c>
       <c r="GB10" t="n">
-        <v>1883.22</v>
+        <v>1990.55089631356</v>
       </c>
       <c r="GC10" t="n">
-        <v>86986.42</v>
+        <v>141116.98</v>
       </c>
       <c r="GD10" t="n">
-        <v>128625.24</v>
+        <v>179368.32</v>
       </c>
       <c r="GE10" t="n">
-        <v>70363.42</v>
+        <v>79143.8299525332</v>
       </c>
       <c r="GF10" t="n">
-        <v>23857.22</v>
+        <v>26059.57</v>
       </c>
       <c r="GG10" t="n">
-        <v>147312.91</v>
+        <v>174486.356896489</v>
       </c>
       <c r="GH10" t="n">
-        <v>37151.39</v>
+        <v>53388.06</v>
       </c>
       <c r="GI10" t="n">
-        <v>572836.6</v>
+        <v>765390.42</v>
       </c>
       <c r="GJ10" t="n">
-        <v>4.37078043</v>
+        <v>4.25709216199596</v>
       </c>
       <c r="GK10" t="n">
-        <v>9.011182249999999</v>
+        <v>10.0933294508934</v>
       </c>
       <c r="GL10" t="n">
-        <v>0.328753435</v>
+        <v>0.260070004052776</v>
       </c>
       <c r="GM10" t="n">
-        <v>15.1852064</v>
+        <v>18.4372545452032</v>
       </c>
       <c r="GN10" t="n">
-        <v>22.454089</v>
+        <v>23.4348791561828</v>
       </c>
       <c r="GO10" t="n">
-        <v>12.28333176</v>
+        <v>10.3403214731291</v>
       </c>
       <c r="GP10" t="n">
-        <v>4.164751344</v>
+        <v>3.40474211840801</v>
       </c>
       <c r="GQ10" t="n">
-        <v>25.71639277</v>
+        <v>22.7970395679226</v>
       </c>
       <c r="GR10" t="n">
-        <v>6.48551262</v>
+        <v>6.97527152221215</v>
       </c>
       <c r="GS10" t="n">
         <v>100</v>
       </c>
       <c r="GT10" t="n">
-        <v>185.78</v>
+        <v>2691.04583151</v>
       </c>
       <c r="GU10" t="n">
-        <v>331.36</v>
+        <v>206.079126999999</v>
       </c>
       <c r="GV10" t="n">
-        <v>-25.45</v>
+        <v>34.056462000002</v>
       </c>
       <c r="GW10" t="n">
-        <v>-1879.05</v>
+        <v>2101.11</v>
       </c>
       <c r="GX10" t="n">
-        <v>-509.92</v>
+        <v>-50.8900000000001</v>
       </c>
       <c r="GY10" t="n">
-        <v>-1914.68</v>
+        <v>1757.21721474</v>
       </c>
       <c r="GZ10" t="n">
-        <v>-334.01</v>
+        <v>-66.1699999999998</v>
       </c>
       <c r="HA10" t="n">
-        <v>-1748.59</v>
+        <v>3778.19136475</v>
       </c>
       <c r="HB10" t="n">
-        <v>-343.22</v>
+        <v>447.400000000001</v>
       </c>
       <c r="HC10" t="n">
-        <v>-6237.78</v>
+        <v>10898.04</v>
       </c>
       <c r="HD10" t="n">
-        <v>-337.42</v>
+        <v>5016.11949830125</v>
       </c>
       <c r="HE10" t="n">
-        <v>1311.78</v>
+        <v>-1957.05845810292</v>
       </c>
       <c r="HF10" t="n">
-        <v>-136.97</v>
+        <v>119.093799688338</v>
       </c>
       <c r="HG10" t="n">
-        <v>-2170.19</v>
+        <v>-2724.13</v>
       </c>
       <c r="HH10" t="n">
-        <v>-2088.12</v>
+        <v>1513.95</v>
       </c>
       <c r="HI10" t="n">
-        <v>-7175.04</v>
+        <v>9322.856478783329</v>
       </c>
       <c r="HJ10" t="n">
-        <v>-1513.83</v>
+        <v>144.31</v>
       </c>
       <c r="HK10" t="n">
-        <v>-7845.6</v>
+        <v>4416.49868132998</v>
       </c>
       <c r="HL10" t="n">
-        <v>-3503.14</v>
+        <v>1649.19</v>
       </c>
       <c r="HM10" t="n">
-        <v>-23458.53</v>
+        <v>17500.83</v>
       </c>
       <c r="HN10" t="n">
-        <v>1.438368048</v>
+        <v>8.795261903733831</v>
       </c>
       <c r="HO10" t="n">
-        <v>-5.59191049</v>
+        <v>0.911589477457792</v>
       </c>
       <c r="HP10" t="n">
-        <v>0.583881428</v>
+        <v>0.617567226962483</v>
       </c>
       <c r="HQ10" t="n">
-        <v>9.25117644</v>
+        <v>25.6911983113804</v>
       </c>
       <c r="HR10" t="n">
-        <v>8.90132502</v>
+        <v>13.973186536432</v>
       </c>
       <c r="HS10" t="n">
-        <v>30.58605974</v>
+        <v>33.9001228105234</v>
       </c>
       <c r="HT10" t="n">
-        <v>6.45321766</v>
+        <v>3.07427978104983</v>
       </c>
       <c r="HU10" t="n">
-        <v>33.4445509</v>
+        <v>6.77516435823715</v>
       </c>
       <c r="HV10" t="n">
-        <v>14.9333313</v>
+        <v>6.26162959422319</v>
       </c>
       <c r="HW10" t="n">
         <v>100</v>
       </c>
       <c r="HX10" t="n">
-        <v>44633.66</v>
+        <v>54103.937897215</v>
       </c>
       <c r="HY10" t="n">
-        <v>4888.9</v>
+        <v>7909.32146616821</v>
       </c>
       <c r="HZ10" t="n">
-        <v>1579.98</v>
+        <v>1907.96363171479</v>
       </c>
       <c r="IA10" t="n">
-        <v>60082.31</v>
+        <v>67005.52</v>
       </c>
       <c r="IB10" t="n">
-        <v>11679.91</v>
+        <v>12956.64</v>
       </c>
       <c r="IC10" t="n">
-        <v>68121.03999999999</v>
+        <v>75182.6217381437</v>
       </c>
       <c r="ID10" t="n">
-        <v>7399.19</v>
+        <v>7201.75</v>
       </c>
       <c r="IE10" t="n">
-        <v>69173.92</v>
+        <v>87598.2152667584</v>
       </c>
       <c r="IF10" t="n">
-        <v>12108.11</v>
+        <v>18910.52</v>
       </c>
       <c r="IG10" t="n">
-        <v>279667.02</v>
+        <v>332776.49</v>
       </c>
       <c r="IH10" t="n">
-        <v>15.9595722</v>
+        <v>16.2583414162506</v>
       </c>
       <c r="II10" t="n">
-        <v>1.748114597</v>
+        <v>2.37676690026035</v>
       </c>
       <c r="IJ10" t="n">
-        <v>0.564950419</v>
+        <v>0.573346882682363</v>
       </c>
       <c r="IK10" t="n">
-        <v>21.48351636</v>
+        <v>20.1352926103644</v>
       </c>
       <c r="IL10" t="n">
-        <v>4.17636302</v>
+        <v>3.89349620221068</v>
       </c>
       <c r="IM10" t="n">
-        <v>24.35790963</v>
+        <v>22.5925280172718</v>
       </c>
       <c r="IN10" t="n">
-        <v>2.64571418</v>
+        <v>2.16414026123059</v>
       </c>
       <c r="IO10" t="n">
-        <v>24.7343859</v>
+        <v>26.3234386740356</v>
       </c>
       <c r="IP10" t="n">
-        <v>4.32947367</v>
+        <v>5.6826490356936</v>
       </c>
       <c r="IQ10" t="n">
         <v>100</v>
       </c>
       <c r="IR10" t="n">
-        <v>297.92</v>
+        <v>108</v>
       </c>
       <c r="IS10" t="n">
-        <v>245.05</v>
+        <v>-154.07</v>
       </c>
       <c r="IT10" t="n">
-        <v>-6.22</v>
+        <v>-3.98</v>
       </c>
       <c r="IU10" t="n">
-        <v>-106.7</v>
+        <v>-46.07</v>
       </c>
       <c r="IV10" t="n">
-        <v>-30.95</v>
+        <v>1.23</v>
       </c>
       <c r="IW10" t="n">
-        <v>-161.58</v>
+        <v>223.4</v>
       </c>
       <c r="IX10" t="n">
-        <v>63.86</v>
+        <v>-64.90000000000001</v>
       </c>
       <c r="IY10" t="n">
-        <v>-224.69</v>
+        <v>-66.2900000000004</v>
       </c>
       <c r="IZ10" t="n">
-        <v>99</v>
+        <v>7.55000000000001</v>
       </c>
       <c r="JA10" t="n">
-        <v>175.69</v>
+        <v>4.86999999999961</v>
       </c>
       <c r="JB10" t="n">
-        <v>-125.16</v>
+        <v>171.22</v>
       </c>
       <c r="JC10" t="n">
-        <v>-3284.58</v>
+        <v>-630.7</v>
       </c>
       <c r="JD10" t="n">
-        <v>-34.62</v>
+        <v>-11.96</v>
       </c>
       <c r="JE10" t="n">
-        <v>-505.09</v>
+        <v>-210.04</v>
       </c>
       <c r="JF10" t="n">
-        <v>-2003.72</v>
+        <v>-27.24</v>
       </c>
       <c r="JG10" t="n">
-        <v>-430.57</v>
+        <v>566.8</v>
       </c>
       <c r="JH10" t="n">
-        <v>-577.16</v>
+        <v>62.17</v>
       </c>
       <c r="JI10" t="n">
-        <v>-3621.4</v>
+        <v>-720</v>
       </c>
       <c r="JJ10" t="n">
-        <v>-280.13</v>
+        <v>55.98</v>
       </c>
       <c r="JK10" t="n">
-        <v>-10862.43</v>
+        <v>-743.77</v>
       </c>
       <c r="JL10" t="n">
-        <v>1.152228369</v>
+        <v>6.07648590799338</v>
       </c>
       <c r="JM10" t="n">
-        <v>30.2379854</v>
+        <v>37.8074883225609</v>
       </c>
       <c r="JN10" t="n">
-        <v>0.318713216</v>
+        <v>0.258678560256992</v>
       </c>
       <c r="JO10" t="n">
-        <v>4.64988037</v>
+        <v>2.81312934279478</v>
       </c>
       <c r="JP10" t="n">
-        <v>18.4463329</v>
+        <v>1.26738435908521</v>
       </c>
       <c r="JQ10" t="n">
-        <v>3.96384603</v>
+        <v>0.541959700973208</v>
       </c>
       <c r="JR10" t="n">
-        <v>5.3133599</v>
+        <v>6.88977692488832</v>
       </c>
       <c r="JS10" t="n">
-        <v>33.3387649</v>
+        <v>40.2329512904054</v>
       </c>
       <c r="JT10" t="n">
-        <v>2.578888886</v>
+        <v>4.11214559104185</v>
       </c>
       <c r="JU10" t="n">
         <v>100</v>
       </c>
       <c r="JV10" t="n">
-        <v>2019.43</v>
+        <v>1561.71</v>
       </c>
       <c r="JW10" t="n">
-        <v>5786.97</v>
+        <v>4084.09</v>
       </c>
       <c r="JX10" t="n">
-        <v>306.04</v>
+        <v>234.6</v>
       </c>
       <c r="JY10" t="n">
-        <v>2036</v>
+        <v>1376.45</v>
       </c>
       <c r="JZ10" t="n">
-        <v>292.96</v>
+        <v>175.22</v>
       </c>
       <c r="KA10" t="n">
-        <v>1116.74</v>
+        <v>2034.21</v>
       </c>
       <c r="KB10" t="n">
-        <v>1243.84</v>
+        <v>1108.67</v>
       </c>
       <c r="KC10" t="n">
-        <v>8261.42</v>
+        <v>6824.58</v>
       </c>
       <c r="KD10" t="n">
-        <v>1119.14</v>
+        <v>1104.27</v>
       </c>
       <c r="KE10" t="n">
-        <v>22182.54</v>
+        <v>18503.8</v>
       </c>
       <c r="KF10" t="n">
-        <v>9.10369146</v>
+        <v>8.439942065954019</v>
       </c>
       <c r="KG10" t="n">
-        <v>26.08795025</v>
+        <v>22.0716285303559</v>
       </c>
       <c r="KH10" t="n">
-        <v>1.37964363</v>
+        <v>1.26784768534031</v>
       </c>
       <c r="KI10" t="n">
-        <v>9.17838985</v>
+        <v>7.43874231238989</v>
       </c>
       <c r="KJ10" t="n">
-        <v>1.320678335</v>
+        <v>0.946940628411462</v>
       </c>
       <c r="KK10" t="n">
-        <v>5.03431978</v>
+        <v>10.9934716112366</v>
       </c>
       <c r="KL10" t="n">
-        <v>5.60729294</v>
+        <v>5.99158010786974</v>
       </c>
       <c r="KM10" t="n">
-        <v>37.2428946</v>
+        <v>36.8820458500416</v>
       </c>
       <c r="KN10" t="n">
-        <v>5.0451391</v>
+        <v>5.96780120840044</v>
       </c>
       <c r="KO10" t="n">
         <v>100</v>
       </c>
       <c r="KP10" t="n">
-        <v>-55.73</v>
+        <v>1562.61</v>
       </c>
       <c r="KQ10" t="n">
-        <v>-2.71</v>
+        <v>-4.29</v>
       </c>
       <c r="KR10" t="n">
-        <v>-0.43</v>
+        <v>-0.93</v>
       </c>
       <c r="KS10" t="n">
-        <v>-6.47</v>
+        <v>-26.22</v>
       </c>
       <c r="KT10" t="n">
         <v>0</v>
       </c>
       <c r="KU10" t="n">
-        <v>-33.7</v>
+        <v>-2.9</v>
       </c>
       <c r="KV10" t="n">
-        <v>26.5</v>
+        <v>-0.1</v>
       </c>
       <c r="KW10" t="n">
-        <v>378.13</v>
+        <v>662.79</v>
       </c>
       <c r="KX10" t="n">
-        <v>36.91</v>
+        <v>82.61</v>
       </c>
       <c r="KY10" t="n">
-        <v>342.5</v>
+        <v>2273.57</v>
       </c>
       <c r="KZ10" t="n">
-        <v>-253.39</v>
+        <v>2995.49</v>
       </c>
       <c r="LA10" t="n">
-        <v>-4.16</v>
+        <v>-19.08</v>
       </c>
       <c r="LB10" t="n">
-        <v>-1.65</v>
+        <v>-4.47</v>
       </c>
       <c r="LC10" t="n">
-        <v>41.12</v>
+        <v>-65.40000000000001</v>
       </c>
       <c r="LD10" t="n">
         <v>0</v>
       </c>
       <c r="LE10" t="n">
-        <v>-27.37</v>
+        <v>-7.97</v>
       </c>
       <c r="LF10" t="n">
-        <v>306.92</v>
+        <v>40.06</v>
       </c>
       <c r="LG10" t="n">
-        <v>1981.27</v>
+        <v>2054.49</v>
       </c>
       <c r="LH10" t="n">
-        <v>410.5</v>
+        <v>312.45</v>
       </c>
       <c r="LI10" t="n">
-        <v>2453.24</v>
+        <v>5305.57</v>
       </c>
       <c r="LJ10" t="n">
-        <v>-10.32878968</v>
+        <v>-153.075720983094</v>
       </c>
       <c r="LK10" t="n">
-        <v>-0.1695716685</v>
+        <v>-0.362267367523796</v>
       </c>
       <c r="LL10" t="n">
-        <v>-0.0672579935</v>
+        <v>-0.546952692143771</v>
       </c>
       <c r="LM10" t="n">
-        <v>1.676150723</v>
+        <v>-2.4861486006535</v>
       </c>
       <c r="LN10" t="n">
         <v>0</v>
       </c>
       <c r="LO10" t="n">
-        <v>-1.115667444</v>
+        <v>0.220201733200739</v>
       </c>
       <c r="LP10" t="n">
-        <v>12.51080204</v>
+        <v>2.7276601790027</v>
       </c>
       <c r="LQ10" t="n">
-        <v>80.76136049999999</v>
+        <v>259.170336695553</v>
       </c>
       <c r="LR10" t="n">
-        <v>16.73297354</v>
+        <v>-5.64710896434152</v>
       </c>
       <c r="LS10" t="n">
         <v>100</v>
       </c>
       <c r="LT10" t="n">
-        <v>4884.71</v>
+        <v>11500.13</v>
       </c>
       <c r="LU10" t="n">
-        <v>121.16</v>
+        <v>130.19</v>
       </c>
       <c r="LV10" t="n">
-        <v>51.98</v>
+        <v>54.18</v>
       </c>
       <c r="LW10" t="n">
-        <v>5409.55</v>
+        <v>5892.61</v>
       </c>
       <c r="LX10" t="n">
         <v>0</v>
       </c>
       <c r="LY10" t="n">
-        <v>39.75</v>
+        <v>35.77</v>
       </c>
       <c r="LZ10" t="n">
-        <v>1969.4</v>
+        <v>2245.7</v>
       </c>
       <c r="MA10" t="n">
-        <v>20769.84</v>
+        <v>24486.27</v>
       </c>
       <c r="MB10" t="n">
-        <v>2842.35</v>
+        <v>3677.86</v>
       </c>
       <c r="MC10" t="n">
-        <v>36088.74</v>
+        <v>48022.71</v>
       </c>
       <c r="MD10" t="n">
-        <v>13.53527444</v>
+        <v>23.9472741126021</v>
       </c>
       <c r="ME10" t="n">
-        <v>0.335727986</v>
+        <v>0.271100902052383</v>
       </c>
       <c r="MF10" t="n">
-        <v>0.1440338455</v>
+        <v>0.112821621270436</v>
       </c>
       <c r="MG10" t="n">
-        <v>14.98957847</v>
+        <v>12.2704653694054</v>
       </c>
       <c r="MH10" t="n">
         <v>0</v>
       </c>
       <c r="MI10" t="n">
-        <v>0.1101451589</v>
+        <v>0.0744855923374587</v>
       </c>
       <c r="MJ10" t="n">
-        <v>5.4571038</v>
+        <v>4.67632917842412</v>
       </c>
       <c r="MK10" t="n">
-        <v>57.552134</v>
+        <v>50.9889383585391</v>
       </c>
       <c r="ML10" t="n">
-        <v>7.87600232</v>
+        <v>7.6585848653689</v>
       </c>
       <c r="MM10" t="n">
         <v>100</v>
@@ -7339,4293 +7339,877 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024-Q1</t>
+          <t>2026-Q1</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-2846.84</v>
+        <v>-1144.41550223</v>
       </c>
       <c r="C11" t="n">
-        <v>10436.47</v>
+        <v>8442.240090650021</v>
       </c>
       <c r="D11" t="n">
-        <v>-1270.42</v>
+        <v>-1728.83321435</v>
       </c>
       <c r="E11" t="n">
-        <v>4101.86</v>
+        <v>13281.13</v>
       </c>
       <c r="F11" t="n">
-        <v>-10013.14</v>
+        <v>-11049.65</v>
       </c>
       <c r="G11" t="n">
-        <v>14230.73</v>
+        <v>-589.7197543900151</v>
       </c>
       <c r="H11" t="n">
-        <v>486.72</v>
+        <v>1706.07</v>
       </c>
       <c r="I11" t="n">
-        <v>8888.57</v>
+        <v>-2241.05161967998</v>
       </c>
       <c r="J11" t="n">
-        <v>773.66</v>
+        <v>4715.11999999998</v>
       </c>
       <c r="K11" t="n">
-        <v>24787.61</v>
+        <v>11390.89</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-1144.41550223</v>
+      </c>
+      <c r="M11" t="n">
+        <v>8442.240090650021</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-1728.83321435</v>
+      </c>
+      <c r="O11" t="n">
+        <v>13281.13</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-11049.65</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-589.7197543900151</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1706.07</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-2241.05161967998</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4715.11999999998</v>
+      </c>
+      <c r="U11" t="n">
+        <v>11390.89</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-10.0467610716107</v>
+      </c>
+      <c r="W11" t="n">
+        <v>74.1139637960686</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-15.1773321869493</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>116.594313525984</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-97.0042727126675</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-5.17711745429913</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>14.9774951737748</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-19.6740695387276</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>41.3937804684267</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>610731.233018934</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>841375.131698034</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>171019.963015561</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>2148547.6</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>2802884.88</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>955168.076699018</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>137560.21</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>729896.295568453</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>172645.48</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>8569828.869999999</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>7.12652775549454</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>9.81787553125357</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.99560534533242</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>25.071067726</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>32.7064276605561</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>11.1457077053514</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.60516869224251</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>8.51704633360378</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>2.01457325016573</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>100</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-948.49</v>
+        <v>-2353.61092268</v>
       </c>
       <c r="BA11" t="n">
-        <v>9851.450000000001</v>
+        <v>4991.22255312002</v>
       </c>
       <c r="BB11" t="n">
-        <v>-938.16</v>
+        <v>-1622.53762901</v>
       </c>
       <c r="BC11" t="n">
-        <v>4432.07</v>
+        <v>9217.469999999999</v>
       </c>
       <c r="BD11" t="n">
-        <v>-3407.28</v>
+        <v>-18165.14</v>
       </c>
       <c r="BE11" t="n">
-        <v>19193.36</v>
+        <v>-784.714074230011</v>
       </c>
       <c r="BF11" t="n">
-        <v>263.81</v>
+        <v>641.79</v>
       </c>
       <c r="BG11" t="n">
-        <v>6591.02</v>
+        <v>-1142.65992719999</v>
       </c>
       <c r="BH11" t="n">
-        <v>-155.79</v>
+        <v>916.099999999984</v>
       </c>
       <c r="BI11" t="n">
-        <v>34881.99</v>
+        <v>-8302.07999999998</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>-2353.61092268</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>4991.22255312002</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>-1622.53762901</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>9217.469999999999</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>-18165.14</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>-784.714074230011</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>641.79</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>-1142.65992719999</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>916.099999999984</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>-8302.07999999998</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>409201.339263486</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>432580.995156433</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>100483.36710573</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>1407479.68</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>2167174.97</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>685767.384854662</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>63504.45</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>417531.91361969</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>85940.5299999998</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>5769664.63</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>7.09228985573613</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>7.49750675121013</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>1.74158072521678</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>24.3944799266435</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>37.5615414235957</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>11.885740832993</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>1.10066102750239</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>7.23667561973511</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>1.4895238373673</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>100</v>
       </c>
       <c r="CX11" t="n">
-        <v>-1024.35</v>
+        <v>-1359.33469086</v>
       </c>
       <c r="CY11" t="n">
-        <v>71.15000000000001</v>
+        <v>1961.95853563</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-202.73</v>
+        <v>-222.999559389998</v>
       </c>
       <c r="DA11" t="n">
-        <v>-2287.96</v>
+        <v>-3767.99</v>
       </c>
       <c r="DB11" t="n">
-        <v>-3048.73</v>
+        <v>-1534.02</v>
       </c>
       <c r="DC11" t="n">
-        <v>-345.5</v>
+        <v>-56.1431836300053</v>
       </c>
       <c r="DD11" t="n">
-        <v>107.09</v>
+        <v>174.26</v>
       </c>
       <c r="DE11" t="n">
-        <v>-432.84</v>
+        <v>-361.771101749997</v>
       </c>
       <c r="DF11" t="n">
-        <v>-635.65</v>
+        <v>-124.76</v>
       </c>
       <c r="DG11" t="n">
-        <v>-7799.52</v>
+        <v>-5290.8</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>-1359.33469086</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>1961.95853563</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>-222.999559389998</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>-3767.99</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>-1534.02</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>-56.1431836300053</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>174.26</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>-361.771101749997</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>-124.76</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>-5290.8</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>100727.014961925</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>319925.028353572</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>66294.1139212194</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>519816.38</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>435396.67</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>93911.02388008519</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>36683.48</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>34814.308883198</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>5480.88</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>1613048.9</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>6.24451093590067</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>19.8335604304105</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>4.10986386843073</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>32.2257049987759</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>26.9921556624849</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>5.82195765299398</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>2.27417036148129</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>2.15829221812172</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0.339783871400303</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>100</v>
       </c>
       <c r="EV11" t="n">
-        <v>390.27</v>
+        <v>-63.303636370003</v>
       </c>
       <c r="EW11" t="n">
-        <v>1680.87</v>
+        <v>1214.18073607</v>
       </c>
       <c r="EX11" t="n">
-        <v>-59.9</v>
+        <v>15.3428540900001</v>
       </c>
       <c r="EY11" t="n">
-        <v>4599.73</v>
+        <v>2873.43</v>
       </c>
       <c r="EZ11" t="n">
-        <v>-2129.56</v>
+        <v>7929.4</v>
       </c>
       <c r="FA11" t="n">
-        <v>-1226.1</v>
+        <v>-568.45920134</v>
       </c>
       <c r="FB11" t="n">
-        <v>614.16</v>
+        <v>-125.84</v>
       </c>
       <c r="FC11" t="n">
-        <v>4184.94</v>
+        <v>2550.62924755</v>
       </c>
       <c r="FD11" t="n">
-        <v>2313.61</v>
+        <v>1187.18</v>
       </c>
       <c r="FE11" t="n">
-        <v>10368.02</v>
+        <v>15012.56</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>-63.303636370003</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>1214.18073607</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>15.3428540900001</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>2873.43</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>7929.4</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>-568.45920134</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>-125.84</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>2550.62924755</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>1187.18</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>15012.56</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>32115.1174292645</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>76869.3487259457</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>1964.13896809915</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>142088.53</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>186414.95</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>93525.00986771189</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>25797.01</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>165307.605008979</v>
+      </c>
+      <c r="GH11" t="n">
+        <v>54815.46</v>
+      </c>
+      <c r="GI11" t="n">
+        <v>778897.17</v>
+      </c>
+      <c r="GJ11" t="n">
+        <v>4.12315240909972</v>
+      </c>
+      <c r="GK11" t="n">
+        <v>9.86899833336739</v>
+      </c>
+      <c r="GL11" t="n">
+        <v>0.25216922640753</v>
+      </c>
+      <c r="GM11" t="n">
+        <v>18.2422706709796</v>
+      </c>
+      <c r="GN11" t="n">
+        <v>23.9331913351284</v>
+      </c>
+      <c r="GO11" t="n">
+        <v>12.0073629061602</v>
+      </c>
+      <c r="GP11" t="n">
+        <v>3.31199174853851</v>
+      </c>
+      <c r="GQ11" t="n">
+        <v>21.2232899766446</v>
+      </c>
+      <c r="GR11" t="n">
+        <v>7.03757339367403</v>
+      </c>
+      <c r="GS11" t="n">
+        <v>100</v>
       </c>
       <c r="GT11" t="n">
-        <v>-875.09</v>
+        <v>1451.44374768</v>
       </c>
       <c r="GU11" t="n">
-        <v>-90.78</v>
+        <v>330.528265829998</v>
       </c>
       <c r="GV11" t="n">
-        <v>-61.5</v>
+        <v>108.68111996</v>
       </c>
       <c r="GW11" t="n">
-        <v>-2558.44</v>
+        <v>5019.32</v>
       </c>
       <c r="GX11" t="n">
-        <v>-1391.51</v>
+        <v>734.87</v>
       </c>
       <c r="GY11" t="n">
-        <v>-3375.92</v>
+        <v>660.836704810001</v>
       </c>
       <c r="GZ11" t="n">
-        <v>-306.15</v>
+        <v>1007.18</v>
       </c>
       <c r="HA11" t="n">
-        <v>-657.02</v>
+        <v>-3285.23983828</v>
       </c>
       <c r="HB11" t="n">
-        <v>-623.5599999999999</v>
+        <v>2635.23</v>
       </c>
       <c r="HC11" t="n">
-        <v>-9939.969999999999</v>
+        <v>8662.85</v>
+      </c>
+      <c r="HD11" t="n">
+        <v>1451.44374768</v>
+      </c>
+      <c r="HE11" t="n">
+        <v>330.528265829998</v>
+      </c>
+      <c r="HF11" t="n">
+        <v>108.68111996</v>
+      </c>
+      <c r="HG11" t="n">
+        <v>5019.32</v>
+      </c>
+      <c r="HH11" t="n">
+        <v>734.87</v>
+      </c>
+      <c r="HI11" t="n">
+        <v>660.836704810001</v>
+      </c>
+      <c r="HJ11" t="n">
+        <v>1007.18</v>
+      </c>
+      <c r="HK11" t="n">
+        <v>-3285.23983828</v>
+      </c>
+      <c r="HL11" t="n">
+        <v>2635.23</v>
+      </c>
+      <c r="HM11" t="n">
+        <v>8662.85</v>
+      </c>
+      <c r="HX11" t="n">
+        <v>55390.8213642587</v>
+      </c>
+      <c r="HY11" t="n">
+        <v>8041.85946208327</v>
+      </c>
+      <c r="HZ11" t="n">
+        <v>2012.17302051254</v>
+      </c>
+      <c r="IA11" t="n">
+        <v>72040.11</v>
+      </c>
+      <c r="IB11" t="n">
+        <v>13742.33</v>
+      </c>
+      <c r="IC11" t="n">
+        <v>79784.7480965588</v>
+      </c>
+      <c r="ID11" t="n">
+        <v>8226.9</v>
+      </c>
+      <c r="IE11" t="n">
+        <v>80701.6680565867</v>
+      </c>
+      <c r="IF11" t="n">
+        <v>21652.28</v>
+      </c>
+      <c r="IG11" t="n">
+        <v>341592.89</v>
+      </c>
+      <c r="IH11" t="n">
+        <v>16.2154491459874</v>
+      </c>
+      <c r="II11" t="n">
+        <v>2.3542233159722</v>
+      </c>
+      <c r="IJ11" t="n">
+        <v>0.589055884773404</v>
+      </c>
+      <c r="IK11" t="n">
+        <v>21.089464127898</v>
+      </c>
+      <c r="IL11" t="n">
+        <v>4.02301406214866</v>
+      </c>
+      <c r="IM11" t="n">
+        <v>23.3566770363865</v>
+      </c>
+      <c r="IN11" t="n">
+        <v>2.40839321919142</v>
+      </c>
+      <c r="IO11" t="n">
+        <v>23.6251018153764</v>
+      </c>
+      <c r="IP11" t="n">
+        <v>6.3386213922661</v>
+      </c>
+      <c r="IQ11" t="n">
+        <v>100</v>
       </c>
       <c r="IR11" t="n">
-        <v>-173.68</v>
+        <v>181.86</v>
       </c>
       <c r="IS11" t="n">
-        <v>-1075.71</v>
+        <v>-46.71</v>
       </c>
       <c r="IT11" t="n">
-        <v>-7.36</v>
+        <v>-5.07</v>
       </c>
       <c r="IU11" t="n">
-        <v>-80.04000000000001</v>
+        <v>-73.05</v>
       </c>
       <c r="IV11" t="n">
-        <v>-36.06</v>
+        <v>-14.76</v>
       </c>
       <c r="IW11" t="n">
-        <v>-15.42</v>
+        <v>161.27</v>
       </c>
       <c r="IX11" t="n">
-        <v>-196.03</v>
+        <v>3.61000000000001</v>
       </c>
       <c r="IY11" t="n">
-        <v>-1162.39</v>
+        <v>55.3999999999999</v>
       </c>
       <c r="IZ11" t="n">
-        <v>-117</v>
+        <v>6.04</v>
       </c>
       <c r="JA11" t="n">
-        <v>-2863.69</v>
+        <v>268.59</v>
+      </c>
+      <c r="JB11" t="n">
+        <v>181.86</v>
+      </c>
+      <c r="JC11" t="n">
+        <v>-46.71</v>
+      </c>
+      <c r="JD11" t="n">
+        <v>-5.07</v>
+      </c>
+      <c r="JE11" t="n">
+        <v>-73.05</v>
+      </c>
+      <c r="JF11" t="n">
+        <v>-14.76</v>
+      </c>
+      <c r="JG11" t="n">
+        <v>161.27</v>
+      </c>
+      <c r="JH11" t="n">
+        <v>3.61000000000001</v>
+      </c>
+      <c r="JI11" t="n">
+        <v>55.3999999999999</v>
+      </c>
+      <c r="JJ11" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="JK11" t="n">
+        <v>268.59</v>
+      </c>
+      <c r="JV11" t="n">
+        <v>1738.51</v>
+      </c>
+      <c r="JW11" t="n">
+        <v>3856.71</v>
+      </c>
+      <c r="JX11" t="n">
+        <v>222.93</v>
+      </c>
+      <c r="JY11" t="n">
+        <v>1243.46</v>
+      </c>
+      <c r="JZ11" t="n">
+        <v>155.96</v>
+      </c>
+      <c r="KA11" t="n">
+        <v>2148.79</v>
+      </c>
+      <c r="KB11" t="n">
+        <v>1097.34</v>
+      </c>
+      <c r="KC11" t="n">
+        <v>6744.97</v>
+      </c>
+      <c r="KD11" t="n">
+        <v>942.86</v>
+      </c>
+      <c r="KE11" t="n">
+        <v>18151.53</v>
+      </c>
+      <c r="KF11" t="n">
+        <v>9.577760111682039</v>
+      </c>
+      <c r="KG11" t="n">
+        <v>21.2472998143958</v>
+      </c>
+      <c r="KH11" t="n">
+        <v>1.22816093188839</v>
+      </c>
+      <c r="KI11" t="n">
+        <v>6.85044180848667</v>
+      </c>
+      <c r="KJ11" t="n">
+        <v>0.859211317172712</v>
+      </c>
+      <c r="KK11" t="n">
+        <v>11.8380654413154</v>
+      </c>
+      <c r="KL11" t="n">
+        <v>6.0454407975526</v>
+      </c>
+      <c r="KM11" t="n">
+        <v>37.1592367144808</v>
+      </c>
+      <c r="KN11" t="n">
+        <v>5.19438306302554</v>
+      </c>
+      <c r="KO11" t="n">
+        <v>100</v>
       </c>
       <c r="KP11" t="n">
-        <v>-215.5</v>
+        <v>998.53</v>
       </c>
       <c r="KQ11" t="n">
-        <v>-0.51</v>
+        <v>-8.94</v>
       </c>
       <c r="KR11" t="n">
-        <v>-0.77</v>
+        <v>-2.25</v>
       </c>
       <c r="KS11" t="n">
-        <v>-3.5</v>
+        <v>11.95</v>
       </c>
       <c r="KT11" t="n">
         <v>0</v>
       </c>
       <c r="KU11" t="n">
-        <v>0.31</v>
+        <v>-2.51</v>
       </c>
       <c r="KV11" t="n">
-        <v>3.84</v>
+        <v>5.07</v>
       </c>
       <c r="KW11" t="n">
-        <v>364.86</v>
+        <v>-57.41</v>
       </c>
       <c r="KX11" t="n">
-        <v>-7.95</v>
+        <v>95.33</v>
       </c>
       <c r="KY11" t="n">
-        <v>140.78</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2024-Q2</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>-2604.05</v>
-      </c>
-      <c r="C12" t="n">
-        <v>5805.8</v>
-      </c>
-      <c r="D12" t="n">
-        <v>-1159.05</v>
-      </c>
-      <c r="E12" t="n">
-        <v>10616.64</v>
-      </c>
-      <c r="F12" t="n">
-        <v>3856.92</v>
-      </c>
-      <c r="G12" t="n">
-        <v>22212.95</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1058.41</v>
-      </c>
-      <c r="I12" t="n">
-        <v>9432.75</v>
-      </c>
-      <c r="J12" t="n">
-        <v>5075.74</v>
-      </c>
-      <c r="K12" t="n">
-        <v>54296.11</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>-1794.31</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4982.56</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>-925.76</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>8908.57</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3517.8</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>17350.57</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>-445.64</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>3293.09</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>415.98</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>35302.86</v>
-      </c>
-      <c r="CX12" t="n">
-        <v>-1360.41</v>
-      </c>
-      <c r="CY12" t="n">
-        <v>-267.12</v>
-      </c>
-      <c r="CZ12" t="n">
-        <v>-153.33</v>
-      </c>
-      <c r="DA12" t="n">
-        <v>-1934.01</v>
-      </c>
-      <c r="DB12" t="n">
-        <v>347.53</v>
-      </c>
-      <c r="DC12" t="n">
-        <v>-247.95</v>
-      </c>
-      <c r="DD12" t="n">
-        <v>323.78</v>
-      </c>
-      <c r="DE12" t="n">
-        <v>-411.09</v>
-      </c>
-      <c r="DF12" t="n">
-        <v>-124.7</v>
-      </c>
-      <c r="DG12" t="n">
-        <v>-3827.3</v>
-      </c>
-      <c r="EV12" t="n">
-        <v>549.3099999999999</v>
-      </c>
-      <c r="EW12" t="n">
-        <v>950.63</v>
-      </c>
-      <c r="EX12" t="n">
-        <v>-43.82</v>
-      </c>
-      <c r="EY12" t="n">
-        <v>3875.55</v>
-      </c>
-      <c r="EZ12" t="n">
-        <v>75.48</v>
-      </c>
-      <c r="FA12" t="n">
-        <v>1324.45</v>
-      </c>
-      <c r="FB12" t="n">
-        <v>900.29</v>
-      </c>
-      <c r="FC12" t="n">
-        <v>5331.06</v>
-      </c>
-      <c r="FD12" t="n">
-        <v>4020.53</v>
-      </c>
-      <c r="FE12" t="n">
-        <v>16983.48</v>
-      </c>
-      <c r="GT12" t="n">
-        <v>-27.97</v>
-      </c>
-      <c r="GU12" t="n">
-        <v>385.44</v>
-      </c>
-      <c r="GV12" t="n">
-        <v>-29.82</v>
-      </c>
-      <c r="GW12" t="n">
-        <v>-193.44</v>
-      </c>
-      <c r="GX12" t="n">
-        <v>-78.72</v>
-      </c>
-      <c r="GY12" t="n">
-        <v>3864.63</v>
-      </c>
-      <c r="GZ12" t="n">
-        <v>35.55</v>
-      </c>
-      <c r="HA12" t="n">
-        <v>1458.74</v>
-      </c>
-      <c r="HB12" t="n">
-        <v>793.5700000000001</v>
-      </c>
-      <c r="HC12" t="n">
-        <v>6207.98</v>
-      </c>
-      <c r="IR12" t="n">
-        <v>-30.11</v>
-      </c>
-      <c r="IS12" t="n">
-        <v>-245.54</v>
-      </c>
-      <c r="IT12" t="n">
-        <v>-5.98</v>
-      </c>
-      <c r="IU12" t="n">
-        <v>-56.27</v>
-      </c>
-      <c r="IV12" t="n">
-        <v>-5.17</v>
-      </c>
-      <c r="IW12" t="n">
-        <v>-78</v>
-      </c>
-      <c r="IX12" t="n">
-        <v>-42.74</v>
-      </c>
-      <c r="IY12" t="n">
-        <v>-40.88</v>
-      </c>
-      <c r="IZ12" t="n">
-        <v>5</v>
-      </c>
-      <c r="JA12" t="n">
-        <v>-499.69</v>
-      </c>
-      <c r="KP12" t="n">
-        <v>59.44</v>
-      </c>
-      <c r="KQ12" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="KR12" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="KS12" t="n">
-        <v>16.24</v>
-      </c>
-      <c r="KT12" t="n">
+        <v>1039.77</v>
+      </c>
+      <c r="KZ11" t="n">
+        <v>998.53</v>
+      </c>
+      <c r="LA11" t="n">
+        <v>-8.94</v>
+      </c>
+      <c r="LB11" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="LC11" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="LD11" t="n">
         <v>0</v>
       </c>
-      <c r="KU12" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="KV12" t="n">
-        <v>287.17</v>
-      </c>
-      <c r="KW12" t="n">
-        <v>-198.17</v>
-      </c>
-      <c r="KX12" t="n">
-        <v>-34.64</v>
-      </c>
-      <c r="KY12" t="n">
-        <v>128.78</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2024-Q3</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>-4922.61</v>
-      </c>
-      <c r="C13" t="n">
-        <v>8729.84</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-1240.2</v>
-      </c>
-      <c r="E13" t="n">
-        <v>13416.36</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-10221.19</v>
-      </c>
-      <c r="G13" t="n">
-        <v>12281.74</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-917.96</v>
-      </c>
-      <c r="I13" t="n">
-        <v>10556.36</v>
-      </c>
-      <c r="J13" t="n">
-        <v>7752.66</v>
-      </c>
-      <c r="K13" t="n">
-        <v>35435</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>-4864.27</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>6161.11</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>-936.16</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>8533.73</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>-7266.41</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>8161.25</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>-960.45</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>5021.32</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>2278.27</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>16128.39</v>
-      </c>
-      <c r="CX13" t="n">
-        <v>-784.26</v>
-      </c>
-      <c r="CY13" t="n">
-        <v>798.22</v>
-      </c>
-      <c r="CZ13" t="n">
-        <v>-309.41</v>
-      </c>
-      <c r="DA13" t="n">
-        <v>-619.25</v>
-      </c>
-      <c r="DB13" t="n">
-        <v>-2511.12</v>
-      </c>
-      <c r="DC13" t="n">
-        <v>507.29</v>
-      </c>
-      <c r="DD13" t="n">
-        <v>49.96</v>
-      </c>
-      <c r="DE13" t="n">
-        <v>600.99</v>
-      </c>
-      <c r="DF13" t="n">
-        <v>-209.12</v>
-      </c>
-      <c r="DG13" t="n">
-        <v>-2476.7</v>
-      </c>
-      <c r="EV13" t="n">
-        <v>630.79</v>
-      </c>
-      <c r="EW13" t="n">
-        <v>928.05</v>
-      </c>
-      <c r="EX13" t="n">
-        <v>-4.56</v>
-      </c>
-      <c r="EY13" t="n">
-        <v>3371.11</v>
-      </c>
-      <c r="EZ13" t="n">
-        <v>-648.85</v>
-      </c>
-      <c r="FA13" t="n">
-        <v>2425.04</v>
-      </c>
-      <c r="FB13" t="n">
-        <v>-404.48</v>
-      </c>
-      <c r="FC13" t="n">
-        <v>-1187.02</v>
-      </c>
-      <c r="FD13" t="n">
-        <v>4799.91</v>
-      </c>
-      <c r="FE13" t="n">
-        <v>9909.99</v>
-      </c>
-      <c r="GT13" t="n">
-        <v>25.55</v>
-      </c>
-      <c r="GU13" t="n">
-        <v>430.5</v>
-      </c>
-      <c r="GV13" t="n">
-        <v>16.38</v>
-      </c>
-      <c r="GW13" t="n">
-        <v>2059.91</v>
-      </c>
-      <c r="GX13" t="n">
-        <v>218.94</v>
-      </c>
-      <c r="GY13" t="n">
-        <v>1182.4</v>
-      </c>
-      <c r="GZ13" t="n">
-        <v>294.7</v>
-      </c>
-      <c r="HA13" t="n">
-        <v>5306.95</v>
-      </c>
-      <c r="HB13" t="n">
-        <v>796.34</v>
-      </c>
-      <c r="HC13" t="n">
-        <v>10331.67</v>
-      </c>
-      <c r="IR13" t="n">
-        <v>48.95</v>
-      </c>
-      <c r="IS13" t="n">
-        <v>410.6</v>
-      </c>
-      <c r="IT13" t="n">
-        <v>-5.86</v>
-      </c>
-      <c r="IU13" t="n">
-        <v>32.08</v>
-      </c>
-      <c r="IV13" t="n">
-        <v>-13.75</v>
-      </c>
-      <c r="IW13" t="n">
-        <v>6.61</v>
-      </c>
-      <c r="IX13" t="n">
-        <v>102.49</v>
-      </c>
-      <c r="IY13" t="n">
-        <v>530.8099999999999</v>
-      </c>
-      <c r="IZ13" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="JA13" t="n">
-        <v>1117.68</v>
-      </c>
-      <c r="KP13" t="n">
-        <v>20.63</v>
-      </c>
-      <c r="KQ13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="KR13" t="n">
-        <v>-0.59</v>
-      </c>
-      <c r="KS13" t="n">
-        <v>38.78</v>
-      </c>
-      <c r="KT13" t="n">
+      <c r="LE11" t="n">
+        <v>-2.51</v>
+      </c>
+      <c r="LF11" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="LG11" t="n">
+        <v>-57.41</v>
+      </c>
+      <c r="LH11" t="n">
+        <v>95.33</v>
+      </c>
+      <c r="LI11" t="n">
+        <v>1039.77</v>
+      </c>
+      <c r="LT11" t="n">
+        <v>11558.43</v>
+      </c>
+      <c r="LU11" t="n">
+        <v>101.19</v>
+      </c>
+      <c r="LV11" t="n">
+        <v>43.24</v>
+      </c>
+      <c r="LW11" t="n">
+        <v>5879.44</v>
+      </c>
+      <c r="LX11" t="n">
         <v>0</v>
       </c>
-      <c r="KU13" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="KV13" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="KW13" t="n">
-        <v>283.31</v>
-      </c>
-      <c r="KX13" t="n">
-        <v>81.51000000000001</v>
-      </c>
-      <c r="KY13" t="n">
-        <v>423.97</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2024-Q4</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>-9229.290000000001</v>
-      </c>
-      <c r="C14" t="n">
-        <v>22625.23</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-1909.67</v>
-      </c>
-      <c r="E14" t="n">
-        <v>7143.34</v>
-      </c>
-      <c r="F14" t="n">
-        <v>33560.91</v>
-      </c>
-      <c r="G14" t="n">
-        <v>8727.379999999999</v>
-      </c>
-      <c r="H14" t="n">
-        <v>535.17</v>
-      </c>
-      <c r="I14" t="n">
-        <v>15436.3</v>
-      </c>
-      <c r="J14" t="n">
-        <v>10491.97</v>
-      </c>
-      <c r="K14" t="n">
-        <v>87381.34</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-19602.79</v>
-      </c>
-      <c r="M14" t="n">
-        <v>47597.34</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-5579.34</v>
-      </c>
-      <c r="O14" t="n">
-        <v>35278.2</v>
-      </c>
-      <c r="P14" t="n">
-        <v>17183.5</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>57452.8</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1162.34</v>
-      </c>
-      <c r="S14" t="n">
-        <v>44313.98</v>
-      </c>
-      <c r="T14" t="n">
-        <v>24094.03</v>
-      </c>
-      <c r="U14" t="n">
-        <v>201900.06</v>
-      </c>
-      <c r="V14" t="n">
-        <v>-9.709155109999999</v>
-      </c>
-      <c r="W14" t="n">
-        <v>23.57470325</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-2.76341671</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>17.4731003</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>8.51089395</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>28.4560589</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0.575700671</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>21.94847292</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>11.93364182</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>602904.4399999999</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>772061.328</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>175604.4773</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1883437.34</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>2692680.01</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>878295.2830000001</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>143261.95</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>912634.072</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>170268.19</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>8231147.09</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>7.32467095</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>9.379753750000001</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2.1334144</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>22.8818331</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>32.71330205</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>10.67038741</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>1.740485845</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>11.0875685</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>2.06858398</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>100</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>-11009.67</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>13085.37</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>-1406.2</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>4746.68</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>2278.23</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>9082.07</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1126.98</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>4345.64</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>135.8</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>22384.9</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>-948.49</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>9851.450000000001</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>-938.16</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>4432.07</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>-3407.28</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>19193.36</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>263.81</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>6591.02</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>-155.79</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>34881.99</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>-2.71913959</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>28.2422247</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>-2.689525454</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>12.7058978</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>-9.76802069</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>55.0236956</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>0.75629286</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>18.8951949</v>
-      </c>
-      <c r="CB14" t="n">
-        <v>-0.446620161</v>
-      </c>
-      <c r="CC14" t="n">
-        <v>100</v>
-      </c>
-      <c r="CD14" t="n">
-        <v>419761.994</v>
-      </c>
-      <c r="CE14" t="n">
-        <v>397115.572</v>
-      </c>
-      <c r="CF14" t="n">
-        <v>107806.702</v>
-      </c>
-      <c r="CG14" t="n">
-        <v>1209980.46</v>
-      </c>
-      <c r="CH14" t="n">
-        <v>2098721.81</v>
-      </c>
-      <c r="CI14" t="n">
-        <v>650546.027</v>
-      </c>
-      <c r="CJ14" t="n">
-        <v>71211.91</v>
-      </c>
-      <c r="CK14" t="n">
-        <v>568388.934</v>
-      </c>
-      <c r="CL14" t="n">
-        <v>94062.34</v>
-      </c>
-      <c r="CM14" t="n">
-        <v>5617595.75</v>
-      </c>
-      <c r="CN14" t="n">
-        <v>7.47227129</v>
-      </c>
-      <c r="CO14" t="n">
-        <v>7.06913758</v>
-      </c>
-      <c r="CP14" t="n">
-        <v>1.91908971</v>
-      </c>
-      <c r="CQ14" t="n">
-        <v>21.5391159</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>37.35978706</v>
-      </c>
-      <c r="CS14" t="n">
-        <v>11.58050626</v>
-      </c>
-      <c r="CT14" t="n">
-        <v>1.267658144</v>
-      </c>
-      <c r="CU14" t="n">
-        <v>10.11801061</v>
-      </c>
-      <c r="CV14" t="n">
-        <v>1.67442344</v>
-      </c>
-      <c r="CW14" t="n">
-        <v>100</v>
-      </c>
-      <c r="CX14" t="n">
-        <v>-1125.12</v>
-      </c>
-      <c r="CY14" t="n">
-        <v>2469.94</v>
-      </c>
-      <c r="CZ14" t="n">
-        <v>-464.22</v>
-      </c>
-      <c r="DA14" t="n">
-        <v>-1417.42</v>
-      </c>
-      <c r="DB14" t="n">
-        <v>4540.23</v>
-      </c>
-      <c r="DC14" t="n">
-        <v>248.7</v>
-      </c>
-      <c r="DD14" t="n">
-        <v>-131.76</v>
-      </c>
-      <c r="DE14" t="n">
-        <v>-652.96</v>
-      </c>
-      <c r="DF14" t="n">
-        <v>414.92</v>
-      </c>
-      <c r="DG14" t="n">
-        <v>3882.31</v>
-      </c>
-      <c r="DH14" t="n">
-        <v>-1024.35</v>
-      </c>
-      <c r="DI14" t="n">
-        <v>71.15000000000001</v>
-      </c>
-      <c r="DJ14" t="n">
-        <v>-202.73</v>
-      </c>
-      <c r="DK14" t="n">
-        <v>-2287.96</v>
-      </c>
-      <c r="DL14" t="n">
-        <v>-3048.73</v>
-      </c>
-      <c r="DM14" t="n">
-        <v>-345.5</v>
-      </c>
-      <c r="DN14" t="n">
-        <v>107.09</v>
-      </c>
-      <c r="DO14" t="n">
-        <v>-432.84</v>
-      </c>
-      <c r="DP14" t="n">
-        <v>-635.65</v>
-      </c>
-      <c r="DQ14" t="n">
-        <v>-7799.52</v>
-      </c>
-      <c r="DR14" t="n">
-        <v>13.13350052</v>
-      </c>
-      <c r="DS14" t="n">
-        <v>-0.912235625</v>
-      </c>
-      <c r="DT14" t="n">
-        <v>2.59926252</v>
-      </c>
-      <c r="DU14" t="n">
-        <v>29.3346257</v>
-      </c>
-      <c r="DV14" t="n">
-        <v>39.0886875</v>
-      </c>
-      <c r="DW14" t="n">
-        <v>4.42975978</v>
-      </c>
-      <c r="DX14" t="n">
-        <v>-1.373033212</v>
-      </c>
-      <c r="DY14" t="n">
-        <v>5.54957228</v>
-      </c>
-      <c r="DZ14" t="n">
-        <v>8.149860500000001</v>
-      </c>
-      <c r="EA14" t="n">
-        <v>100</v>
-      </c>
-      <c r="EB14" t="n">
-        <v>105292.5633</v>
-      </c>
-      <c r="EC14" t="n">
-        <v>299348.4076</v>
-      </c>
-      <c r="ED14" t="n">
-        <v>64056.8468</v>
-      </c>
-      <c r="EE14" t="n">
-        <v>504309.07</v>
-      </c>
-      <c r="EF14" t="n">
-        <v>416437.18</v>
-      </c>
-      <c r="EG14" t="n">
-        <v>78271.9596</v>
-      </c>
-      <c r="EH14" t="n">
-        <v>35063.6</v>
-      </c>
-      <c r="EI14" t="n">
-        <v>47093.2026</v>
-      </c>
-      <c r="EJ14" t="n">
-        <v>10883.73</v>
-      </c>
-      <c r="EK14" t="n">
-        <v>1560756.56</v>
-      </c>
-      <c r="EL14" t="n">
-        <v>6.74625153</v>
-      </c>
-      <c r="EM14" t="n">
-        <v>19.17969883</v>
-      </c>
-      <c r="EN14" t="n">
-        <v>4.10421769</v>
-      </c>
-      <c r="EO14" t="n">
-        <v>32.3118341</v>
-      </c>
-      <c r="EP14" t="n">
-        <v>26.68175106</v>
-      </c>
-      <c r="EQ14" t="n">
-        <v>5.01500116</v>
-      </c>
-      <c r="ER14" t="n">
-        <v>2.246577134</v>
-      </c>
-      <c r="ES14" t="n">
-        <v>3.01733171</v>
-      </c>
-      <c r="ET14" t="n">
-        <v>0.69733681</v>
-      </c>
-      <c r="EU14" t="n">
-        <v>100</v>
-      </c>
-      <c r="EV14" t="n">
-        <v>2678.01</v>
-      </c>
-      <c r="EW14" t="n">
-        <v>1511.54</v>
-      </c>
-      <c r="EX14" t="n">
-        <v>-25.71</v>
-      </c>
-      <c r="EY14" t="n">
-        <v>3707.12</v>
-      </c>
-      <c r="EZ14" t="n">
-        <v>26558.65</v>
-      </c>
-      <c r="FA14" t="n">
-        <v>1378.13</v>
-      </c>
-      <c r="FB14" t="n">
-        <v>-1066.83</v>
-      </c>
-      <c r="FC14" t="n">
-        <v>1654.49</v>
-      </c>
-      <c r="FD14" t="n">
-        <v>10103.84</v>
-      </c>
-      <c r="FE14" t="n">
-        <v>46499.24</v>
-      </c>
-      <c r="FF14" t="n">
-        <v>390.27</v>
-      </c>
-      <c r="FG14" t="n">
-        <v>1680.87</v>
-      </c>
-      <c r="FH14" t="n">
-        <v>-59.9</v>
-      </c>
-      <c r="FI14" t="n">
-        <v>4599.73</v>
-      </c>
-      <c r="FJ14" t="n">
-        <v>-2129.56</v>
-      </c>
-      <c r="FK14" t="n">
-        <v>-1226.1</v>
-      </c>
-      <c r="FL14" t="n">
-        <v>614.16</v>
-      </c>
-      <c r="FM14" t="n">
-        <v>4184.94</v>
-      </c>
-      <c r="FN14" t="n">
-        <v>2313.61</v>
-      </c>
-      <c r="FO14" t="n">
-        <v>10368.02</v>
-      </c>
-      <c r="FP14" t="n">
-        <v>3.76417098</v>
-      </c>
-      <c r="FQ14" t="n">
-        <v>16.21206363</v>
-      </c>
-      <c r="FR14" t="n">
-        <v>-0.577738083</v>
-      </c>
-      <c r="FS14" t="n">
-        <v>44.3645942</v>
-      </c>
-      <c r="FT14" t="n">
-        <v>-20.53969803</v>
-      </c>
-      <c r="FU14" t="n">
-        <v>-11.82578737</v>
-      </c>
-      <c r="FV14" t="n">
-        <v>5.92359968</v>
-      </c>
-      <c r="FW14" t="n">
-        <v>40.3639268</v>
-      </c>
-      <c r="FX14" t="n">
-        <v>22.3148682</v>
-      </c>
-      <c r="FY14" t="n">
-        <v>100</v>
-      </c>
-      <c r="FZ14" t="n">
-        <v>27841.9316</v>
-      </c>
-      <c r="GA14" t="n">
-        <v>59302.3723</v>
-      </c>
-      <c r="GB14" t="n">
-        <v>1813.20115</v>
-      </c>
-      <c r="GC14" t="n">
-        <v>102542.81</v>
-      </c>
-      <c r="GD14" t="n">
-        <v>166190.35</v>
-      </c>
-      <c r="GE14" t="n">
-        <v>79250.7991</v>
-      </c>
-      <c r="GF14" t="n">
-        <v>25007.9</v>
-      </c>
-      <c r="GG14" t="n">
-        <v>168685.3058</v>
-      </c>
-      <c r="GH14" t="n">
-        <v>47842.95</v>
-      </c>
-      <c r="GI14" t="n">
-        <v>678477.62</v>
-      </c>
-      <c r="GJ14" t="n">
-        <v>4.1035888</v>
-      </c>
-      <c r="GK14" t="n">
-        <v>8.740505300000001</v>
-      </c>
-      <c r="GL14" t="n">
-        <v>0.2672455357</v>
-      </c>
-      <c r="GM14" t="n">
-        <v>15.11366138</v>
-      </c>
-      <c r="GN14" t="n">
-        <v>24.4945957</v>
-      </c>
-      <c r="GO14" t="n">
-        <v>11.68067992</v>
-      </c>
-      <c r="GP14" t="n">
-        <v>3.68588429</v>
-      </c>
-      <c r="GQ14" t="n">
-        <v>24.86232424</v>
-      </c>
-      <c r="GR14" t="n">
-        <v>7.05151483</v>
-      </c>
-      <c r="GS14" t="n">
-        <v>100</v>
-      </c>
-      <c r="GT14" t="n">
-        <v>11.43</v>
-      </c>
-      <c r="GU14" t="n">
-        <v>5856.58</v>
-      </c>
-      <c r="GV14" t="n">
-        <v>-6.15</v>
-      </c>
-      <c r="GW14" t="n">
-        <v>139.76</v>
-      </c>
-      <c r="GX14" t="n">
-        <v>193.27</v>
-      </c>
-      <c r="GY14" t="n">
-        <v>-1941.4</v>
-      </c>
-      <c r="GZ14" t="n">
-        <v>517.03</v>
-      </c>
-      <c r="HA14" t="n">
-        <v>7571.79</v>
-      </c>
-      <c r="HB14" t="n">
-        <v>-275.71</v>
-      </c>
-      <c r="HC14" t="n">
-        <v>12066.6</v>
-      </c>
-      <c r="HD14" t="n">
-        <v>-875.87</v>
-      </c>
-      <c r="HE14" t="n">
-        <v>-90.78</v>
-      </c>
-      <c r="HF14" t="n">
-        <v>-61.5</v>
-      </c>
-      <c r="HG14" t="n">
-        <v>-2558.44</v>
-      </c>
-      <c r="HH14" t="n">
-        <v>-1391.51</v>
-      </c>
-      <c r="HI14" t="n">
-        <v>-3375.92</v>
-      </c>
-      <c r="HJ14" t="n">
-        <v>-306.15</v>
-      </c>
-      <c r="HK14" t="n">
-        <v>-674.7</v>
-      </c>
-      <c r="HL14" t="n">
-        <v>-623.5599999999999</v>
-      </c>
-      <c r="HM14" t="n">
-        <v>-9958.43</v>
-      </c>
-      <c r="HN14" t="n">
-        <v>8.7952619</v>
-      </c>
-      <c r="HO14" t="n">
-        <v>0.911589477</v>
-      </c>
-      <c r="HP14" t="n">
-        <v>0.617567227</v>
-      </c>
-      <c r="HQ14" t="n">
-        <v>25.6911983</v>
-      </c>
-      <c r="HR14" t="n">
-        <v>13.97318654</v>
-      </c>
-      <c r="HS14" t="n">
-        <v>33.9001228</v>
-      </c>
-      <c r="HT14" t="n">
-        <v>3.07427978</v>
-      </c>
-      <c r="HU14" t="n">
-        <v>6.77516436</v>
-      </c>
-      <c r="HV14" t="n">
-        <v>6.2616296</v>
-      </c>
-      <c r="HW14" t="n">
-        <v>100</v>
-      </c>
-      <c r="HX14" t="n">
-        <v>42485.79095</v>
-      </c>
-      <c r="HY14" t="n">
-        <v>11521.70548</v>
-      </c>
-      <c r="HZ14" t="n">
-        <v>1577.687518</v>
-      </c>
-      <c r="IA14" t="n">
-        <v>59092.6</v>
-      </c>
-      <c r="IB14" t="n">
-        <v>11097.25</v>
-      </c>
-      <c r="IC14" t="n">
-        <v>68357.33689999999</v>
-      </c>
-      <c r="ID14" t="n">
-        <v>8538.07</v>
-      </c>
-      <c r="IE14" t="n">
-        <v>96695.96920000001</v>
-      </c>
-      <c r="IF14" t="n">
-        <v>13232.06</v>
-      </c>
-      <c r="IG14" t="n">
-        <v>312598.47</v>
-      </c>
-      <c r="IH14" t="n">
-        <v>13.59117047</v>
-      </c>
-      <c r="II14" t="n">
-        <v>3.68578435</v>
-      </c>
-      <c r="IJ14" t="n">
-        <v>0.5047009730000001</v>
-      </c>
-      <c r="IK14" t="n">
-        <v>18.90367538</v>
-      </c>
-      <c r="IL14" t="n">
-        <v>3.55000138</v>
-      </c>
-      <c r="IM14" t="n">
-        <v>21.8674573</v>
-      </c>
-      <c r="IN14" t="n">
-        <v>2.73132175</v>
-      </c>
-      <c r="IO14" t="n">
-        <v>30.93296303</v>
-      </c>
-      <c r="IP14" t="n">
-        <v>4.23292539</v>
-      </c>
-      <c r="IQ14" t="n">
-        <v>100</v>
-      </c>
-      <c r="IR14" t="n">
-        <v>-48.5</v>
-      </c>
-      <c r="IS14" t="n">
-        <v>-307.96</v>
-      </c>
-      <c r="IT14" t="n">
-        <v>-6.75</v>
-      </c>
-      <c r="IU14" t="n">
-        <v>-52.43</v>
-      </c>
-      <c r="IV14" t="n">
-        <v>-9.470000000000001</v>
-      </c>
-      <c r="IW14" t="n">
-        <v>-42.39</v>
-      </c>
-      <c r="IX14" t="n">
-        <v>-46.26</v>
-      </c>
-      <c r="IY14" t="n">
-        <v>-447.75</v>
-      </c>
-      <c r="IZ14" t="n">
-        <v>-41.16</v>
-      </c>
-      <c r="JA14" t="n">
-        <v>-1002.67</v>
-      </c>
-      <c r="JB14" t="n">
-        <v>-172.89</v>
-      </c>
-      <c r="JC14" t="n">
-        <v>-1075.71</v>
-      </c>
-      <c r="JD14" t="n">
-        <v>-7.36</v>
-      </c>
-      <c r="JE14" t="n">
-        <v>-80.04000000000001</v>
-      </c>
-      <c r="JF14" t="n">
-        <v>-36.06</v>
-      </c>
-      <c r="JG14" t="n">
-        <v>-15.42</v>
-      </c>
-      <c r="JH14" t="n">
-        <v>-196.03</v>
-      </c>
-      <c r="JI14" t="n">
-        <v>-1144.72</v>
-      </c>
-      <c r="JJ14" t="n">
-        <v>-117</v>
-      </c>
-      <c r="JK14" t="n">
-        <v>-2845.23</v>
-      </c>
-      <c r="JL14" t="n">
-        <v>6.07648591</v>
-      </c>
-      <c r="JM14" t="n">
-        <v>37.8074883</v>
-      </c>
-      <c r="JN14" t="n">
-        <v>0.25867856</v>
-      </c>
-      <c r="JO14" t="n">
-        <v>2.81312934</v>
-      </c>
-      <c r="JP14" t="n">
-        <v>1.26738436</v>
-      </c>
-      <c r="JQ14" t="n">
-        <v>0.541959701</v>
-      </c>
-      <c r="JR14" t="n">
-        <v>6.88977692</v>
-      </c>
-      <c r="JS14" t="n">
-        <v>40.2329513</v>
-      </c>
-      <c r="JT14" t="n">
-        <v>4.11214559</v>
-      </c>
-      <c r="JU14" t="n">
-        <v>100</v>
-      </c>
-      <c r="JV14" t="n">
-        <v>1443.13</v>
-      </c>
-      <c r="JW14" t="n">
-        <v>4606.12</v>
-      </c>
-      <c r="JX14" t="n">
-        <v>284.77</v>
-      </c>
-      <c r="JY14" t="n">
-        <v>1708.31</v>
-      </c>
-      <c r="JZ14" t="n">
-        <v>233.42</v>
-      </c>
-      <c r="KA14" t="n">
-        <v>1822.26</v>
-      </c>
-      <c r="KB14" t="n">
-        <v>1092.12</v>
-      </c>
-      <c r="KC14" t="n">
-        <v>7133.39</v>
-      </c>
-      <c r="KD14" t="n">
-        <v>1035.18</v>
-      </c>
-      <c r="KE14" t="n">
-        <v>19358.7</v>
-      </c>
-      <c r="KF14" t="n">
-        <v>7.45468446</v>
-      </c>
-      <c r="KG14" t="n">
-        <v>23.79353986</v>
-      </c>
-      <c r="KH14" t="n">
-        <v>1.4710182</v>
-      </c>
-      <c r="KI14" t="n">
-        <v>8.824507840000001</v>
-      </c>
-      <c r="KJ14" t="n">
-        <v>1.205762784</v>
-      </c>
-      <c r="KK14" t="n">
-        <v>9.41313208</v>
-      </c>
-      <c r="KL14" t="n">
-        <v>5.64149452</v>
-      </c>
-      <c r="KM14" t="n">
-        <v>36.84849706</v>
-      </c>
-      <c r="KN14" t="n">
-        <v>5.3473632</v>
-      </c>
-      <c r="KO14" t="n">
-        <v>100</v>
-      </c>
-      <c r="KP14" t="n">
-        <v>264.56</v>
-      </c>
-      <c r="KQ14" t="n">
-        <v>9.76</v>
-      </c>
-      <c r="KR14" t="n">
-        <v>-0.64</v>
-      </c>
-      <c r="KS14" t="n">
-        <v>19.63</v>
-      </c>
-      <c r="KT14" t="n">
+      <c r="LY11" t="n">
+        <v>31.12</v>
+      </c>
+      <c r="LZ11" t="n">
+        <v>2251.03</v>
+      </c>
+      <c r="MA11" t="n">
+        <v>24795.83</v>
+      </c>
+      <c r="MB11" t="n">
+        <v>3813.47</v>
+      </c>
+      <c r="MC11" t="n">
+        <v>48473.75</v>
+      </c>
+      <c r="MD11" t="n">
+        <v>23.8447200804559</v>
+      </c>
+      <c r="ME11" t="n">
+        <v>0.20875215967405</v>
+      </c>
+      <c r="MF11" t="n">
+        <v>0.08920291910570149</v>
+      </c>
+      <c r="MG11" t="n">
+        <v>12.1291214317027</v>
+      </c>
+      <c r="MH11" t="n">
         <v>0</v>
       </c>
-      <c r="KU14" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="KV14" t="n">
-        <v>136.01</v>
-      </c>
-      <c r="KW14" t="n">
-        <v>2965.09</v>
-      </c>
-      <c r="KX14" t="n">
-        <v>154.28</v>
-      </c>
-      <c r="KY14" t="n">
-        <v>3550.96</v>
-      </c>
-      <c r="KZ14" t="n">
-        <v>-215.5</v>
-      </c>
-      <c r="LA14" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="LB14" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="LC14" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="LD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="LE14" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="LF14" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="LG14" t="n">
-        <v>364.86</v>
-      </c>
-      <c r="LH14" t="n">
-        <v>-7.95</v>
-      </c>
-      <c r="LI14" t="n">
-        <v>140.78</v>
-      </c>
-      <c r="LJ14" t="n">
-        <v>-153.075721</v>
-      </c>
-      <c r="LK14" t="n">
-        <v>-0.3622673675</v>
-      </c>
-      <c r="LL14" t="n">
-        <v>-0.546952692</v>
-      </c>
-      <c r="LM14" t="n">
-        <v>-2.4861486</v>
-      </c>
-      <c r="LN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="LO14" t="n">
-        <v>0.220201733</v>
-      </c>
-      <c r="LP14" t="n">
-        <v>2.72766018</v>
-      </c>
-      <c r="LQ14" t="n">
-        <v>259.1703367</v>
-      </c>
-      <c r="LR14" t="n">
-        <v>-5.64710896</v>
-      </c>
-      <c r="LS14" t="n">
-        <v>100</v>
-      </c>
-      <c r="LT14" t="n">
-        <v>6079.03</v>
-      </c>
-      <c r="LU14" t="n">
-        <v>167.15</v>
-      </c>
-      <c r="LV14" t="n">
-        <v>65.27</v>
-      </c>
-      <c r="LW14" t="n">
-        <v>5804.09</v>
-      </c>
-      <c r="LX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY14" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="LZ14" t="n">
-        <v>2348.35</v>
-      </c>
-      <c r="MA14" t="n">
-        <v>24637.27</v>
-      </c>
-      <c r="MB14" t="n">
-        <v>3211.93</v>
-      </c>
-      <c r="MC14" t="n">
-        <v>42359.99</v>
-      </c>
-      <c r="MD14" t="n">
-        <v>14.35087685</v>
-      </c>
-      <c r="ME14" t="n">
-        <v>0.39459405</v>
-      </c>
-      <c r="MF14" t="n">
-        <v>0.154084078</v>
-      </c>
-      <c r="MG14" t="n">
-        <v>13.701821</v>
-      </c>
-      <c r="MH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="MI14" t="n">
-        <v>0.1107176843</v>
-      </c>
-      <c r="MJ14" t="n">
-        <v>5.54379262</v>
-      </c>
-      <c r="MK14" t="n">
-        <v>58.1616521</v>
-      </c>
-      <c r="ML14" t="n">
-        <v>7.58246166</v>
-      </c>
-      <c r="MM14" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2025-Q1</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>-4445.28667</v>
-      </c>
-      <c r="C15" t="n">
-        <v>17585.26833</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-1459.825833</v>
-      </c>
-      <c r="E15" t="n">
-        <v>8627.24</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-4406.11</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-3783.07583</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1171.41</v>
-      </c>
-      <c r="I15" t="n">
-        <v>13756.81</v>
-      </c>
-      <c r="J15" t="n">
-        <v>4649.59</v>
-      </c>
-      <c r="K15" t="n">
-        <v>31696.02</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>-3140.8925</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>11190.52667</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>-1228.155833</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>4639.73</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>-5457.56</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>-9418.83833</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>-320.99</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>5290.3</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>4191.08</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>5745.2</v>
-      </c>
-      <c r="CX15" t="n">
-        <v>-1550.116667</v>
-      </c>
-      <c r="CY15" t="n">
-        <v>2578.0425</v>
-      </c>
-      <c r="CZ15" t="n">
-        <v>-256.115</v>
-      </c>
-      <c r="DA15" t="n">
-        <v>-2033.82</v>
-      </c>
-      <c r="DB15" t="n">
-        <v>-1629.21</v>
-      </c>
-      <c r="DC15" t="n">
-        <v>-938.990833</v>
-      </c>
-      <c r="DD15" t="n">
-        <v>452.65</v>
-      </c>
-      <c r="DE15" t="n">
-        <v>288.05</v>
-      </c>
-      <c r="DF15" t="n">
-        <v>-82.05</v>
-      </c>
-      <c r="DG15" t="n">
-        <v>-3171.56</v>
-      </c>
-      <c r="EV15" t="n">
-        <v>-240.4175</v>
-      </c>
-      <c r="EW15" t="n">
-        <v>6049.70167</v>
-      </c>
-      <c r="EX15" t="n">
-        <v>-8.733333330000001</v>
-      </c>
-      <c r="EY15" t="n">
-        <v>2680.92</v>
-      </c>
-      <c r="EZ15" t="n">
-        <v>823.9400000000001</v>
-      </c>
-      <c r="FA15" t="n">
-        <v>4238.47917</v>
-      </c>
-      <c r="FB15" t="n">
-        <v>1051.99</v>
-      </c>
-      <c r="FC15" t="n">
-        <v>7583.34</v>
-      </c>
-      <c r="FD15" t="n">
-        <v>-174.32</v>
-      </c>
-      <c r="FE15" t="n">
-        <v>22004.9</v>
-      </c>
-      <c r="GT15" t="n">
-        <v>278.66</v>
-      </c>
-      <c r="GU15" t="n">
-        <v>-1959.7425</v>
-      </c>
-      <c r="GV15" t="n">
-        <v>37.6683333</v>
-      </c>
-      <c r="GW15" t="n">
-        <v>3431.57</v>
-      </c>
-      <c r="GX15" t="n">
-        <v>1880.6</v>
-      </c>
-      <c r="GY15" t="n">
-        <v>2336.084167</v>
-      </c>
-      <c r="GZ15" t="n">
-        <v>-51.33</v>
-      </c>
-      <c r="HA15" t="n">
-        <v>921.0599999999999</v>
-      </c>
-      <c r="HB15" t="n">
-        <v>579.11</v>
-      </c>
-      <c r="HC15" t="n">
-        <v>7453.68</v>
-      </c>
-      <c r="IR15" t="n">
-        <v>-32.75</v>
-      </c>
-      <c r="IS15" t="n">
-        <v>-265.08</v>
-      </c>
-      <c r="IT15" t="n">
-        <v>-2.89</v>
-      </c>
-      <c r="IU15" t="n">
-        <v>-59.27</v>
-      </c>
-      <c r="IV15" t="n">
-        <v>-23.88</v>
-      </c>
-      <c r="IW15" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="IX15" t="n">
-        <v>34.06</v>
-      </c>
-      <c r="IY15" t="n">
-        <v>-510.54</v>
-      </c>
-      <c r="IZ15" t="n">
-        <v>38.18</v>
-      </c>
-      <c r="JA15" t="n">
-        <v>-820.1799999999999</v>
-      </c>
-      <c r="KP15" t="n">
-        <v>240.23</v>
-      </c>
-      <c r="KQ15" t="n">
-        <v>-8.18</v>
-      </c>
-      <c r="KR15" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="KS15" t="n">
-        <v>-31.89</v>
-      </c>
-      <c r="KT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="KU15" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="KV15" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="KW15" t="n">
-        <v>184.6</v>
-      </c>
-      <c r="KX15" t="n">
-        <v>97.59</v>
-      </c>
-      <c r="KY15" t="n">
-        <v>483.98</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2025-Q2</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1534.123333</v>
-      </c>
-      <c r="C16" t="n">
-        <v>8558.49833</v>
-      </c>
-      <c r="D16" t="n">
-        <v>-1224.455833</v>
-      </c>
-      <c r="E16" t="n">
-        <v>16238.2</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-449.37</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-1490.095833</v>
-      </c>
-      <c r="H16" t="n">
-        <v>165.9</v>
-      </c>
-      <c r="I16" t="n">
-        <v>29926.96</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1574.45</v>
-      </c>
-      <c r="K16" t="n">
-        <v>54834.21</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>-4675.2825</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>6512.38667</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>-1019.795833</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>22749.82</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>-2093.23</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>-1353.778333</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>-450.96</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>5756.84</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>-15.93</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>25410.07</v>
-      </c>
-      <c r="CX16" t="n">
-        <v>3223.543333</v>
-      </c>
-      <c r="CY16" t="n">
-        <v>314.5425</v>
-      </c>
-      <c r="CZ16" t="n">
-        <v>-224.685</v>
-      </c>
-      <c r="DA16" t="n">
-        <v>2080.08</v>
-      </c>
-      <c r="DB16" t="n">
-        <v>125.83</v>
-      </c>
-      <c r="DC16" t="n">
-        <v>-4935.89083</v>
-      </c>
-      <c r="DD16" t="n">
-        <v>12.84</v>
-      </c>
-      <c r="DE16" t="n">
-        <v>-2.92</v>
-      </c>
-      <c r="DF16" t="n">
-        <v>-133.99</v>
-      </c>
-      <c r="DG16" t="n">
-        <v>459.35</v>
-      </c>
-      <c r="EV16" t="n">
-        <v>1287.6525</v>
-      </c>
-      <c r="EW16" t="n">
-        <v>2510.561667</v>
-      </c>
-      <c r="EX16" t="n">
-        <v>2.726666667</v>
-      </c>
-      <c r="EY16" t="n">
-        <v>-4712.74</v>
-      </c>
-      <c r="EZ16" t="n">
-        <v>1347.61</v>
-      </c>
-      <c r="FA16" t="n">
-        <v>-712.160833</v>
-      </c>
-      <c r="FB16" t="n">
-        <v>422.01</v>
-      </c>
-      <c r="FC16" t="n">
-        <v>21855.49</v>
-      </c>
-      <c r="FD16" t="n">
-        <v>1004.52</v>
-      </c>
-      <c r="FE16" t="n">
-        <v>23005.67</v>
-      </c>
-      <c r="GT16" t="n">
-        <v>1468.53</v>
-      </c>
-      <c r="GU16" t="n">
-        <v>-587.1725</v>
-      </c>
-      <c r="GV16" t="n">
-        <v>20.02833333</v>
-      </c>
-      <c r="GW16" t="n">
-        <v>-3837.39</v>
-      </c>
-      <c r="GX16" t="n">
-        <v>172.83</v>
-      </c>
-      <c r="GY16" t="n">
-        <v>5474.87417</v>
-      </c>
-      <c r="GZ16" t="n">
-        <v>87.06999999999999</v>
-      </c>
-      <c r="HA16" t="n">
-        <v>1855.26</v>
-      </c>
-      <c r="HB16" t="n">
-        <v>614.8099999999999</v>
-      </c>
-      <c r="HC16" t="n">
-        <v>5268.84</v>
-      </c>
-      <c r="IR16" t="n">
-        <v>-61.92</v>
-      </c>
-      <c r="IS16" t="n">
-        <v>-188.78</v>
-      </c>
-      <c r="IT16" t="n">
-        <v>-1.64</v>
-      </c>
-      <c r="IU16" t="n">
-        <v>-46.68</v>
-      </c>
-      <c r="IV16" t="n">
-        <v>-2.41</v>
-      </c>
-      <c r="IW16" t="n">
-        <v>38.73</v>
-      </c>
-      <c r="IX16" t="n">
-        <v>90.81</v>
-      </c>
-      <c r="IY16" t="n">
-        <v>-210.85</v>
-      </c>
-      <c r="IZ16" t="n">
-        <v>22.55</v>
-      </c>
-      <c r="JA16" t="n">
-        <v>-360.19</v>
-      </c>
-      <c r="KP16" t="n">
-        <v>291.6</v>
-      </c>
-      <c r="KQ16" t="n">
-        <v>-3.04</v>
-      </c>
-      <c r="KR16" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="KS16" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="KT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="KU16" t="n">
-        <v>-1.87</v>
-      </c>
-      <c r="KV16" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="KW16" t="n">
-        <v>673.14</v>
-      </c>
-      <c r="KX16" t="n">
-        <v>82.48999999999999</v>
-      </c>
-      <c r="KY16" t="n">
-        <v>1050.47</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2025-Q3</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>-732.225322</v>
-      </c>
-      <c r="C17" t="n">
-        <v>12888.30844</v>
-      </c>
-      <c r="D17" t="n">
-        <v>-960.702042</v>
-      </c>
-      <c r="E17" t="n">
-        <v>16686.64</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-10236.24</v>
-      </c>
-      <c r="G17" t="n">
-        <v>9765.483840000001</v>
-      </c>
-      <c r="H17" t="n">
-        <v>763.54</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1352.365082</v>
-      </c>
-      <c r="J17" t="n">
-        <v>804.1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>30331.27</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>-2926.749857</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>7980.02418</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>-794.050235</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>21011.21</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>-6748.36</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>6949.11814</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>18.92</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>-353.442234</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>-326.51</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>24810.16</v>
-      </c>
-      <c r="CX17" t="n">
-        <v>-503.449644</v>
-      </c>
-      <c r="CY17" t="n">
-        <v>2461.91358</v>
-      </c>
-      <c r="CZ17" t="n">
-        <v>-185.2937687</v>
-      </c>
-      <c r="DA17" t="n">
-        <v>298.45</v>
-      </c>
-      <c r="DB17" t="n">
-        <v>-1892.47</v>
-      </c>
-      <c r="DC17" t="n">
-        <v>164.461575</v>
-      </c>
-      <c r="DD17" t="n">
-        <v>110.77</v>
-      </c>
-      <c r="DE17" t="n">
-        <v>-132.5517436</v>
-      </c>
-      <c r="DF17" t="n">
-        <v>-16.33</v>
-      </c>
-      <c r="DG17" t="n">
-        <v>305.5</v>
-      </c>
-      <c r="EV17" t="n">
-        <v>1061.150512</v>
-      </c>
-      <c r="EW17" t="n">
-        <v>2088.93326</v>
-      </c>
-      <c r="EX17" t="n">
-        <v>-4.39870979</v>
-      </c>
-      <c r="EY17" t="n">
-        <v>-133.18</v>
-      </c>
-      <c r="EZ17" t="n">
-        <v>-1104.64</v>
-      </c>
-      <c r="FA17" t="n">
-        <v>2595.943194</v>
-      </c>
-      <c r="FB17" t="n">
-        <v>425.91</v>
-      </c>
-      <c r="FC17" t="n">
-        <v>3374.73174</v>
-      </c>
-      <c r="FD17" t="n">
-        <v>1101.61</v>
-      </c>
-      <c r="FE17" t="n">
-        <v>9406.059999999999</v>
-      </c>
-      <c r="GT17" t="n">
-        <v>577.8836669999999</v>
-      </c>
-      <c r="GU17" t="n">
-        <v>383.777415</v>
-      </c>
-      <c r="GV17" t="n">
-        <v>27.340671</v>
-      </c>
-      <c r="GW17" t="n">
-        <v>-4419.42</v>
-      </c>
-      <c r="GX17" t="n">
-        <v>-488.59</v>
-      </c>
-      <c r="GY17" t="n">
-        <v>-245.3190693</v>
-      </c>
-      <c r="GZ17" t="n">
-        <v>174.74</v>
-      </c>
-      <c r="HA17" t="n">
-        <v>-2138.012683</v>
-      </c>
-      <c r="HB17" t="n">
-        <v>7.87</v>
-      </c>
-      <c r="HC17" t="n">
-        <v>-6119.73</v>
-      </c>
-      <c r="IR17" t="n">
-        <v>157.89</v>
-      </c>
-      <c r="IS17" t="n">
-        <v>-22.77</v>
-      </c>
-      <c r="IT17" t="n">
-        <v>-3.45</v>
-      </c>
-      <c r="IU17" t="n">
-        <v>-58.02</v>
-      </c>
-      <c r="IV17" t="n">
-        <v>-2.18</v>
-      </c>
-      <c r="IW17" t="n">
-        <v>302.68</v>
-      </c>
-      <c r="IX17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="IY17" t="n">
-        <v>67.68000000000001</v>
-      </c>
-      <c r="IZ17" t="n">
-        <v>-12.3</v>
-      </c>
-      <c r="JA17" t="n">
-        <v>431.73</v>
-      </c>
-      <c r="KP17" t="n">
-        <v>901.05</v>
-      </c>
-      <c r="KQ17" t="n">
-        <v>-3.57</v>
-      </c>
-      <c r="KR17" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="KS17" t="n">
-        <v>-12.4</v>
-      </c>
-      <c r="KT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="KU17" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="KV17" t="n">
-        <v>31</v>
-      </c>
-      <c r="KW17" t="n">
-        <v>533.96</v>
-      </c>
-      <c r="KX17" t="n">
-        <v>49.76</v>
-      </c>
-      <c r="KY17" t="n">
-        <v>1497.55</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2025-Q4</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2800.79429</v>
-      </c>
-      <c r="C18" t="n">
-        <v>14300.39619</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-1864.687988</v>
-      </c>
-      <c r="E18" t="n">
-        <v>13967.5</v>
-      </c>
-      <c r="F18" t="n">
-        <v>44651.99</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3491.41591</v>
-      </c>
-      <c r="H18" t="n">
-        <v>474.92</v>
-      </c>
-      <c r="I18" t="n">
-        <v>8269.8316</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-602.28</v>
-      </c>
-      <c r="K18" t="n">
-        <v>85489.88</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-842.594366</v>
-      </c>
-      <c r="M18" t="n">
-        <v>53332.4713</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-5509.6717</v>
-      </c>
-      <c r="O18" t="n">
-        <v>55519.58</v>
-      </c>
-      <c r="P18" t="n">
-        <v>29560.27</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>7983.72808</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2575.77</v>
-      </c>
-      <c r="S18" t="n">
-        <v>53305.9667</v>
-      </c>
-      <c r="T18" t="n">
-        <v>6425.86</v>
-      </c>
-      <c r="U18" t="n">
-        <v>202351.38</v>
-      </c>
-      <c r="V18" t="n">
-        <v>-0.416401591</v>
-      </c>
-      <c r="W18" t="n">
-        <v>26.3563665</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-2.72282388</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>27.4372134</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>14.60838567</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>3.94547746</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.272919414</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>26.34326817</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>3.17559485</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>628732.566</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>860084.683</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>177034.4934</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>2216419.76</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>2859093.89</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>894816.964</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>139669.23</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>781962.004</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>181114.79</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>8738928.380000001</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>7.19461859</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>9.84199259</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>2.025814673</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>25.36260356</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>32.7167562</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>10.23943583</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>1.598242072</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>8.948030810000001</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>2.072505714</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>100</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>-1765.124588</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>7391.93939</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>-1629.391766</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>7368.11</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>32451.96</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>716.09324</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>687.37</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>1237.84373</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>-188.19</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>46270.61</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>-12508.04944</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>33074.8769</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>-4671.39367</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>55768.87</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>18152.81</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>-3107.405286</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>-65.66</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>11931.5415</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>3660.45</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>102236.04</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>-2.71913959</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>28.2422247</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>-2.689525454</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>12.7058978</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>-9.76802069</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>55.0236956</v>
-      </c>
-      <c r="BZ18" t="n">
-        <v>0.75629286</v>
-      </c>
-      <c r="CA18" t="n">
-        <v>18.8951949</v>
-      </c>
-      <c r="CB18" t="n">
-        <v>-0.446620161</v>
-      </c>
-      <c r="CC18" t="n">
-        <v>100</v>
-      </c>
-      <c r="CD18" t="n">
-        <v>424191.9125</v>
-      </c>
-      <c r="CE18" t="n">
-        <v>443197.1665</v>
-      </c>
-      <c r="CF18" t="n">
-        <v>105252.1988</v>
-      </c>
-      <c r="CG18" t="n">
-        <v>1467277.16</v>
-      </c>
-      <c r="CH18" t="n">
-        <v>2222430.51</v>
-      </c>
-      <c r="CI18" t="n">
-        <v>656430.684</v>
-      </c>
-      <c r="CJ18" t="n">
-        <v>65796.00999999999</v>
-      </c>
-      <c r="CK18" t="n">
-        <v>452093.838</v>
-      </c>
-      <c r="CL18" t="n">
-        <v>93611.33</v>
-      </c>
-      <c r="CM18" t="n">
-        <v>5930280.81</v>
-      </c>
-      <c r="CN18" t="n">
-        <v>7.15298189</v>
-      </c>
-      <c r="CO18" t="n">
-        <v>7.47346004</v>
-      </c>
-      <c r="CP18" t="n">
-        <v>1.77482656</v>
-      </c>
-      <c r="CQ18" t="n">
-        <v>24.7421194</v>
-      </c>
-      <c r="CR18" t="n">
-        <v>37.47597426</v>
-      </c>
-      <c r="CS18" t="n">
-        <v>11.06913323</v>
-      </c>
-      <c r="CT18" t="n">
-        <v>1.109492318</v>
-      </c>
-      <c r="CU18" t="n">
-        <v>7.62348112</v>
-      </c>
-      <c r="CV18" t="n">
-        <v>1.578531152</v>
-      </c>
-      <c r="CW18" t="n">
-        <v>100</v>
-      </c>
-      <c r="CX18" t="n">
-        <v>809.9950669999999</v>
-      </c>
-      <c r="CY18" t="n">
-        <v>3927.37031</v>
-      </c>
-      <c r="CZ18" t="n">
-        <v>-277.7020215</v>
-      </c>
-      <c r="DA18" t="n">
-        <v>-203.75</v>
-      </c>
-      <c r="DB18" t="n">
-        <v>5362.54</v>
-      </c>
-      <c r="DC18" t="n">
-        <v>-343.880324</v>
-      </c>
-      <c r="DD18" t="n">
-        <v>-3.27</v>
-      </c>
-      <c r="DE18" t="n">
-        <v>-678.433032</v>
-      </c>
-      <c r="DF18" t="n">
-        <v>79.42</v>
-      </c>
-      <c r="DG18" t="n">
-        <v>8672.290000000001</v>
-      </c>
-      <c r="DH18" t="n">
-        <v>1979.97209</v>
-      </c>
-      <c r="DI18" t="n">
-        <v>9281.868899999999</v>
-      </c>
-      <c r="DJ18" t="n">
-        <v>-943.79579</v>
-      </c>
-      <c r="DK18" t="n">
-        <v>140.96</v>
-      </c>
-      <c r="DL18" t="n">
-        <v>1966.69</v>
-      </c>
-      <c r="DM18" t="n">
-        <v>-6054.30042</v>
-      </c>
-      <c r="DN18" t="n">
-        <v>572.99</v>
-      </c>
-      <c r="DO18" t="n">
-        <v>-525.854775</v>
-      </c>
-      <c r="DP18" t="n">
-        <v>-152.95</v>
-      </c>
-      <c r="DQ18" t="n">
-        <v>6265.58</v>
-      </c>
-      <c r="DR18" t="n">
-        <v>13.13350052</v>
-      </c>
-      <c r="DS18" t="n">
-        <v>-0.912235625</v>
-      </c>
-      <c r="DT18" t="n">
-        <v>2.59926252</v>
-      </c>
-      <c r="DU18" t="n">
-        <v>29.3346257</v>
-      </c>
-      <c r="DV18" t="n">
-        <v>39.0886875</v>
-      </c>
-      <c r="DW18" t="n">
-        <v>4.42975978</v>
-      </c>
-      <c r="DX18" t="n">
-        <v>-1.373033212</v>
-      </c>
-      <c r="DY18" t="n">
-        <v>5.54957228</v>
-      </c>
-      <c r="DZ18" t="n">
-        <v>8.149860500000001</v>
-      </c>
-      <c r="EA18" t="n">
-        <v>100</v>
-      </c>
-      <c r="EB18" t="n">
-        <v>104791.4997</v>
-      </c>
-      <c r="EC18" t="n">
-        <v>327510.539</v>
-      </c>
-      <c r="ED18" t="n">
-        <v>67595</v>
-      </c>
-      <c r="EE18" t="n">
-        <v>533751.04</v>
-      </c>
-      <c r="EF18" t="n">
-        <v>444163.2</v>
-      </c>
-      <c r="EG18" t="n">
-        <v>81989.84789999999</v>
-      </c>
-      <c r="EH18" t="n">
-        <v>37257.53</v>
-      </c>
-      <c r="EI18" t="n">
-        <v>36472.74355</v>
-      </c>
-      <c r="EJ18" t="n">
-        <v>10422.75</v>
-      </c>
-      <c r="EK18" t="n">
-        <v>1643954.15</v>
-      </c>
-      <c r="EL18" t="n">
-        <v>6.37435659</v>
-      </c>
-      <c r="EM18" t="n">
-        <v>19.92212124</v>
-      </c>
-      <c r="EN18" t="n">
-        <v>4.11173268</v>
-      </c>
-      <c r="EO18" t="n">
-        <v>32.4675138</v>
-      </c>
-      <c r="EP18" t="n">
-        <v>27.0179798</v>
-      </c>
-      <c r="EQ18" t="n">
-        <v>4.98735612</v>
-      </c>
-      <c r="ER18" t="n">
-        <v>2.26633632</v>
-      </c>
-      <c r="ES18" t="n">
-        <v>2.218598588</v>
-      </c>
-      <c r="ET18" t="n">
-        <v>0.634004908</v>
-      </c>
-      <c r="EU18" t="n">
-        <v>100</v>
-      </c>
-      <c r="EV18" t="n">
-        <v>-605.732021</v>
-      </c>
-      <c r="EW18" t="n">
-        <v>2933.36736</v>
-      </c>
-      <c r="EX18" t="n">
-        <v>13.25933785</v>
-      </c>
-      <c r="EY18" t="n">
-        <v>4774.32</v>
-      </c>
-      <c r="EZ18" t="n">
-        <v>6887.15</v>
-      </c>
-      <c r="FA18" t="n">
-        <v>1141.48578</v>
-      </c>
-      <c r="FB18" t="n">
-        <v>-78.01000000000001</v>
-      </c>
-      <c r="FC18" t="n">
-        <v>3335.72954</v>
-      </c>
-      <c r="FD18" t="n">
-        <v>-1031.07</v>
-      </c>
-      <c r="FE18" t="n">
-        <v>17370.5</v>
-      </c>
-      <c r="FF18" t="n">
-        <v>1502.65349</v>
-      </c>
-      <c r="FG18" t="n">
-        <v>13582.56396</v>
-      </c>
-      <c r="FH18" t="n">
-        <v>2.85396139</v>
-      </c>
-      <c r="FI18" t="n">
-        <v>2609.32</v>
-      </c>
-      <c r="FJ18" t="n">
-        <v>7954.06</v>
-      </c>
-      <c r="FK18" t="n">
-        <v>7263.7473</v>
-      </c>
-      <c r="FL18" t="n">
-        <v>1821.9</v>
-      </c>
-      <c r="FM18" t="n">
-        <v>36149.2913</v>
-      </c>
-      <c r="FN18" t="n">
-        <v>900.74</v>
-      </c>
-      <c r="FO18" t="n">
-        <v>71787.13</v>
-      </c>
-      <c r="FP18" t="n">
-        <v>3.76417098</v>
-      </c>
-      <c r="FQ18" t="n">
-        <v>16.21206363</v>
-      </c>
-      <c r="FR18" t="n">
-        <v>-0.577738083</v>
-      </c>
-      <c r="FS18" t="n">
-        <v>44.3645942</v>
-      </c>
-      <c r="FT18" t="n">
-        <v>-20.53969803</v>
-      </c>
-      <c r="FU18" t="n">
-        <v>-11.82578737</v>
-      </c>
-      <c r="FV18" t="n">
-        <v>5.92359968</v>
-      </c>
-      <c r="FW18" t="n">
-        <v>40.3639268</v>
-      </c>
-      <c r="FX18" t="n">
-        <v>22.3148682</v>
-      </c>
-      <c r="FY18" t="n">
-        <v>100</v>
-      </c>
-      <c r="FZ18" t="n">
-        <v>32583.3756</v>
-      </c>
-      <c r="GA18" t="n">
-        <v>77253.37669999999</v>
-      </c>
-      <c r="GB18" t="n">
-        <v>1990.550896</v>
-      </c>
-      <c r="GC18" t="n">
-        <v>141116.98</v>
-      </c>
-      <c r="GD18" t="n">
-        <v>179368.32</v>
-      </c>
-      <c r="GE18" t="n">
-        <v>79143.83</v>
-      </c>
-      <c r="GF18" t="n">
-        <v>26059.57</v>
-      </c>
-      <c r="GG18" t="n">
-        <v>174486.357</v>
-      </c>
-      <c r="GH18" t="n">
-        <v>53388.06</v>
-      </c>
-      <c r="GI18" t="n">
-        <v>765390.42</v>
-      </c>
-      <c r="GJ18" t="n">
-        <v>4.25709216</v>
-      </c>
-      <c r="GK18" t="n">
-        <v>10.09332945</v>
-      </c>
-      <c r="GL18" t="n">
-        <v>0.260070004</v>
-      </c>
-      <c r="GM18" t="n">
-        <v>18.43725455</v>
-      </c>
-      <c r="GN18" t="n">
-        <v>23.43487916</v>
-      </c>
-      <c r="GO18" t="n">
-        <v>10.34032147</v>
-      </c>
-      <c r="GP18" t="n">
-        <v>3.40474212</v>
-      </c>
-      <c r="GQ18" t="n">
-        <v>22.79703957</v>
-      </c>
-      <c r="GR18" t="n">
-        <v>6.97527152</v>
-      </c>
-      <c r="GS18" t="n">
-        <v>100</v>
-      </c>
-      <c r="GT18" t="n">
-        <v>2691.04583</v>
-      </c>
-      <c r="GU18" t="n">
-        <v>206.079127</v>
-      </c>
-      <c r="GV18" t="n">
-        <v>34.056462</v>
-      </c>
-      <c r="GW18" t="n">
-        <v>2101.11</v>
-      </c>
-      <c r="GX18" t="n">
-        <v>-50.89</v>
-      </c>
-      <c r="GY18" t="n">
-        <v>1757.217215</v>
-      </c>
-      <c r="GZ18" t="n">
-        <v>-66.17</v>
-      </c>
-      <c r="HA18" t="n">
-        <v>3778.191365</v>
-      </c>
-      <c r="HB18" t="n">
-        <v>447.4</v>
-      </c>
-      <c r="HC18" t="n">
-        <v>10898.04</v>
-      </c>
-      <c r="HD18" t="n">
-        <v>5016.1195</v>
-      </c>
-      <c r="HE18" t="n">
-        <v>-1957.05846</v>
-      </c>
-      <c r="HF18" t="n">
-        <v>119.0937997</v>
-      </c>
-      <c r="HG18" t="n">
-        <v>-2724.13</v>
-      </c>
-      <c r="HH18" t="n">
-        <v>1513.95</v>
-      </c>
-      <c r="HI18" t="n">
-        <v>9322.85648</v>
-      </c>
-      <c r="HJ18" t="n">
-        <v>144.31</v>
-      </c>
-      <c r="HK18" t="n">
-        <v>4416.49868</v>
-      </c>
-      <c r="HL18" t="n">
-        <v>1649.19</v>
-      </c>
-      <c r="HM18" t="n">
-        <v>17500.83</v>
-      </c>
-      <c r="HN18" t="n">
-        <v>8.7952619</v>
-      </c>
-      <c r="HO18" t="n">
-        <v>0.911589477</v>
-      </c>
-      <c r="HP18" t="n">
-        <v>0.617567227</v>
-      </c>
-      <c r="HQ18" t="n">
-        <v>25.6911983</v>
-      </c>
-      <c r="HR18" t="n">
-        <v>13.97318654</v>
-      </c>
-      <c r="HS18" t="n">
-        <v>33.9001228</v>
-      </c>
-      <c r="HT18" t="n">
-        <v>3.07427978</v>
-      </c>
-      <c r="HU18" t="n">
-        <v>6.77516436</v>
-      </c>
-      <c r="HV18" t="n">
-        <v>6.2616296</v>
-      </c>
-      <c r="HW18" t="n">
-        <v>100</v>
-      </c>
-      <c r="HX18" t="n">
-        <v>54103.9379</v>
-      </c>
-      <c r="HY18" t="n">
-        <v>7909.32147</v>
-      </c>
-      <c r="HZ18" t="n">
-        <v>1907.96363</v>
-      </c>
-      <c r="IA18" t="n">
-        <v>67005.52</v>
-      </c>
-      <c r="IB18" t="n">
-        <v>12956.64</v>
-      </c>
-      <c r="IC18" t="n">
-        <v>75182.6217</v>
-      </c>
-      <c r="ID18" t="n">
-        <v>7201.75</v>
-      </c>
-      <c r="IE18" t="n">
-        <v>87598.2153</v>
-      </c>
-      <c r="IF18" t="n">
-        <v>18910.52</v>
-      </c>
-      <c r="IG18" t="n">
-        <v>332776.49</v>
-      </c>
-      <c r="IH18" t="n">
-        <v>16.2583414</v>
-      </c>
-      <c r="II18" t="n">
-        <v>2.3767669</v>
-      </c>
-      <c r="IJ18" t="n">
-        <v>0.573346883</v>
-      </c>
-      <c r="IK18" t="n">
-        <v>20.1352926</v>
-      </c>
-      <c r="IL18" t="n">
-        <v>3.8934962</v>
-      </c>
-      <c r="IM18" t="n">
-        <v>22.592528</v>
-      </c>
-      <c r="IN18" t="n">
-        <v>2.16414026</v>
-      </c>
-      <c r="IO18" t="n">
-        <v>26.3234387</v>
-      </c>
-      <c r="IP18" t="n">
-        <v>5.68264904</v>
-      </c>
-      <c r="IQ18" t="n">
-        <v>100</v>
-      </c>
-      <c r="IR18" t="n">
-        <v>108</v>
-      </c>
-      <c r="IS18" t="n">
-        <v>-154.07</v>
-      </c>
-      <c r="IT18" t="n">
-        <v>-3.98</v>
-      </c>
-      <c r="IU18" t="n">
-        <v>-46.07</v>
-      </c>
-      <c r="IV18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="IW18" t="n">
-        <v>223.4</v>
-      </c>
-      <c r="IX18" t="n">
-        <v>-64.90000000000001</v>
-      </c>
-      <c r="IY18" t="n">
-        <v>-66.29000000000001</v>
-      </c>
-      <c r="IZ18" t="n">
-        <v>7.55</v>
-      </c>
-      <c r="JA18" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="JB18" t="n">
-        <v>171.22</v>
-      </c>
-      <c r="JC18" t="n">
-        <v>-630.7</v>
-      </c>
-      <c r="JD18" t="n">
-        <v>-11.96</v>
-      </c>
-      <c r="JE18" t="n">
-        <v>-210.04</v>
-      </c>
-      <c r="JF18" t="n">
-        <v>-27.24</v>
-      </c>
-      <c r="JG18" t="n">
-        <v>566.8</v>
-      </c>
-      <c r="JH18" t="n">
-        <v>62.17</v>
-      </c>
-      <c r="JI18" t="n">
-        <v>-720</v>
-      </c>
-      <c r="JJ18" t="n">
-        <v>55.98</v>
-      </c>
-      <c r="JK18" t="n">
-        <v>-743.77</v>
-      </c>
-      <c r="JL18" t="n">
-        <v>6.07648591</v>
-      </c>
-      <c r="JM18" t="n">
-        <v>37.8074883</v>
-      </c>
-      <c r="JN18" t="n">
-        <v>0.25867856</v>
-      </c>
-      <c r="JO18" t="n">
-        <v>2.81312934</v>
-      </c>
-      <c r="JP18" t="n">
-        <v>1.26738436</v>
-      </c>
-      <c r="JQ18" t="n">
-        <v>0.541959701</v>
-      </c>
-      <c r="JR18" t="n">
-        <v>6.88977692</v>
-      </c>
-      <c r="JS18" t="n">
-        <v>40.2329513</v>
-      </c>
-      <c r="JT18" t="n">
-        <v>4.11214559</v>
-      </c>
-      <c r="JU18" t="n">
-        <v>100</v>
-      </c>
-      <c r="JV18" t="n">
-        <v>1561.71</v>
-      </c>
-      <c r="JW18" t="n">
-        <v>4084.09</v>
-      </c>
-      <c r="JX18" t="n">
-        <v>234.6</v>
-      </c>
-      <c r="JY18" t="n">
-        <v>1376.45</v>
-      </c>
-      <c r="JZ18" t="n">
-        <v>175.22</v>
-      </c>
-      <c r="KA18" t="n">
-        <v>2034.21</v>
-      </c>
-      <c r="KB18" t="n">
-        <v>1108.67</v>
-      </c>
-      <c r="KC18" t="n">
-        <v>6824.58</v>
-      </c>
-      <c r="KD18" t="n">
-        <v>1104.27</v>
-      </c>
-      <c r="KE18" t="n">
-        <v>18503.8</v>
-      </c>
-      <c r="KF18" t="n">
-        <v>8.439942070000001</v>
-      </c>
-      <c r="KG18" t="n">
-        <v>22.07162853</v>
-      </c>
-      <c r="KH18" t="n">
-        <v>1.267847685</v>
-      </c>
-      <c r="KI18" t="n">
-        <v>7.43874231</v>
-      </c>
-      <c r="KJ18" t="n">
-        <v>0.946940628</v>
-      </c>
-      <c r="KK18" t="n">
-        <v>10.99347161</v>
-      </c>
-      <c r="KL18" t="n">
-        <v>5.99158011</v>
-      </c>
-      <c r="KM18" t="n">
-        <v>36.88204585</v>
-      </c>
-      <c r="KN18" t="n">
-        <v>5.96780121</v>
-      </c>
-      <c r="KO18" t="n">
-        <v>100</v>
-      </c>
-      <c r="KP18" t="n">
-        <v>1562.61</v>
-      </c>
-      <c r="KQ18" t="n">
-        <v>-4.29</v>
-      </c>
-      <c r="KR18" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="KS18" t="n">
-        <v>-26.22</v>
-      </c>
-      <c r="KT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="KU18" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="KV18" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="KW18" t="n">
-        <v>662.79</v>
-      </c>
-      <c r="KX18" t="n">
-        <v>82.61</v>
-      </c>
-      <c r="KY18" t="n">
-        <v>2273.57</v>
-      </c>
-      <c r="KZ18" t="n">
-        <v>2995.49</v>
-      </c>
-      <c r="LA18" t="n">
-        <v>-19.08</v>
-      </c>
-      <c r="LB18" t="n">
-        <v>-4.47</v>
-      </c>
-      <c r="LC18" t="n">
-        <v>-65.40000000000001</v>
-      </c>
-      <c r="LD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="LE18" t="n">
-        <v>-7.97</v>
-      </c>
-      <c r="LF18" t="n">
-        <v>40.06</v>
-      </c>
-      <c r="LG18" t="n">
-        <v>2054.49</v>
-      </c>
-      <c r="LH18" t="n">
-        <v>312.45</v>
-      </c>
-      <c r="LI18" t="n">
-        <v>5305.57</v>
-      </c>
-      <c r="LJ18" t="n">
-        <v>-153.075721</v>
-      </c>
-      <c r="LK18" t="n">
-        <v>-0.3622673675</v>
-      </c>
-      <c r="LL18" t="n">
-        <v>-0.546952692</v>
-      </c>
-      <c r="LM18" t="n">
-        <v>-2.4861486</v>
-      </c>
-      <c r="LN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="LO18" t="n">
-        <v>0.220201733</v>
-      </c>
-      <c r="LP18" t="n">
-        <v>2.72766018</v>
-      </c>
-      <c r="LQ18" t="n">
-        <v>259.1703367</v>
-      </c>
-      <c r="LR18" t="n">
-        <v>-5.64710896</v>
-      </c>
-      <c r="LS18" t="n">
-        <v>100</v>
-      </c>
-      <c r="LT18" t="n">
-        <v>11500.13</v>
-      </c>
-      <c r="LU18" t="n">
-        <v>130.19</v>
-      </c>
-      <c r="LV18" t="n">
-        <v>54.18</v>
-      </c>
-      <c r="LW18" t="n">
-        <v>5892.61</v>
-      </c>
-      <c r="LX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY18" t="n">
-        <v>35.77</v>
-      </c>
-      <c r="LZ18" t="n">
-        <v>2245.7</v>
-      </c>
-      <c r="MA18" t="n">
-        <v>24486.27</v>
-      </c>
-      <c r="MB18" t="n">
-        <v>3677.86</v>
-      </c>
-      <c r="MC18" t="n">
-        <v>48022.71</v>
-      </c>
-      <c r="MD18" t="n">
-        <v>23.9472741</v>
-      </c>
-      <c r="ME18" t="n">
-        <v>0.271100902</v>
-      </c>
-      <c r="MF18" t="n">
-        <v>0.1128216213</v>
-      </c>
-      <c r="MG18" t="n">
-        <v>12.27046537</v>
-      </c>
-      <c r="MH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="MI18" t="n">
-        <v>0.0744855923</v>
-      </c>
-      <c r="MJ18" t="n">
-        <v>4.67632918</v>
-      </c>
-      <c r="MK18" t="n">
-        <v>50.9889384</v>
-      </c>
-      <c r="ML18" t="n">
-        <v>7.65858487</v>
-      </c>
-      <c r="MM18" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-Q1</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>-1144.415502</v>
-      </c>
-      <c r="C19" t="n">
-        <v>8442.240089999999</v>
-      </c>
-      <c r="D19" t="n">
-        <v>-1728.833214</v>
-      </c>
-      <c r="E19" t="n">
-        <v>13281.13</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-11049.65</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-589.719754</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1706.07</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-2241.05162</v>
-      </c>
-      <c r="J19" t="n">
-        <v>4715.12</v>
-      </c>
-      <c r="K19" t="n">
-        <v>11390.89</v>
-      </c>
-      <c r="L19" t="n">
-        <v>-1144.415502</v>
-      </c>
-      <c r="M19" t="n">
-        <v>8442.240089999999</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-1728.833214</v>
-      </c>
-      <c r="O19" t="n">
-        <v>13281.13</v>
-      </c>
-      <c r="P19" t="n">
-        <v>-11049.65</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>-589.719754</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1706.07</v>
-      </c>
-      <c r="S19" t="n">
-        <v>-2241.05162</v>
-      </c>
-      <c r="T19" t="n">
-        <v>4715.12</v>
-      </c>
-      <c r="U19" t="n">
-        <v>11390.89</v>
-      </c>
-      <c r="V19" t="n">
-        <v>-10.04676107</v>
-      </c>
-      <c r="W19" t="n">
-        <v>74.11396379999999</v>
-      </c>
-      <c r="X19" t="n">
-        <v>-15.1773322</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>116.5943135</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>-97.0042727</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>-5.17711745</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>14.97749517</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>-19.67406954</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>41.3937805</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>610731.233</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>841375.132</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>171019.963</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>2148547.6</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>2802884.88</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>955168.077</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>137560.21</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>729896.296</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>172645.48</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>8569828.869999999</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>7.12652776</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>9.81787553</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.995605345</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>25.07106773</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>32.70642766</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>11.1457077</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>1.605168692</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>8.517046329999999</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>2.01457325</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>100</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>-2353.610923</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>4991.22255</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>-1622.53763</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>9217.469999999999</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>-18165.14</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>-784.714074</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>641.79</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>-1142.659927</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>916.1</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>-8302.08</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>-2353.610923</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>4991.22255</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>-1622.53763</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>9217.469999999999</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>-18165.14</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>-784.714074</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>641.79</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>-1142.659927</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>916.1</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>-8302.08</v>
-      </c>
-      <c r="CD19" t="n">
-        <v>409201.339</v>
-      </c>
-      <c r="CE19" t="n">
-        <v>432580.995</v>
-      </c>
-      <c r="CF19" t="n">
-        <v>100483.3671</v>
-      </c>
-      <c r="CG19" t="n">
-        <v>1407479.68</v>
-      </c>
-      <c r="CH19" t="n">
-        <v>2167174.97</v>
-      </c>
-      <c r="CI19" t="n">
-        <v>685767.385</v>
-      </c>
-      <c r="CJ19" t="n">
-        <v>63504.45</v>
-      </c>
-      <c r="CK19" t="n">
-        <v>417531.914</v>
-      </c>
-      <c r="CL19" t="n">
-        <v>85940.53</v>
-      </c>
-      <c r="CM19" t="n">
-        <v>5769664.63</v>
-      </c>
-      <c r="CN19" t="n">
-        <v>7.09228986</v>
-      </c>
-      <c r="CO19" t="n">
-        <v>7.49750675</v>
-      </c>
-      <c r="CP19" t="n">
-        <v>1.741580725</v>
-      </c>
-      <c r="CQ19" t="n">
-        <v>24.39447993</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>37.5615414</v>
-      </c>
-      <c r="CS19" t="n">
-        <v>11.88574083</v>
-      </c>
-      <c r="CT19" t="n">
-        <v>1.100661028</v>
-      </c>
-      <c r="CU19" t="n">
-        <v>7.23667562</v>
-      </c>
-      <c r="CV19" t="n">
-        <v>1.489523837</v>
-      </c>
-      <c r="CW19" t="n">
-        <v>100</v>
-      </c>
-      <c r="CX19" t="n">
-        <v>-1359.33469</v>
-      </c>
-      <c r="CY19" t="n">
-        <v>1961.958536</v>
-      </c>
-      <c r="CZ19" t="n">
-        <v>-222.9995594</v>
-      </c>
-      <c r="DA19" t="n">
-        <v>-3767.99</v>
-      </c>
-      <c r="DB19" t="n">
-        <v>-1534.02</v>
-      </c>
-      <c r="DC19" t="n">
-        <v>-56.1431836</v>
-      </c>
-      <c r="DD19" t="n">
-        <v>174.26</v>
-      </c>
-      <c r="DE19" t="n">
-        <v>-361.771102</v>
-      </c>
-      <c r="DF19" t="n">
-        <v>-124.76</v>
-      </c>
-      <c r="DG19" t="n">
-        <v>-5290.8</v>
-      </c>
-      <c r="DH19" t="n">
-        <v>-1359.33469</v>
-      </c>
-      <c r="DI19" t="n">
-        <v>1961.958536</v>
-      </c>
-      <c r="DJ19" t="n">
-        <v>-222.9995594</v>
-      </c>
-      <c r="DK19" t="n">
-        <v>-3767.99</v>
-      </c>
-      <c r="DL19" t="n">
-        <v>-1534.02</v>
-      </c>
-      <c r="DM19" t="n">
-        <v>-56.1431836</v>
-      </c>
-      <c r="DN19" t="n">
-        <v>174.26</v>
-      </c>
-      <c r="DO19" t="n">
-        <v>-361.771102</v>
-      </c>
-      <c r="DP19" t="n">
-        <v>-124.76</v>
-      </c>
-      <c r="DQ19" t="n">
-        <v>-5290.8</v>
-      </c>
-      <c r="EB19" t="n">
-        <v>100727.015</v>
-      </c>
-      <c r="EC19" t="n">
-        <v>319925.0284</v>
-      </c>
-      <c r="ED19" t="n">
-        <v>66294.1139</v>
-      </c>
-      <c r="EE19" t="n">
-        <v>519816.38</v>
-      </c>
-      <c r="EF19" t="n">
-        <v>435396.67</v>
-      </c>
-      <c r="EG19" t="n">
-        <v>93911.0239</v>
-      </c>
-      <c r="EH19" t="n">
-        <v>36683.48</v>
-      </c>
-      <c r="EI19" t="n">
-        <v>34814.3089</v>
-      </c>
-      <c r="EJ19" t="n">
-        <v>5480.88</v>
-      </c>
-      <c r="EK19" t="n">
-        <v>1613048.9</v>
-      </c>
-      <c r="EL19" t="n">
-        <v>6.24451094</v>
-      </c>
-      <c r="EM19" t="n">
-        <v>19.83356043</v>
-      </c>
-      <c r="EN19" t="n">
-        <v>4.10986387</v>
-      </c>
-      <c r="EO19" t="n">
-        <v>32.225705</v>
-      </c>
-      <c r="EP19" t="n">
-        <v>26.99215566</v>
-      </c>
-      <c r="EQ19" t="n">
-        <v>5.82195765</v>
-      </c>
-      <c r="ER19" t="n">
-        <v>2.27417036</v>
-      </c>
-      <c r="ES19" t="n">
-        <v>2.15829222</v>
-      </c>
-      <c r="ET19" t="n">
-        <v>0.3397838714</v>
-      </c>
-      <c r="EU19" t="n">
-        <v>100</v>
-      </c>
-      <c r="EV19" t="n">
-        <v>-63.3036364</v>
-      </c>
-      <c r="EW19" t="n">
-        <v>1214.180736</v>
-      </c>
-      <c r="EX19" t="n">
-        <v>15.3428541</v>
-      </c>
-      <c r="EY19" t="n">
-        <v>2873.43</v>
-      </c>
-      <c r="EZ19" t="n">
-        <v>7929.4</v>
-      </c>
-      <c r="FA19" t="n">
-        <v>-568.459201</v>
-      </c>
-      <c r="FB19" t="n">
-        <v>-125.84</v>
-      </c>
-      <c r="FC19" t="n">
-        <v>2550.62925</v>
-      </c>
-      <c r="FD19" t="n">
-        <v>1187.18</v>
-      </c>
-      <c r="FE19" t="n">
-        <v>15012.56</v>
-      </c>
-      <c r="FF19" t="n">
-        <v>-63.3036364</v>
-      </c>
-      <c r="FG19" t="n">
-        <v>1214.180736</v>
-      </c>
-      <c r="FH19" t="n">
-        <v>15.3428541</v>
-      </c>
-      <c r="FI19" t="n">
-        <v>2873.43</v>
-      </c>
-      <c r="FJ19" t="n">
-        <v>7929.4</v>
-      </c>
-      <c r="FK19" t="n">
-        <v>-568.459201</v>
-      </c>
-      <c r="FL19" t="n">
-        <v>-125.84</v>
-      </c>
-      <c r="FM19" t="n">
-        <v>2550.62925</v>
-      </c>
-      <c r="FN19" t="n">
-        <v>1187.18</v>
-      </c>
-      <c r="FO19" t="n">
-        <v>15012.56</v>
-      </c>
-      <c r="FZ19" t="n">
-        <v>32115.1174</v>
-      </c>
-      <c r="GA19" t="n">
-        <v>76869.3487</v>
-      </c>
-      <c r="GB19" t="n">
-        <v>1964.13897</v>
-      </c>
-      <c r="GC19" t="n">
-        <v>142088.53</v>
-      </c>
-      <c r="GD19" t="n">
-        <v>186414.95</v>
-      </c>
-      <c r="GE19" t="n">
-        <v>93525.0099</v>
-      </c>
-      <c r="GF19" t="n">
-        <v>25797.01</v>
-      </c>
-      <c r="GG19" t="n">
-        <v>165307.605</v>
-      </c>
-      <c r="GH19" t="n">
-        <v>54815.46</v>
-      </c>
-      <c r="GI19" t="n">
-        <v>778897.17</v>
-      </c>
-      <c r="GJ19" t="n">
-        <v>4.12315241</v>
-      </c>
-      <c r="GK19" t="n">
-        <v>9.86899833</v>
-      </c>
-      <c r="GL19" t="n">
-        <v>0.2521692264</v>
-      </c>
-      <c r="GM19" t="n">
-        <v>18.24227067</v>
-      </c>
-      <c r="GN19" t="n">
-        <v>23.93319134</v>
-      </c>
-      <c r="GO19" t="n">
-        <v>12.0073629</v>
-      </c>
-      <c r="GP19" t="n">
-        <v>3.31199175</v>
-      </c>
-      <c r="GQ19" t="n">
-        <v>21.22328998</v>
-      </c>
-      <c r="GR19" t="n">
-        <v>7.0375734</v>
-      </c>
-      <c r="GS19" t="n">
-        <v>100</v>
-      </c>
-      <c r="GT19" t="n">
-        <v>1451.443748</v>
-      </c>
-      <c r="GU19" t="n">
-        <v>330.528266</v>
-      </c>
-      <c r="GV19" t="n">
-        <v>108.68112</v>
-      </c>
-      <c r="GW19" t="n">
-        <v>5019.32</v>
-      </c>
-      <c r="GX19" t="n">
-        <v>734.87</v>
-      </c>
-      <c r="GY19" t="n">
-        <v>660.8367050000001</v>
-      </c>
-      <c r="GZ19" t="n">
-        <v>1007.18</v>
-      </c>
-      <c r="HA19" t="n">
-        <v>-3285.23984</v>
-      </c>
-      <c r="HB19" t="n">
-        <v>2635.23</v>
-      </c>
-      <c r="HC19" t="n">
-        <v>8662.85</v>
-      </c>
-      <c r="HD19" t="n">
-        <v>1451.443748</v>
-      </c>
-      <c r="HE19" t="n">
-        <v>330.528266</v>
-      </c>
-      <c r="HF19" t="n">
-        <v>108.68112</v>
-      </c>
-      <c r="HG19" t="n">
-        <v>5019.32</v>
-      </c>
-      <c r="HH19" t="n">
-        <v>734.87</v>
-      </c>
-      <c r="HI19" t="n">
-        <v>660.8367050000001</v>
-      </c>
-      <c r="HJ19" t="n">
-        <v>1007.18</v>
-      </c>
-      <c r="HK19" t="n">
-        <v>-3285.23984</v>
-      </c>
-      <c r="HL19" t="n">
-        <v>2635.23</v>
-      </c>
-      <c r="HM19" t="n">
-        <v>8662.85</v>
-      </c>
-      <c r="HX19" t="n">
-        <v>55390.8214</v>
-      </c>
-      <c r="HY19" t="n">
-        <v>8041.85946</v>
-      </c>
-      <c r="HZ19" t="n">
-        <v>2012.17302</v>
-      </c>
-      <c r="IA19" t="n">
-        <v>72040.11</v>
-      </c>
-      <c r="IB19" t="n">
-        <v>13742.33</v>
-      </c>
-      <c r="IC19" t="n">
-        <v>79784.7481</v>
-      </c>
-      <c r="ID19" t="n">
-        <v>8226.9</v>
-      </c>
-      <c r="IE19" t="n">
-        <v>80701.66800000001</v>
-      </c>
-      <c r="IF19" t="n">
-        <v>21652.28</v>
-      </c>
-      <c r="IG19" t="n">
-        <v>341592.89</v>
-      </c>
-      <c r="IH19" t="n">
-        <v>16.21544915</v>
-      </c>
-      <c r="II19" t="n">
-        <v>2.354223316</v>
-      </c>
-      <c r="IJ19" t="n">
-        <v>0.5890558849999999</v>
-      </c>
-      <c r="IK19" t="n">
-        <v>21.08946413</v>
-      </c>
-      <c r="IL19" t="n">
-        <v>4.02301406</v>
-      </c>
-      <c r="IM19" t="n">
-        <v>23.35667704</v>
-      </c>
-      <c r="IN19" t="n">
-        <v>2.40839322</v>
-      </c>
-      <c r="IO19" t="n">
-        <v>23.6251018</v>
-      </c>
-      <c r="IP19" t="n">
-        <v>6.33862139</v>
-      </c>
-      <c r="IQ19" t="n">
-        <v>100</v>
-      </c>
-      <c r="IR19" t="n">
-        <v>181.86</v>
-      </c>
-      <c r="IS19" t="n">
-        <v>-46.71</v>
-      </c>
-      <c r="IT19" t="n">
-        <v>-5.07</v>
-      </c>
-      <c r="IU19" t="n">
-        <v>-73.05</v>
-      </c>
-      <c r="IV19" t="n">
-        <v>-14.76</v>
-      </c>
-      <c r="IW19" t="n">
-        <v>161.27</v>
-      </c>
-      <c r="IX19" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="IY19" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="IZ19" t="n">
-        <v>6.04</v>
-      </c>
-      <c r="JA19" t="n">
-        <v>268.59</v>
-      </c>
-      <c r="JB19" t="n">
-        <v>181.86</v>
-      </c>
-      <c r="JC19" t="n">
-        <v>-46.71</v>
-      </c>
-      <c r="JD19" t="n">
-        <v>-5.07</v>
-      </c>
-      <c r="JE19" t="n">
-        <v>-73.05</v>
-      </c>
-      <c r="JF19" t="n">
-        <v>-14.76</v>
-      </c>
-      <c r="JG19" t="n">
-        <v>161.27</v>
-      </c>
-      <c r="JH19" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="JI19" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="JJ19" t="n">
-        <v>6.04</v>
-      </c>
-      <c r="JK19" t="n">
-        <v>268.59</v>
-      </c>
-      <c r="JV19" t="n">
-        <v>1738.51</v>
-      </c>
-      <c r="JW19" t="n">
-        <v>3856.71</v>
-      </c>
-      <c r="JX19" t="n">
-        <v>222.93</v>
-      </c>
-      <c r="JY19" t="n">
-        <v>1243.46</v>
-      </c>
-      <c r="JZ19" t="n">
-        <v>155.96</v>
-      </c>
-      <c r="KA19" t="n">
-        <v>2148.79</v>
-      </c>
-      <c r="KB19" t="n">
-        <v>1097.34</v>
-      </c>
-      <c r="KC19" t="n">
-        <v>6744.97</v>
-      </c>
-      <c r="KD19" t="n">
-        <v>942.86</v>
-      </c>
-      <c r="KE19" t="n">
-        <v>18151.53</v>
-      </c>
-      <c r="KF19" t="n">
-        <v>9.57776011</v>
-      </c>
-      <c r="KG19" t="n">
-        <v>21.2472998</v>
-      </c>
-      <c r="KH19" t="n">
-        <v>1.228160932</v>
-      </c>
-      <c r="KI19" t="n">
-        <v>6.85044181</v>
-      </c>
-      <c r="KJ19" t="n">
-        <v>0.859211317</v>
-      </c>
-      <c r="KK19" t="n">
-        <v>11.83806544</v>
-      </c>
-      <c r="KL19" t="n">
-        <v>6.0454408</v>
-      </c>
-      <c r="KM19" t="n">
-        <v>37.1592367</v>
-      </c>
-      <c r="KN19" t="n">
-        <v>5.19438306</v>
-      </c>
-      <c r="KO19" t="n">
-        <v>100</v>
-      </c>
-      <c r="KP19" t="n">
-        <v>998.53</v>
-      </c>
-      <c r="KQ19" t="n">
-        <v>-8.94</v>
-      </c>
-      <c r="KR19" t="n">
-        <v>-2.25</v>
-      </c>
-      <c r="KS19" t="n">
-        <v>11.95</v>
-      </c>
-      <c r="KT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="KU19" t="n">
-        <v>-2.51</v>
-      </c>
-      <c r="KV19" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="KW19" t="n">
-        <v>-57.41</v>
-      </c>
-      <c r="KX19" t="n">
-        <v>95.33</v>
-      </c>
-      <c r="KY19" t="n">
-        <v>1039.77</v>
-      </c>
-      <c r="KZ19" t="n">
-        <v>998.53</v>
-      </c>
-      <c r="LA19" t="n">
-        <v>-8.94</v>
-      </c>
-      <c r="LB19" t="n">
-        <v>-2.25</v>
-      </c>
-      <c r="LC19" t="n">
-        <v>11.95</v>
-      </c>
-      <c r="LD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="LE19" t="n">
-        <v>-2.51</v>
-      </c>
-      <c r="LF19" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="LG19" t="n">
-        <v>-57.41</v>
-      </c>
-      <c r="LH19" t="n">
-        <v>95.33</v>
-      </c>
-      <c r="LI19" t="n">
-        <v>1039.77</v>
-      </c>
-      <c r="LT19" t="n">
-        <v>11558.43</v>
-      </c>
-      <c r="LU19" t="n">
-        <v>101.19</v>
-      </c>
-      <c r="LV19" t="n">
-        <v>43.24</v>
-      </c>
-      <c r="LW19" t="n">
-        <v>5879.44</v>
-      </c>
-      <c r="LX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="LY19" t="n">
-        <v>31.12</v>
-      </c>
-      <c r="LZ19" t="n">
-        <v>2251.03</v>
-      </c>
-      <c r="MA19" t="n">
-        <v>24795.83</v>
-      </c>
-      <c r="MB19" t="n">
-        <v>3813.47</v>
-      </c>
-      <c r="MC19" t="n">
-        <v>48473.75</v>
-      </c>
-      <c r="MD19" t="n">
-        <v>23.8447201</v>
-      </c>
-      <c r="ME19" t="n">
-        <v>0.2087521597</v>
-      </c>
-      <c r="MF19" t="n">
-        <v>0.0892029191</v>
-      </c>
-      <c r="MG19" t="n">
-        <v>12.12912143</v>
-      </c>
-      <c r="MH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="MI19" t="n">
-        <v>0.0641996957</v>
-      </c>
-      <c r="MJ19" t="n">
-        <v>4.64381237</v>
-      </c>
-      <c r="MK19" t="n">
-        <v>51.1531086</v>
-      </c>
-      <c r="ML19" t="n">
-        <v>7.8670827</v>
-      </c>
-      <c r="MM19" t="n">
+      <c r="MI11" t="n">
+        <v>0.06419969571159651</v>
+      </c>
+      <c r="MJ11" t="n">
+        <v>4.64381237267593</v>
+      </c>
+      <c r="MK11" t="n">
+        <v>51.1531086412749</v>
+      </c>
+      <c r="ML11" t="n">
+        <v>7.86708269939916</v>
+      </c>
+      <c r="MM11" t="n">
         <v>100</v>
       </c>
     </row>

--- a/output/latest/SIFA_DATA_latest.xlsx
+++ b/output/latest/SIFA_DATA_latest.xlsx
@@ -4203,36 +4203,6 @@
       <c r="U4" t="n">
         <v>80868.03999999999</v>
       </c>
-      <c r="V4" t="n">
-        <v>-3.23083364820021</v>
-      </c>
-      <c r="W4" t="n">
-        <v>31.6123166833399</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-3.94380367943874</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>40.0760053044441</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-16.6352244965996</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>26.3989582155076</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>3.18358154840899</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>12.8899718532315</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>9.649028219306389</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>100</v>
-      </c>
       <c r="AF4" t="n">
         <v>683449.042811719</v>
       </c>
